--- a/Financial Analysis/NFLX.xlsx
+++ b/Financial Analysis/NFLX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6FC23E-7EB2-4143-9DD5-80178DCD70F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3972666-C021-4840-BB16-DC2C31A91F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="639" activeTab="1" xr2:uid="{0F574E5A-2072-44A4-9588-9F3B274273C1}"/>
   </bookViews>
@@ -1085,14 +1085,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="17">
-        <v>996.3</v>
+        <v>1194.18</v>
       </c>
       <c r="E3" s="4">
-        <v>45769</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45782</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45854</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>424124.91</v>
+        <v>508362.42600000004</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>430770.91</v>
+        <v>515008.42600000004</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="CE52" s="17">
         <f>Main!D3</f>
-        <v>996.3</v>
+        <v>1194.18</v>
       </c>
     </row>
     <row r="53" spans="2:83">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="CE53" s="10">
         <f>CE51/CE52-1</f>
-        <v>-0.45650787239829793</v>
+        <v>-0.5465665086255207</v>
       </c>
     </row>
     <row r="54" spans="2:83">

--- a/Financial Analysis/NFLX.xlsx
+++ b/Financial Analysis/NFLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3972666-C021-4840-BB16-DC2C31A91F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC87849C-6BE5-4A09-9270-ACBC788B334B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="639" activeTab="1" xr2:uid="{0F574E5A-2072-44A4-9588-9F3B274273C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="639" xr2:uid="{0F574E5A-2072-44A4-9588-9F3B274273C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="141">
   <si>
     <t>NFLX</t>
   </si>
@@ -467,19 +467,22 @@
     <t>Q424</t>
   </si>
   <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q225 8K</t>
+  </si>
+  <si>
     <t>Overvalued</t>
-  </si>
-  <si>
-    <t>Q125</t>
-  </si>
-  <si>
-    <t>Q225</t>
-  </si>
-  <si>
-    <t>Q325</t>
-  </si>
-  <si>
-    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -662,14 +665,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -686,7 +689,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="31737300" y="0"/>
+          <a:off x="32948880" y="0"/>
           <a:ext cx="0" cy="10896600"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1085,17 +1088,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="17">
-        <v>1194.18</v>
+        <v>1230.08</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="G3" s="4">
-        <v>45854</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -1103,10 +1106,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>425.7</v>
+        <f>425.2</f>
+        <v>425.2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -1115,7 +1119,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>508362.42600000004</v>
+        <v>523030.01599999995</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1123,8 +1127,8 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>7199.8+1171.1</f>
-        <v>8370.9</v>
+        <f>8117.4+213.1</f>
+        <v>8330.5</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>136</v>
@@ -1135,8 +1139,8 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>1005.9+14011</f>
-        <v>15016.9</v>
+        <f>1728.4+14453.2</f>
+        <v>16181.6</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>136</v>
@@ -1148,7 +1152,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>-6646</v>
+        <v>-7851.1</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>515008.42600000004</v>
+        <v>530881.11599999992</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -1328,16 +1332,16 @@
         <v>134</v>
       </c>
       <c r="AY2" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AZ2" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="AZ2" s="5" t="s">
+      <c r="BA2" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="BA2" s="5" t="s">
+      <c r="BB2" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="BB2" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="BC2" s="5"/>
       <c r="BD2">
@@ -5146,16 +5150,15 @@
         <v>10542.8</v>
       </c>
       <c r="AZ26" s="16">
-        <f>AV26*1.16</f>
-        <v>11088.787999999999</v>
+        <v>11079.2</v>
       </c>
       <c r="BA26" s="16">
         <f>AW26*1.13</f>
         <v>11101.911</v>
       </c>
       <c r="BB26" s="16">
-        <f>AX26*1.06</f>
-        <v>10861.29</v>
+        <f>AX26*1.12</f>
+        <v>11476.080000000002</v>
       </c>
       <c r="BD26" s="16">
         <v>3204.5770000000002</v>
@@ -5213,47 +5216,47 @@
       </c>
       <c r="BR26" s="16">
         <f>SUM(AY26:BB26)</f>
-        <v>43594.788999999997</v>
+        <v>44199.991000000002</v>
       </c>
       <c r="BS26" s="16">
-        <f>BR26*1.08</f>
-        <v>47082.37212</v>
+        <f>BR26*1.09</f>
+        <v>48177.990190000004</v>
       </c>
       <c r="BT26" s="16">
-        <f>BS26*1.05</f>
-        <v>49436.490726000004</v>
+        <f>BS26*1.06</f>
+        <v>51068.669601400004</v>
       </c>
       <c r="BU26" s="16">
-        <f>BT26*1.03</f>
-        <v>50919.585447780002</v>
+        <f>BT26*1.05</f>
+        <v>53622.103081470006</v>
       </c>
       <c r="BV26" s="16">
-        <f>BU26*1.02</f>
-        <v>51937.9771567356</v>
+        <f>BU26*1.04</f>
+        <v>55766.987204728808</v>
       </c>
       <c r="BW26" s="16">
-        <f>BV26*1.01</f>
-        <v>52457.356928302957</v>
+        <f>BV26*1.03</f>
+        <v>57439.99682087067</v>
       </c>
       <c r="BX26" s="16">
-        <f t="shared" ref="BX26:CB26" si="118">BW26*1.01</f>
-        <v>52981.930497585985</v>
+        <f t="shared" ref="BX26:CB26" si="118">BW26*1.02</f>
+        <v>58588.796757288088</v>
       </c>
       <c r="BY26" s="16">
         <f t="shared" si="118"/>
-        <v>53511.749802561848</v>
+        <v>59760.572692433852</v>
       </c>
       <c r="BZ26" s="16">
         <f t="shared" si="118"/>
-        <v>54046.867300587466</v>
+        <v>60955.784146282531</v>
       </c>
       <c r="CA26" s="16">
         <f t="shared" si="118"/>
-        <v>54587.335973593341</v>
+        <v>62174.899829208181</v>
       </c>
       <c r="CB26" s="16">
         <f t="shared" si="118"/>
-        <v>55133.209333329272</v>
+        <v>63418.397825792345</v>
       </c>
     </row>
     <row r="27" spans="2:80">
@@ -5415,16 +5418,15 @@
         <v>5263.1</v>
       </c>
       <c r="AZ27" s="2">
-        <f t="shared" ref="AZ27:BB27" si="120">AZ26-AZ28</f>
-        <v>5766.1697599999998</v>
+        <v>5325.3</v>
       </c>
       <c r="BA27" s="2">
-        <f t="shared" si="120"/>
-        <v>5772.9937200000004</v>
+        <f t="shared" ref="BA27:BB27" si="120">BA26-BA28</f>
+        <v>5439.9363899999998</v>
       </c>
       <c r="BB27" s="2">
         <f t="shared" si="120"/>
-        <v>5865.0965999999999</v>
+        <v>6082.3224000000009</v>
       </c>
       <c r="BD27" s="2">
         <v>2039.9010000000001</v>
@@ -5482,47 +5484,47 @@
       </c>
       <c r="BR27" s="2">
         <f>SUM(AY27:BB27)</f>
-        <v>22667.360080000002</v>
+        <v>22110.658790000001</v>
       </c>
       <c r="BS27" s="2">
         <f t="shared" ref="BS27:BW27" si="124">BS26-BS28</f>
-        <v>23541.18606</v>
+        <v>23125.435291199999</v>
       </c>
       <c r="BT27" s="2">
         <f t="shared" si="124"/>
-        <v>23729.515548480002</v>
+        <v>24002.274712658</v>
       </c>
       <c r="BU27" s="2">
         <f t="shared" si="124"/>
-        <v>23932.2051604566</v>
+        <v>24666.167417476201</v>
       </c>
       <c r="BV27" s="2">
         <f t="shared" si="124"/>
-        <v>23891.469492098375</v>
+        <v>25095.144242127961</v>
       </c>
       <c r="BW27" s="2">
         <f t="shared" si="124"/>
-        <v>24130.384187019357</v>
+        <v>25847.998569391799</v>
       </c>
       <c r="BX27" s="2">
         <f t="shared" ref="BX27:CB27" si="125">BX26-BX28</f>
-        <v>24371.688028889552</v>
+        <v>26364.958540779637</v>
       </c>
       <c r="BY27" s="2">
         <f t="shared" si="125"/>
-        <v>24615.404909178447</v>
+        <v>26892.25771159523</v>
       </c>
       <c r="BZ27" s="2">
         <f t="shared" si="125"/>
-        <v>24861.558958270234</v>
+        <v>27430.102865827139</v>
       </c>
       <c r="CA27" s="2">
         <f t="shared" si="125"/>
-        <v>25110.174547852934</v>
+        <v>27978.704923143676</v>
       </c>
       <c r="CB27" s="2">
         <f t="shared" si="125"/>
-        <v>25361.276293331463</v>
+        <v>28538.279021606555</v>
       </c>
     </row>
     <row r="28" spans="2:80" s="1" customFormat="1">
@@ -5702,7 +5704,7 @@
         <v>3610.9000000000005</v>
       </c>
       <c r="AT28" s="16">
-        <f t="shared" ref="AT28:AY28" si="135">AT26-AT27</f>
+        <f t="shared" ref="AT28:AZ28" si="135">AT26-AT27</f>
         <v>3525.2999999999993</v>
       </c>
       <c r="AU28" s="16">
@@ -5726,16 +5728,16 @@
         <v>5279.6999999999989</v>
       </c>
       <c r="AZ28" s="16">
-        <f t="shared" ref="AZ28:BA28" si="136">AZ26*0.48</f>
-        <v>5322.6182399999989</v>
+        <f t="shared" si="135"/>
+        <v>5753.9000000000005</v>
       </c>
       <c r="BA28" s="16">
-        <f t="shared" si="136"/>
-        <v>5328.9172799999997</v>
+        <f>BA26*0.51</f>
+        <v>5661.9746100000002</v>
       </c>
       <c r="BB28" s="16">
-        <f>BB26*0.46</f>
-        <v>4996.193400000001</v>
+        <f>BB26*0.47</f>
+        <v>5393.7576000000008</v>
       </c>
       <c r="BD28" s="16">
         <f>BD26-BD27</f>
@@ -5758,84 +5760,84 @@
         <v>2188.0300000000007</v>
       </c>
       <c r="BI28" s="16">
-        <f t="shared" ref="BI28:BR28" si="137">BI26-BI27</f>
+        <f t="shared" ref="BI28:BR28" si="136">BI26-BI27</f>
         <v>2631.9942000000001</v>
       </c>
       <c r="BJ28" s="16">
+        <f t="shared" si="136"/>
+        <v>3659.5239999999994</v>
+      </c>
+      <c r="BK28" s="16">
+        <f t="shared" si="136"/>
+        <v>5827.2133200000007</v>
+      </c>
+      <c r="BL28" s="16">
+        <f t="shared" si="136"/>
+        <v>7713.7999999999993</v>
+      </c>
+      <c r="BM28" s="16">
+        <f t="shared" si="136"/>
+        <v>9715.7999999999993</v>
+      </c>
+      <c r="BN28" s="16">
+        <f t="shared" si="136"/>
+        <v>12365.899999999998</v>
+      </c>
+      <c r="BO28" s="16">
+        <f t="shared" si="136"/>
+        <v>12447.199999999997</v>
+      </c>
+      <c r="BP28" s="16">
+        <f t="shared" si="136"/>
+        <v>14007.900000000001</v>
+      </c>
+      <c r="BQ28" s="16">
+        <f t="shared" si="136"/>
+        <v>17962.399999999994</v>
+      </c>
+      <c r="BR28" s="16">
+        <f t="shared" si="136"/>
+        <v>22089.33221</v>
+      </c>
+      <c r="BS28" s="16">
+        <f>BS26*0.52</f>
+        <v>25052.554898800005</v>
+      </c>
+      <c r="BT28" s="16">
+        <f>BT26*0.53</f>
+        <v>27066.394888742005</v>
+      </c>
+      <c r="BU28" s="16">
+        <f>BU26*0.54</f>
+        <v>28955.935663993805</v>
+      </c>
+      <c r="BV28" s="16">
+        <f>BV26*0.55</f>
+        <v>30671.842962600847</v>
+      </c>
+      <c r="BW28" s="16">
+        <f t="shared" ref="BW28:CB28" si="137">BW26*0.55</f>
+        <v>31591.998251478872</v>
+      </c>
+      <c r="BX28" s="16">
         <f t="shared" si="137"/>
-        <v>3659.5239999999994</v>
-      </c>
-      <c r="BK28" s="16">
+        <v>32223.838216508451</v>
+      </c>
+      <c r="BY28" s="16">
         <f t="shared" si="137"/>
-        <v>5827.2133200000007</v>
-      </c>
-      <c r="BL28" s="16">
+        <v>32868.314980838622</v>
+      </c>
+      <c r="BZ28" s="16">
         <f t="shared" si="137"/>
-        <v>7713.7999999999993</v>
-      </c>
-      <c r="BM28" s="16">
+        <v>33525.681280455392</v>
+      </c>
+      <c r="CA28" s="16">
         <f t="shared" si="137"/>
-        <v>9715.7999999999993</v>
-      </c>
-      <c r="BN28" s="16">
+        <v>34196.194906064506</v>
+      </c>
+      <c r="CB28" s="16">
         <f t="shared" si="137"/>
-        <v>12365.899999999998</v>
-      </c>
-      <c r="BO28" s="16">
-        <f t="shared" si="137"/>
-        <v>12447.199999999997</v>
-      </c>
-      <c r="BP28" s="16">
-        <f t="shared" si="137"/>
-        <v>14007.900000000001</v>
-      </c>
-      <c r="BQ28" s="16">
-        <f t="shared" si="137"/>
-        <v>17962.399999999994</v>
-      </c>
-      <c r="BR28" s="16">
-        <f t="shared" si="137"/>
-        <v>20927.428919999995</v>
-      </c>
-      <c r="BS28" s="16">
-        <f>BS26*0.5</f>
-        <v>23541.18606</v>
-      </c>
-      <c r="BT28" s="16">
-        <f>BT26*0.52</f>
-        <v>25706.975177520002</v>
-      </c>
-      <c r="BU28" s="16">
-        <f>BU26*0.53</f>
-        <v>26987.380287323402</v>
-      </c>
-      <c r="BV28" s="16">
-        <f>BV26*0.54</f>
-        <v>28046.507664637225</v>
-      </c>
-      <c r="BW28" s="16">
-        <f t="shared" ref="BW28:CB28" si="138">BW26*0.54</f>
-        <v>28326.9727412836</v>
-      </c>
-      <c r="BX28" s="16">
-        <f t="shared" si="138"/>
-        <v>28610.242468696433</v>
-      </c>
-      <c r="BY28" s="16">
-        <f t="shared" si="138"/>
-        <v>28896.344893383401</v>
-      </c>
-      <c r="BZ28" s="16">
-        <f t="shared" si="138"/>
-        <v>29185.308342317232</v>
-      </c>
-      <c r="CA28" s="16">
-        <f t="shared" si="138"/>
-        <v>29477.161425740407</v>
-      </c>
-      <c r="CB28" s="16">
-        <f t="shared" si="138"/>
-        <v>29771.93303999781</v>
+        <v>34880.118804185789</v>
       </c>
     </row>
     <row r="29" spans="2:80">
@@ -5883,15 +5885,15 @@
         <v>227.46719999999999</v>
       </c>
       <c r="P29" s="2">
-        <f t="shared" ref="P29:R29" si="139">P26*0.12</f>
+        <f t="shared" ref="P29:R29" si="138">P26*0.12</f>
         <v>231.82919999999999</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>239.23199999999997</v>
       </c>
       <c r="R29" s="2">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>258.56039999999996</v>
       </c>
       <c r="S29" s="2">
@@ -5997,16 +5999,15 @@
         <v>688.4</v>
       </c>
       <c r="AZ29" s="2">
-        <f t="shared" ref="AZ29:BA29" si="140">AZ26*0.07</f>
-        <v>776.21515999999997</v>
+        <v>713.3</v>
       </c>
       <c r="BA29" s="2">
-        <f t="shared" si="140"/>
+        <f t="shared" ref="BA29" si="139">BA26*0.07</f>
         <v>777.13377000000003</v>
       </c>
       <c r="BB29" s="2">
         <f>BB26*0.1</f>
-        <v>1086.1290000000001</v>
+        <v>1147.6080000000002</v>
       </c>
       <c r="BD29" s="2">
         <v>402.63799999999998</v>
@@ -6031,15 +6032,15 @@
         <v>957.08879999999988</v>
       </c>
       <c r="BJ29" s="15">
-        <f t="shared" ref="BJ29:BJ31" si="141">SUM(S29:V29)</f>
+        <f t="shared" ref="BJ29:BJ31" si="140">SUM(S29:V29)</f>
         <v>1436.3000000000002</v>
       </c>
       <c r="BK29" s="15">
-        <f t="shared" ref="BK29:BK31" si="142">SUM(W29:Z29)</f>
+        <f t="shared" ref="BK29:BK31" si="141">SUM(W29:Z29)</f>
         <v>2369.5</v>
       </c>
       <c r="BL29" s="15">
-        <f t="shared" ref="BL29:BL31" si="143">SUM(AA29:AD29)</f>
+        <f t="shared" ref="BL29:BL31" si="142">SUM(AA29:AD29)</f>
         <v>2652.5</v>
       </c>
       <c r="BM29" s="15">
@@ -6064,47 +6065,47 @@
       </c>
       <c r="BR29" s="2">
         <f>SUM(AY29:BB29)</f>
-        <v>3327.8779299999997</v>
+        <v>3326.4417699999999</v>
       </c>
       <c r="BS29" s="2">
-        <f t="shared" ref="BS29:CB29" si="144">BS26*0.07</f>
-        <v>3295.7660484000003</v>
+        <f t="shared" ref="BS29:CB29" si="143">BS26*0.07</f>
+        <v>3372.4593133000008</v>
       </c>
       <c r="BT29" s="2">
-        <f t="shared" si="144"/>
-        <v>3460.5543508200008</v>
+        <f t="shared" si="143"/>
+        <v>3574.8068720980004</v>
       </c>
       <c r="BU29" s="2">
-        <f t="shared" si="144"/>
-        <v>3564.3709813446003</v>
+        <f t="shared" si="143"/>
+        <v>3753.5472157029008</v>
       </c>
       <c r="BV29" s="2">
-        <f t="shared" si="144"/>
-        <v>3635.6584009714925</v>
+        <f t="shared" si="143"/>
+        <v>3903.689104331017</v>
       </c>
       <c r="BW29" s="2">
-        <f t="shared" si="144"/>
-        <v>3672.0149849812074</v>
+        <f t="shared" si="143"/>
+        <v>4020.7997774609471</v>
       </c>
       <c r="BX29" s="2">
-        <f t="shared" si="144"/>
-        <v>3708.7351348310194</v>
+        <f t="shared" si="143"/>
+        <v>4101.2157730101662</v>
       </c>
       <c r="BY29" s="2">
-        <f t="shared" si="144"/>
-        <v>3745.8224861793296</v>
+        <f t="shared" si="143"/>
+        <v>4183.2400884703702</v>
       </c>
       <c r="BZ29" s="2">
-        <f t="shared" si="144"/>
-        <v>3783.2807110411231</v>
+        <f t="shared" si="143"/>
+        <v>4266.9048902397772</v>
       </c>
       <c r="CA29" s="2">
-        <f t="shared" si="144"/>
-        <v>3821.1135181515342</v>
+        <f t="shared" si="143"/>
+        <v>4352.2429880445734</v>
       </c>
       <c r="CB29" s="2">
-        <f t="shared" si="144"/>
-        <v>3859.3246533330494</v>
+        <f t="shared" si="143"/>
+        <v>4439.2878478054645</v>
       </c>
     </row>
     <row r="30" spans="2:80">
@@ -6152,15 +6153,15 @@
         <v>189.55600000000001</v>
       </c>
       <c r="P30" s="2">
-        <f t="shared" ref="P30:R30" si="145">P26*0.1</f>
+        <f t="shared" ref="P30:R30" si="144">P26*0.1</f>
         <v>193.191</v>
       </c>
       <c r="Q30" s="2">
-        <f t="shared" si="145"/>
+        <f t="shared" si="144"/>
         <v>199.36</v>
       </c>
       <c r="R30" s="2">
-        <f t="shared" si="145"/>
+        <f t="shared" si="144"/>
         <v>215.46699999999998</v>
       </c>
       <c r="S30" s="2">
@@ -6266,16 +6267,15 @@
         <v>822.8</v>
       </c>
       <c r="AZ30" s="2">
-        <f>AV30*1.13</f>
-        <v>803.76899999999989</v>
+        <v>824.7</v>
       </c>
       <c r="BA30" s="2">
-        <f>AW30*1.09</f>
-        <v>801.25900000000013</v>
+        <f>AW30*1.13</f>
+        <v>830.6629999999999</v>
       </c>
       <c r="BB30" s="2">
-        <f>AX30*1.05</f>
-        <v>815.32500000000005</v>
+        <f>AX30*1.1</f>
+        <v>854.15000000000009</v>
       </c>
       <c r="BD30" s="2">
         <v>259.03300000000002</v>
@@ -6300,15 +6300,15 @@
         <v>797.57399999999996</v>
       </c>
       <c r="BJ30" s="15">
+        <f t="shared" si="140"/>
+        <v>953.7</v>
+      </c>
+      <c r="BK30" s="15">
         <f t="shared" si="141"/>
-        <v>953.7</v>
-      </c>
-      <c r="BK30" s="15">
+        <v>1221.8</v>
+      </c>
+      <c r="BL30" s="15">
         <f t="shared" si="142"/>
-        <v>1221.8</v>
-      </c>
-      <c r="BL30" s="15">
-        <f t="shared" si="143"/>
         <v>1545</v>
       </c>
       <c r="BM30" s="15">
@@ -6333,47 +6333,47 @@
       </c>
       <c r="BR30" s="2">
         <f>SUM(AY30:BB30)</f>
-        <v>3243.1530000000002</v>
+        <v>3332.3130000000001</v>
       </c>
       <c r="BS30" s="2">
-        <f>BR30*1.05</f>
-        <v>3405.3106500000004</v>
+        <f>BR30*1.07</f>
+        <v>3565.5749100000003</v>
       </c>
       <c r="BT30" s="2">
-        <f>BS30*1.03</f>
-        <v>3507.4699695000004</v>
+        <f>BS30*1.04</f>
+        <v>3708.1979064000002</v>
       </c>
       <c r="BU30" s="2">
-        <f>BT30*1.02</f>
-        <v>3577.6193688900003</v>
+        <f>BT30*1.03</f>
+        <v>3819.4438435920001</v>
       </c>
       <c r="BV30" s="2">
-        <f t="shared" ref="BV30:CB31" si="146">BU30*1.01</f>
-        <v>3613.3955625789004</v>
+        <f>BU30*1.02</f>
+        <v>3895.8327204638404</v>
       </c>
       <c r="BW30" s="2">
-        <f t="shared" si="146"/>
-        <v>3649.5295182046893</v>
+        <f t="shared" ref="BW30:CB31" si="145">BV30*1.01</f>
+        <v>3934.7910476684788</v>
       </c>
       <c r="BX30" s="2">
-        <f t="shared" si="146"/>
-        <v>3686.0248133867362</v>
+        <f t="shared" si="145"/>
+        <v>3974.1389581451635</v>
       </c>
       <c r="BY30" s="2">
-        <f t="shared" si="146"/>
-        <v>3722.8850615206038</v>
+        <f t="shared" si="145"/>
+        <v>4013.8803477266151</v>
       </c>
       <c r="BZ30" s="2">
-        <f t="shared" si="146"/>
-        <v>3760.1139121358101</v>
+        <f t="shared" si="145"/>
+        <v>4054.0191512038814</v>
       </c>
       <c r="CA30" s="2">
-        <f t="shared" si="146"/>
-        <v>3797.7150512571684</v>
+        <f t="shared" si="145"/>
+        <v>4094.5593427159201</v>
       </c>
       <c r="CB30" s="2">
-        <f t="shared" si="146"/>
-        <v>3835.6922017697402</v>
+        <f t="shared" si="145"/>
+        <v>4135.5049361430792</v>
       </c>
     </row>
     <row r="31" spans="2:80">
@@ -6421,15 +6421,15 @@
         <v>113.7336</v>
       </c>
       <c r="P31" s="2">
-        <f t="shared" ref="P31:R31" si="147">P26*0.06</f>
+        <f t="shared" ref="P31:R31" si="146">P26*0.06</f>
         <v>115.91459999999999</v>
       </c>
       <c r="Q31" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="146"/>
         <v>119.61599999999999</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="146"/>
         <v>129.28019999999998</v>
       </c>
       <c r="S31" s="2">
@@ -6535,15 +6535,14 @@
         <v>421.5</v>
       </c>
       <c r="AZ31" s="2">
-        <f t="shared" ref="AZ31:BB31" si="148">AV31*1.03</f>
-        <v>439.81</v>
+        <v>441.2</v>
       </c>
       <c r="BA31" s="2">
-        <f t="shared" si="148"/>
+        <f t="shared" ref="BA31:BB31" si="147">AW31*1.03</f>
         <v>429.92199999999997</v>
       </c>
       <c r="BB31" s="2">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>467.31099999999998</v>
       </c>
       <c r="BD31" s="2">
@@ -6569,15 +6568,15 @@
         <v>478.54439999999994</v>
       </c>
       <c r="BJ31" s="15">
+        <f t="shared" si="140"/>
+        <v>431</v>
+      </c>
+      <c r="BK31" s="15">
         <f t="shared" si="141"/>
-        <v>431</v>
-      </c>
-      <c r="BK31" s="15">
+        <v>630.29999999999995</v>
+      </c>
+      <c r="BL31" s="15">
         <f t="shared" si="142"/>
-        <v>630.29999999999995</v>
-      </c>
-      <c r="BL31" s="15">
-        <f t="shared" si="143"/>
         <v>914.40000000000009</v>
       </c>
       <c r="BM31" s="15">
@@ -6602,47 +6601,47 @@
       </c>
       <c r="BR31" s="2">
         <f>SUM(AY31:BB31)</f>
-        <v>1758.5429999999999</v>
+        <v>1759.933</v>
       </c>
       <c r="BS31" s="2">
         <f>BR31*1.02</f>
-        <v>1793.7138599999998</v>
+        <v>1795.13166</v>
       </c>
       <c r="BT31" s="2">
         <f>BS31*1.02</f>
-        <v>1829.5881371999999</v>
+        <v>1831.0342932000001</v>
       </c>
       <c r="BU31" s="2">
-        <f t="shared" ref="BU31" si="149">BT31*1.01</f>
-        <v>1847.8840185719998</v>
+        <f>BT31*1.02</f>
+        <v>1867.6549790640001</v>
       </c>
       <c r="BV31" s="2">
-        <f t="shared" si="146"/>
-        <v>1866.3628587577198</v>
+        <f>BU31*1.02</f>
+        <v>1905.0080786452802</v>
       </c>
       <c r="BW31" s="2">
-        <f t="shared" si="146"/>
-        <v>1885.026487345297</v>
+        <f t="shared" si="145"/>
+        <v>1924.058159431733</v>
       </c>
       <c r="BX31" s="2">
-        <f t="shared" si="146"/>
-        <v>1903.87675221875</v>
+        <f t="shared" si="145"/>
+        <v>1943.2987410260503</v>
       </c>
       <c r="BY31" s="2">
-        <f t="shared" si="146"/>
-        <v>1922.9155197409375</v>
+        <f t="shared" si="145"/>
+        <v>1962.7317284363107</v>
       </c>
       <c r="BZ31" s="2">
-        <f t="shared" si="146"/>
-        <v>1942.144674938347</v>
+        <f t="shared" si="145"/>
+        <v>1982.3590457206737</v>
       </c>
       <c r="CA31" s="2">
-        <f t="shared" si="146"/>
-        <v>1961.5661216877304</v>
+        <f t="shared" si="145"/>
+        <v>2002.1826361778806</v>
       </c>
       <c r="CB31" s="2">
-        <f t="shared" si="146"/>
-        <v>1981.1817829046076</v>
+        <f t="shared" si="145"/>
+        <v>2022.2044625396593</v>
       </c>
     </row>
     <row r="32" spans="2:80" s="1" customFormat="1">
@@ -6650,212 +6649,212 @@
         <v>32</v>
       </c>
       <c r="C32" s="7">
-        <f t="shared" ref="C32:N32" si="150">C28-C29-C30-C31</f>
+        <f t="shared" ref="C32:N32" si="148">C28-C29-C30-C31</f>
         <v>31.82200000000001</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>57.117000000000097</v>
       </c>
       <c r="E32" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>57.120000000000033</v>
       </c>
       <c r="F32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>82.288000000000011</v>
       </c>
       <c r="G32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>97.594999999999885</v>
       </c>
       <c r="H32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>129.60000000000014</v>
       </c>
       <c r="I32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>110.40700000000001</v>
       </c>
       <c r="J32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>65.046000000000078</v>
       </c>
       <c r="K32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>97.456000000000046</v>
       </c>
       <c r="L32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>74.835000000000008</v>
       </c>
       <c r="M32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>73.640999999999963</v>
       </c>
       <c r="N32" s="16">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>59.891000000000219</v>
       </c>
       <c r="O32" s="16">
-        <f t="shared" ref="O32" si="151">O28-O29-O30-O31</f>
+        <f t="shared" ref="O32" si="149">O28-O29-O30-O31</f>
         <v>94.77800000000002</v>
       </c>
       <c r="P32" s="16">
-        <f t="shared" ref="P32" si="152">P28-P29-P30-P31</f>
+        <f t="shared" ref="P32" si="150">P28-P29-P30-P31</f>
         <v>96.595500000000001</v>
       </c>
       <c r="Q32" s="16">
-        <f t="shared" ref="Q32" si="153">Q28-Q29-Q30-Q31</f>
+        <f t="shared" ref="Q32" si="151">Q28-Q29-Q30-Q31</f>
         <v>99.680000000000064</v>
       </c>
       <c r="R32" s="16">
-        <f t="shared" ref="R32:S32" si="154">R28-R29-R30-R31</f>
+        <f t="shared" ref="R32:S32" si="152">R28-R29-R30-R31</f>
         <v>107.73349999999999</v>
       </c>
       <c r="S32" s="16">
-        <f t="shared" si="154"/>
+        <f t="shared" si="152"/>
         <v>258.10000000000019</v>
       </c>
       <c r="T32" s="16">
-        <f t="shared" ref="T32:V32" si="155">T28-T29-T30-T31</f>
+        <f t="shared" ref="T32:V32" si="153">T28-T29-T30-T31</f>
         <v>128.32000000000014</v>
       </c>
       <c r="U32" s="16">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>207.69199999999984</v>
       </c>
       <c r="V32" s="16">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>244.41200000000001</v>
       </c>
       <c r="W32" s="16">
-        <f t="shared" ref="W32" si="156">W28-W29-W30-W31</f>
+        <f t="shared" ref="W32" si="154">W28-W29-W30-W31</f>
         <v>447.57600000000019</v>
       </c>
       <c r="X32" s="16">
-        <f t="shared" ref="X32" si="157">X28-X29-X30-X31</f>
+        <f t="shared" ref="X32" si="155">X28-X29-X30-X31</f>
         <v>461.79519999999985</v>
       </c>
       <c r="Y32" s="16">
-        <f t="shared" ref="Y32:Z32" si="158">Y28-Y29-Y30-Y31</f>
+        <f t="shared" ref="Y32:Z32" si="156">Y28-Y29-Y30-Y31</f>
         <v>480.41252000000009</v>
       </c>
       <c r="Z32" s="16">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>215.82960000000111</v>
       </c>
       <c r="AA32" s="16">
-        <f t="shared" ref="AA32" si="159">AA28-AA29-AA30-AA31</f>
+        <f t="shared" ref="AA32" si="157">AA28-AA29-AA30-AA31</f>
         <v>459.00000000000023</v>
       </c>
       <c r="AB32" s="16">
-        <f t="shared" ref="AB32" si="160">AB28-AB29-AB30-AB31</f>
+        <f t="shared" ref="AB32" si="158">AB28-AB29-AB30-AB31</f>
         <v>706.2</v>
       </c>
       <c r="AC32" s="16">
-        <f t="shared" ref="AC32:AD32" si="161">AC28-AC29-AC30-AC31</f>
+        <f t="shared" ref="AC32:AD32" si="159">AC28-AC29-AC30-AC31</f>
         <v>988.3</v>
       </c>
       <c r="AD32" s="16">
-        <f t="shared" si="161"/>
+        <f t="shared" si="159"/>
         <v>458.3999999999989</v>
       </c>
       <c r="AE32" s="16">
-        <f t="shared" ref="AE32:AM32" si="162">AE28-AE29-AE30-AE31</f>
+        <f t="shared" ref="AE32:AM32" si="160">AE28-AE29-AE30-AE31</f>
         <v>958.60000000000025</v>
       </c>
       <c r="AF32" s="16">
+        <f t="shared" si="160"/>
+        <v>1357.9</v>
+      </c>
+      <c r="AG32" s="16">
+        <f t="shared" si="160"/>
+        <v>1311.1999999999998</v>
+      </c>
+      <c r="AH32" s="16">
+        <f t="shared" si="160"/>
+        <v>954</v>
+      </c>
+      <c r="AI32" s="16">
+        <f t="shared" si="160"/>
+        <v>1960.6000000000001</v>
+      </c>
+      <c r="AJ32" s="16">
+        <f t="shared" si="160"/>
+        <v>1847.7</v>
+      </c>
+      <c r="AK32" s="16">
+        <f t="shared" si="160"/>
+        <v>1755.2999999999995</v>
+      </c>
+      <c r="AL32" s="16">
+        <f t="shared" ref="AL32" si="161">AL28-AL29-AL30-AL31</f>
+        <v>631.69999999999982</v>
+      </c>
+      <c r="AM32" s="16">
+        <f t="shared" si="160"/>
+        <v>1971.7000000000003</v>
+      </c>
+      <c r="AN32" s="16">
+        <f t="shared" ref="AN32:AO32" si="162">AN28-AN29-AN30-AN31</f>
+        <v>1578.2000000000003</v>
+      </c>
+      <c r="AO32" s="16">
         <f t="shared" si="162"/>
-        <v>1357.9</v>
-      </c>
-      <c r="AG32" s="16">
-        <f t="shared" si="162"/>
-        <v>1311.1999999999998</v>
-      </c>
-      <c r="AH32" s="16">
-        <f t="shared" si="162"/>
-        <v>954</v>
-      </c>
-      <c r="AI32" s="16">
-        <f t="shared" si="162"/>
-        <v>1960.6000000000001</v>
-      </c>
-      <c r="AJ32" s="16">
-        <f t="shared" si="162"/>
-        <v>1847.7</v>
-      </c>
-      <c r="AK32" s="16">
-        <f t="shared" si="162"/>
-        <v>1755.2999999999995</v>
-      </c>
-      <c r="AL32" s="16">
-        <f t="shared" ref="AL32" si="163">AL28-AL29-AL30-AL31</f>
-        <v>631.69999999999982</v>
-      </c>
-      <c r="AM32" s="16">
-        <f t="shared" si="162"/>
-        <v>1971.7000000000003</v>
-      </c>
-      <c r="AN32" s="16">
-        <f t="shared" ref="AN32:AO32" si="164">AN28-AN29-AN30-AN31</f>
-        <v>1578.2000000000003</v>
-      </c>
-      <c r="AO32" s="16">
-        <f t="shared" si="164"/>
         <v>1533.0000000000005</v>
       </c>
       <c r="AP32" s="16">
-        <f t="shared" ref="AP32:AR32" si="165">AP28-AP29-AP30-AP31</f>
+        <f t="shared" ref="AP32:AR32" si="163">AP28-AP29-AP30-AP31</f>
         <v>549.90000000000066</v>
       </c>
       <c r="AQ32" s="16">
-        <f t="shared" ref="AQ32" si="166">AQ28-AQ29-AQ30-AQ31</f>
+        <f t="shared" ref="AQ32" si="164">AQ28-AQ29-AQ30-AQ31</f>
         <v>1714.2999999999997</v>
       </c>
       <c r="AR32" s="16">
-        <f t="shared" si="165"/>
+        <f t="shared" si="163"/>
         <v>1827.1000000000004</v>
       </c>
       <c r="AS32" s="16">
-        <f t="shared" ref="AS32" si="167">AS28-AS29-AS30-AS31</f>
+        <f t="shared" ref="AS32" si="165">AS28-AS29-AS30-AS31</f>
         <v>1916.400000000001</v>
       </c>
       <c r="AT32" s="16">
-        <f t="shared" ref="AT32:BB32" si="168">AT28-AT29-AT30-AT31</f>
+        <f t="shared" ref="AT32:BB32" si="166">AT28-AT29-AT30-AT31</f>
         <v>1496.0999999999995</v>
       </c>
       <c r="AU32" s="16">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>2632.4999999999991</v>
       </c>
       <c r="AV32" s="16">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>2602.7999999999993</v>
       </c>
       <c r="AW32" s="16">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>2909.400000000001</v>
       </c>
       <c r="AX32" s="16">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>2272.7000000000007</v>
       </c>
       <c r="AY32" s="16">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>3346.9999999999991</v>
       </c>
       <c r="AZ32" s="16">
-        <f t="shared" si="168"/>
-        <v>3302.8240799999994</v>
+        <f t="shared" si="166"/>
+        <v>3774.7000000000007</v>
       </c>
       <c r="BA32" s="16">
-        <f t="shared" si="168"/>
-        <v>3320.6025099999993</v>
+        <f t="shared" si="166"/>
+        <v>3624.2558399999998</v>
       </c>
       <c r="BB32" s="16">
-        <f t="shared" si="168"/>
-        <v>2627.4284000000011</v>
+        <f t="shared" si="166"/>
+        <v>2924.6886000000004</v>
       </c>
       <c r="BD32" s="16">
         <f>BD28-BD29-BD30-BD31</f>
@@ -6878,84 +6877,84 @@
         <v>305.82300000000066</v>
       </c>
       <c r="BI32" s="16">
-        <f t="shared" ref="BI32:BW32" si="169">BI28-BI29-BI30-BI31</f>
+        <f t="shared" ref="BI32:BW32" si="167">BI28-BI29-BI30-BI31</f>
         <v>398.78700000000021</v>
       </c>
       <c r="BJ32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>838.52399999999921</v>
       </c>
       <c r="BK32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>1605.6133200000006</v>
       </c>
       <c r="BL32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>2601.8999999999992</v>
       </c>
       <c r="BM32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>4581.7</v>
       </c>
       <c r="BN32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>6195.2999999999975</v>
       </c>
       <c r="BO32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>5632.7999999999975</v>
       </c>
       <c r="BP32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>6953.9000000000005</v>
       </c>
       <c r="BQ32" s="16">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>10417.399999999994</v>
       </c>
       <c r="BR32" s="16">
-        <f t="shared" si="169"/>
-        <v>12597.854989999996</v>
+        <f t="shared" si="167"/>
+        <v>13670.64444</v>
       </c>
       <c r="BS32" s="16">
-        <f t="shared" si="169"/>
-        <v>15046.3955016</v>
+        <f t="shared" si="167"/>
+        <v>16319.389015500004</v>
       </c>
       <c r="BT32" s="16">
-        <f t="shared" si="169"/>
-        <v>16909.362719999997</v>
+        <f t="shared" si="167"/>
+        <v>17952.355817044005</v>
       </c>
       <c r="BU32" s="16">
-        <f t="shared" si="169"/>
-        <v>17997.505918516803</v>
+        <f t="shared" si="167"/>
+        <v>19515.289625634905</v>
       </c>
       <c r="BV32" s="16">
-        <f t="shared" si="169"/>
-        <v>18931.090842329111</v>
+        <f t="shared" si="167"/>
+        <v>20967.313059160708</v>
       </c>
       <c r="BW32" s="16">
-        <f t="shared" si="169"/>
-        <v>19120.401750752404</v>
+        <f t="shared" si="167"/>
+        <v>21712.349266917714</v>
       </c>
       <c r="BX32" s="16">
-        <f t="shared" ref="BX32:CB32" si="170">BX28-BX29-BX30-BX31</f>
-        <v>19311.605768259928</v>
+        <f t="shared" ref="BX32:CB32" si="168">BX28-BX29-BX30-BX31</f>
+        <v>22205.184744327074</v>
       </c>
       <c r="BY32" s="16">
-        <f t="shared" si="170"/>
-        <v>19504.721825942532</v>
+        <f t="shared" si="168"/>
+        <v>22708.462816205327</v>
       </c>
       <c r="BZ32" s="16">
-        <f t="shared" si="170"/>
-        <v>19699.769044201952</v>
+        <f t="shared" si="168"/>
+        <v>23222.398193291061</v>
       </c>
       <c r="CA32" s="16">
-        <f t="shared" si="170"/>
-        <v>19896.766734643974</v>
+        <f t="shared" si="168"/>
+        <v>23747.209939126129</v>
       </c>
       <c r="CB32" s="16">
-        <f t="shared" si="170"/>
-        <v>20095.734401990412</v>
+        <f t="shared" si="168"/>
+        <v>24283.121557697588</v>
       </c>
     </row>
     <row r="33" spans="2:150">
@@ -7004,15 +7003,15 @@
         <v>35.783290000000001</v>
       </c>
       <c r="P33" s="2">
-        <f t="shared" ref="P33:R33" si="171">O33*1.01</f>
+        <f t="shared" ref="P33:R33" si="169">O33*1.01</f>
         <v>36.141122899999999</v>
       </c>
       <c r="Q33" s="2">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>36.502534128999997</v>
       </c>
       <c r="R33" s="2">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>36.867559470289997</v>
       </c>
       <c r="S33" s="2">
@@ -7118,15 +7117,14 @@
         <v>184.2</v>
       </c>
       <c r="AZ33" s="2">
-        <f t="shared" ref="AZ33:BB34" si="172">AV33*1.03</f>
-        <v>173.04</v>
+        <v>182.6</v>
       </c>
       <c r="BA33" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" ref="BA33:BB34" si="170">AW33*1.03</f>
         <v>190.34400000000002</v>
       </c>
       <c r="BB33" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>198.37799999999999</v>
       </c>
       <c r="BD33" s="2">
@@ -7152,15 +7150,15 @@
         <v>145.29450649928998</v>
       </c>
       <c r="BJ33" s="15">
-        <f t="shared" ref="BJ33:BJ34" si="173">SUM(S33:V33)</f>
+        <f t="shared" ref="BJ33:BJ34" si="171">SUM(S33:V33)</f>
         <v>238.2</v>
       </c>
       <c r="BK33" s="15">
-        <f t="shared" ref="BK33:BK34" si="174">SUM(W33:Z33)</f>
+        <f t="shared" ref="BK33:BK34" si="172">SUM(W33:Z33)</f>
         <v>420.50000000000006</v>
       </c>
       <c r="BL33" s="15">
-        <f t="shared" ref="BL33" si="175">SUM(AA33:AD33)</f>
+        <f t="shared" ref="BL33" si="173">SUM(AA33:AD33)</f>
         <v>626</v>
       </c>
       <c r="BM33" s="15">
@@ -7185,47 +7183,47 @@
       </c>
       <c r="BR33" s="2">
         <f>SUM(AY33:BB33)</f>
-        <v>745.96199999999999</v>
+        <v>755.52199999999993</v>
       </c>
       <c r="BS33" s="2">
-        <f t="shared" ref="BS33:CB34" si="176">BR33*1.01</f>
-        <v>753.42161999999996</v>
+        <f t="shared" ref="BS33:CB34" si="174">BR33*1.01</f>
+        <v>763.0772199999999</v>
       </c>
       <c r="BT33" s="2">
-        <f t="shared" si="176"/>
-        <v>760.95583620000002</v>
+        <f t="shared" si="174"/>
+        <v>770.70799219999992</v>
       </c>
       <c r="BU33" s="2">
-        <f t="shared" si="176"/>
-        <v>768.56539456200005</v>
+        <f t="shared" si="174"/>
+        <v>778.41507212199997</v>
       </c>
       <c r="BV33" s="2">
-        <f t="shared" si="176"/>
-        <v>776.25104850762011</v>
+        <f t="shared" si="174"/>
+        <v>786.19922284322001</v>
       </c>
       <c r="BW33" s="2">
-        <f t="shared" si="176"/>
-        <v>784.01355899269629</v>
+        <f t="shared" si="174"/>
+        <v>794.06121507165221</v>
       </c>
       <c r="BX33" s="2">
-        <f t="shared" si="176"/>
-        <v>791.85369458262323</v>
+        <f t="shared" si="174"/>
+        <v>802.00182722236877</v>
       </c>
       <c r="BY33" s="2">
-        <f t="shared" si="176"/>
-        <v>799.77223152844942</v>
+        <f t="shared" si="174"/>
+        <v>810.02184549459253</v>
       </c>
       <c r="BZ33" s="2">
-        <f t="shared" si="176"/>
-        <v>807.7699538437339</v>
+        <f t="shared" si="174"/>
+        <v>818.12206394953841</v>
       </c>
       <c r="CA33" s="2">
-        <f t="shared" si="176"/>
-        <v>815.8476533821713</v>
+        <f t="shared" si="174"/>
+        <v>826.30328458903375</v>
       </c>
       <c r="CB33" s="2">
-        <f t="shared" si="176"/>
-        <v>824.00612991599303</v>
+        <f t="shared" si="174"/>
+        <v>834.56631743492414</v>
       </c>
     </row>
     <row r="34" spans="2:150">
@@ -7383,15 +7381,14 @@
         <v>-50.9</v>
       </c>
       <c r="AZ34" s="2">
-        <f t="shared" si="172"/>
-        <v>-81.37</v>
+        <v>-39.6</v>
       </c>
       <c r="BA34" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>22.350999999999999</v>
       </c>
       <c r="BB34" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>-55.723000000000006</v>
       </c>
       <c r="BD34" s="2">
@@ -7416,15 +7413,15 @@
         <v>50</v>
       </c>
       <c r="BJ34" s="15">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>115.2</v>
       </c>
       <c r="BK34" s="15">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>-41.7</v>
       </c>
       <c r="BL34" s="15">
-        <f t="shared" ref="BL34" si="177">SUM(AA34:AD34)</f>
+        <f t="shared" ref="BL34" si="175">SUM(AA34:AD34)</f>
         <v>-84</v>
       </c>
       <c r="BM34" s="15">
@@ -7449,47 +7446,47 @@
       </c>
       <c r="BR34" s="2">
         <f>SUM(AY34:BB34)</f>
-        <v>-165.64200000000002</v>
+        <v>-123.87200000000001</v>
       </c>
       <c r="BS34" s="2">
-        <f t="shared" si="176"/>
-        <v>-167.29842000000002</v>
+        <f t="shared" si="174"/>
+        <v>-125.11072000000001</v>
       </c>
       <c r="BT34" s="2">
-        <f t="shared" si="176"/>
-        <v>-168.97140420000002</v>
+        <f t="shared" si="174"/>
+        <v>-126.36182720000002</v>
       </c>
       <c r="BU34" s="2">
-        <f t="shared" si="176"/>
-        <v>-170.66111824200001</v>
+        <f t="shared" si="174"/>
+        <v>-127.62544547200002</v>
       </c>
       <c r="BV34" s="2">
-        <f t="shared" si="176"/>
-        <v>-172.36772942442002</v>
+        <f t="shared" si="174"/>
+        <v>-128.90169992672003</v>
       </c>
       <c r="BW34" s="2">
-        <f t="shared" si="176"/>
-        <v>-174.09140671866422</v>
+        <f t="shared" si="174"/>
+        <v>-130.19071692598723</v>
       </c>
       <c r="BX34" s="2">
-        <f t="shared" si="176"/>
-        <v>-175.83232078585087</v>
+        <f t="shared" si="174"/>
+        <v>-131.49262409524709</v>
       </c>
       <c r="BY34" s="2">
-        <f t="shared" si="176"/>
-        <v>-177.59064399370939</v>
+        <f t="shared" si="174"/>
+        <v>-132.80755033619957</v>
       </c>
       <c r="BZ34" s="2">
-        <f t="shared" si="176"/>
-        <v>-179.36655043364649</v>
+        <f t="shared" si="174"/>
+        <v>-134.13562583956156</v>
       </c>
       <c r="CA34" s="2">
-        <f t="shared" si="176"/>
-        <v>-181.16021593798297</v>
+        <f t="shared" si="174"/>
+        <v>-135.47698209795718</v>
       </c>
       <c r="CB34" s="2">
-        <f t="shared" si="176"/>
-        <v>-182.97181809736281</v>
+        <f t="shared" si="174"/>
+        <v>-136.83175191893676</v>
       </c>
     </row>
     <row r="35" spans="2:150" s="1" customFormat="1">
@@ -7497,212 +7494,212 @@
         <v>35</v>
       </c>
       <c r="C35" s="7">
-        <f t="shared" ref="C35:N35" si="178">C32-C33-C34</f>
+        <f t="shared" ref="C35:N35" si="176">C32-C33-C34</f>
         <v>0.93000000000001004</v>
       </c>
       <c r="D35" s="7">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>46.6490000000001</v>
       </c>
       <c r="E35" s="7">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>49.491000000000035</v>
       </c>
       <c r="F35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>74.004000000000005</v>
       </c>
       <c r="G35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>88.943999999999889</v>
       </c>
       <c r="H35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>117.37200000000013</v>
       </c>
       <c r="I35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>97.537000000000006</v>
       </c>
       <c r="J35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>45.516000000000076</v>
       </c>
       <c r="K35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>38.426000000000052</v>
       </c>
       <c r="L35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>40.490000000000009</v>
       </c>
       <c r="M35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>42.237999999999964</v>
       </c>
       <c r="N35" s="16">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>20.728000000000215</v>
       </c>
       <c r="O35" s="16">
-        <f t="shared" ref="O35" si="179">O32-O33-O34</f>
+        <f t="shared" ref="O35" si="177">O32-O33-O34</f>
         <v>57.994710000000019</v>
       </c>
       <c r="P35" s="16">
-        <f t="shared" ref="P35" si="180">P32-P33-P34</f>
+        <f t="shared" ref="P35" si="178">P32-P33-P34</f>
         <v>59.454377100000002</v>
       </c>
       <c r="Q35" s="16">
-        <f t="shared" ref="Q35" si="181">Q32-Q33-Q34</f>
+        <f t="shared" ref="Q35" si="179">Q32-Q33-Q34</f>
         <v>62.177465871000066</v>
       </c>
       <c r="R35" s="16">
-        <f t="shared" ref="R35:S35" si="182">R32-R33-R34</f>
+        <f t="shared" ref="R35:S35" si="180">R32-R33-R34</f>
         <v>69.865940529710002</v>
       </c>
       <c r="S35" s="16">
-        <f t="shared" si="182"/>
+        <f t="shared" si="180"/>
         <v>225.0000000000002</v>
       </c>
       <c r="T35" s="16">
-        <f t="shared" ref="T35:V35" si="183">T32-T33-T34</f>
+        <f t="shared" ref="T35:V35" si="181">T32-T33-T34</f>
         <v>14.420000000000137</v>
       </c>
       <c r="U35" s="16">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>115.29199999999985</v>
       </c>
       <c r="V35" s="16">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>130.41200000000003</v>
       </c>
       <c r="W35" s="16">
-        <f t="shared" ref="W35" si="184">W32-W33-W34</f>
+        <f t="shared" ref="W35" si="182">W32-W33-W34</f>
         <v>300.67600000000022</v>
       </c>
       <c r="X35" s="16">
-        <f t="shared" ref="X35" si="185">X32-X33-X34</f>
+        <f t="shared" ref="X35" si="183">X32-X33-X34</f>
         <v>428.19519999999989</v>
       </c>
       <c r="Y35" s="16">
-        <f t="shared" ref="Y35:Z35" si="186">Y32-Y33-Y34</f>
+        <f t="shared" ref="Y35:Z35" si="184">Y32-Y33-Y34</f>
         <v>378.51252000000011</v>
       </c>
       <c r="Z35" s="16">
-        <f t="shared" si="186"/>
+        <f t="shared" si="184"/>
         <v>119.4296000000011</v>
       </c>
       <c r="AA35" s="16">
-        <f t="shared" ref="AA35" si="187">AA32-AA33-AA34</f>
+        <f t="shared" ref="AA35" si="185">AA32-AA33-AA34</f>
         <v>247.40000000000023</v>
       </c>
       <c r="AB35" s="16">
-        <f t="shared" ref="AB35" si="188">AB32-AB33-AB34</f>
+        <f t="shared" ref="AB35" si="186">AB32-AB33-AB34</f>
         <v>500.70000000000005</v>
       </c>
       <c r="AC35" s="16">
-        <f t="shared" ref="AC35:AD35" si="189">AC32-AC33-AC34</f>
+        <f t="shared" ref="AC35:AD35" si="187">AC32-AC33-AC34</f>
         <v>1020.3</v>
       </c>
       <c r="AD35" s="16">
-        <f t="shared" si="189"/>
+        <f t="shared" si="187"/>
         <v>301.49999999999886</v>
       </c>
       <c r="AE35" s="16">
-        <f t="shared" ref="AE35:AM35" si="190">AE32-AE33-AE34</f>
+        <f t="shared" ref="AE35:AM35" si="188">AE32-AE33-AE34</f>
         <v>796.20000000000027</v>
       </c>
       <c r="AF35" s="16">
+        <f t="shared" si="188"/>
+        <v>1035.5</v>
+      </c>
+      <c r="AG35" s="16">
+        <f t="shared" si="188"/>
+        <v>857.8</v>
+      </c>
+      <c r="AH35" s="16">
+        <f t="shared" si="188"/>
+        <v>506.19999999999993</v>
+      </c>
+      <c r="AI35" s="16">
+        <f t="shared" si="188"/>
+        <v>2035.3000000000002</v>
+      </c>
+      <c r="AJ35" s="16">
+        <f t="shared" si="188"/>
+        <v>1593.9</v>
+      </c>
+      <c r="AK35" s="16">
+        <f t="shared" si="188"/>
+        <v>1660.9999999999993</v>
+      </c>
+      <c r="AL35" s="16">
+        <f t="shared" ref="AL35" si="189">AL32-AL33-AL34</f>
+        <v>550.79999999999984</v>
+      </c>
+      <c r="AM35" s="16">
+        <f t="shared" si="188"/>
+        <v>1979.7000000000003</v>
+      </c>
+      <c r="AN35" s="16">
+        <f t="shared" ref="AN35:AO35" si="190">AN32-AN33-AN34</f>
+        <v>1622.9000000000003</v>
+      </c>
+      <c r="AO35" s="16">
         <f t="shared" si="190"/>
-        <v>1035.5</v>
-      </c>
-      <c r="AG35" s="16">
-        <f t="shared" si="190"/>
-        <v>857.8</v>
-      </c>
-      <c r="AH35" s="16">
-        <f t="shared" si="190"/>
-        <v>506.19999999999993</v>
-      </c>
-      <c r="AI35" s="16">
-        <f t="shared" si="190"/>
-        <v>2035.3000000000002</v>
-      </c>
-      <c r="AJ35" s="16">
-        <f t="shared" si="190"/>
-        <v>1593.9</v>
-      </c>
-      <c r="AK35" s="16">
-        <f t="shared" si="190"/>
-        <v>1660.9999999999993</v>
-      </c>
-      <c r="AL35" s="16">
-        <f t="shared" ref="AL35" si="191">AL32-AL33-AL34</f>
-        <v>550.79999999999984</v>
-      </c>
-      <c r="AM35" s="16">
-        <f t="shared" si="190"/>
-        <v>1979.7000000000003</v>
-      </c>
-      <c r="AN35" s="16">
-        <f t="shared" ref="AN35:AO35" si="192">AN32-AN33-AN34</f>
-        <v>1622.9000000000003</v>
-      </c>
-      <c r="AO35" s="16">
-        <f t="shared" si="192"/>
         <v>1621.9000000000005</v>
       </c>
       <c r="AP35" s="16">
-        <f t="shared" ref="AP35:AR35" si="193">AP32-AP33-AP34</f>
+        <f t="shared" ref="AP35:AR35" si="191">AP32-AP33-AP34</f>
         <v>39.300000000000637</v>
       </c>
       <c r="AQ35" s="16">
-        <f t="shared" ref="AQ35" si="194">AQ32-AQ33-AQ34</f>
+        <f t="shared" ref="AQ35" si="192">AQ32-AQ33-AQ34</f>
         <v>1468.8999999999996</v>
       </c>
       <c r="AR35" s="16">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>1679.3000000000004</v>
       </c>
       <c r="AS35" s="16">
-        <f t="shared" ref="AS35" si="195">AS32-AS33-AS34</f>
+        <f t="shared" ref="AS35" si="193">AS32-AS33-AS34</f>
         <v>1909.0000000000011</v>
       </c>
       <c r="AT35" s="16">
-        <f t="shared" ref="AT35:BB35" si="196">AT32-AT33-AT34</f>
+        <f t="shared" ref="AT35:BB35" si="194">AT32-AT33-AT34</f>
         <v>1148.1999999999994</v>
       </c>
       <c r="AU35" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>2614.599999999999</v>
       </c>
       <c r="AV35" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>2513.7999999999993</v>
       </c>
       <c r="AW35" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>2702.900000000001</v>
       </c>
       <c r="AX35" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>2134.2000000000007</v>
       </c>
       <c r="AY35" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>3213.6999999999994</v>
       </c>
       <c r="AZ35" s="16">
-        <f t="shared" si="196"/>
-        <v>3211.1540799999993</v>
+        <f t="shared" si="194"/>
+        <v>3631.7000000000007</v>
       </c>
       <c r="BA35" s="16">
-        <f t="shared" si="196"/>
-        <v>3107.9075099999991</v>
+        <f t="shared" si="194"/>
+        <v>3411.5608399999996</v>
       </c>
       <c r="BB35" s="16">
-        <f t="shared" si="196"/>
-        <v>2484.7734000000009</v>
+        <f t="shared" si="194"/>
+        <v>2782.0336000000002</v>
       </c>
       <c r="BD35" s="16">
         <f>BD32-BD33-BD34</f>
@@ -7725,84 +7722,84 @@
         <v>141.88200000000066</v>
       </c>
       <c r="BI35" s="16">
-        <f t="shared" ref="BI35:BW35" si="197">BI32-BI33-BI34</f>
+        <f t="shared" ref="BI35:BW35" si="195">BI32-BI33-BI34</f>
         <v>203.49249350071022</v>
       </c>
       <c r="BJ35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>485.12399999999917</v>
       </c>
       <c r="BK35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>1226.8133200000007</v>
       </c>
       <c r="BL35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>2059.8999999999992</v>
       </c>
       <c r="BM35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>3195.7</v>
       </c>
       <c r="BN35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>5840.9999999999973</v>
       </c>
       <c r="BO35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>5263.7999999999975</v>
       </c>
       <c r="BP35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>6205.4000000000005</v>
       </c>
       <c r="BQ35" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>9965.4999999999927</v>
       </c>
       <c r="BR35" s="16">
-        <f t="shared" si="197"/>
-        <v>12017.534989999996</v>
+        <f t="shared" si="195"/>
+        <v>13038.994439999999</v>
       </c>
       <c r="BS35" s="16">
-        <f t="shared" si="197"/>
-        <v>14460.2723016</v>
+        <f t="shared" si="195"/>
+        <v>15681.422515500006</v>
       </c>
       <c r="BT35" s="16">
-        <f t="shared" si="197"/>
-        <v>16317.378287999996</v>
+        <f t="shared" si="195"/>
+        <v>17308.009652044002</v>
       </c>
       <c r="BU35" s="16">
-        <f t="shared" si="197"/>
-        <v>17399.601642196802</v>
+        <f t="shared" si="195"/>
+        <v>18864.499998984906</v>
       </c>
       <c r="BV35" s="16">
-        <f t="shared" si="197"/>
-        <v>18327.20752324591</v>
+        <f t="shared" si="195"/>
+        <v>20310.015536244206</v>
       </c>
       <c r="BW35" s="16">
-        <f t="shared" si="197"/>
-        <v>18510.47959847837</v>
+        <f t="shared" si="195"/>
+        <v>21048.478768772049</v>
       </c>
       <c r="BX35" s="16">
-        <f t="shared" ref="BX35:CB35" si="198">BX32-BX33-BX34</f>
-        <v>18695.584394463156</v>
+        <f t="shared" ref="BX35:CB35" si="196">BX32-BX33-BX34</f>
+        <v>21534.675541199955</v>
       </c>
       <c r="BY35" s="16">
-        <f t="shared" si="198"/>
-        <v>18882.540238407793</v>
+        <f t="shared" si="196"/>
+        <v>22031.248521046931</v>
       </c>
       <c r="BZ35" s="16">
-        <f t="shared" si="198"/>
-        <v>19071.365640791864</v>
+        <f t="shared" si="196"/>
+        <v>22538.411755181085</v>
       </c>
       <c r="CA35" s="16">
-        <f t="shared" si="198"/>
-        <v>19262.079297199787</v>
+        <f t="shared" si="196"/>
+        <v>23056.383636635052</v>
       </c>
       <c r="CB35" s="16">
-        <f t="shared" si="198"/>
-        <v>19454.70009017178</v>
+        <f t="shared" si="196"/>
+        <v>23585.3869921816</v>
       </c>
     </row>
     <row r="36" spans="2:150">
@@ -7846,19 +7843,19 @@
         <v>-22.446999999999999</v>
       </c>
       <c r="O36" s="2">
-        <f t="shared" ref="O36:R36" si="199">O35*0.3</f>
+        <f t="shared" ref="O36:R36" si="197">O35*0.3</f>
         <v>17.398413000000005</v>
       </c>
       <c r="P36" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="197"/>
         <v>17.836313130000001</v>
       </c>
       <c r="Q36" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="197"/>
         <v>18.653239761300018</v>
       </c>
       <c r="R36" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="197"/>
         <v>20.959782158913001</v>
       </c>
       <c r="S36" s="2">
@@ -7964,16 +7961,15 @@
         <v>323.39999999999998</v>
       </c>
       <c r="AZ36" s="2">
-        <f t="shared" ref="AZ36:BB36" si="200">AZ35*0.12</f>
-        <v>385.33848959999989</v>
+        <v>506.3</v>
       </c>
       <c r="BA36" s="2">
-        <f t="shared" si="200"/>
-        <v>372.94890119999985</v>
+        <f t="shared" ref="BA36:BB36" si="198">BA35*0.12</f>
+        <v>409.38730079999993</v>
       </c>
       <c r="BB36" s="2">
-        <f t="shared" si="200"/>
-        <v>298.17280800000009</v>
+        <f t="shared" si="198"/>
+        <v>333.84403200000003</v>
       </c>
       <c r="BD36" s="2">
         <v>133.39599999999999</v>
@@ -7998,15 +7994,15 @@
         <v>74.847748050213028</v>
       </c>
       <c r="BJ36" s="15">
-        <f t="shared" ref="BJ36" si="201">SUM(S36:V36)</f>
+        <f t="shared" ref="BJ36" si="199">SUM(S36:V36)</f>
         <v>-73.599999999999994</v>
       </c>
       <c r="BK36" s="15">
-        <f t="shared" ref="BK36" si="202">SUM(W36:Z36)</f>
+        <f t="shared" ref="BK36" si="200">SUM(W36:Z36)</f>
         <v>15.199999999999996</v>
       </c>
       <c r="BL36" s="15">
-        <f t="shared" ref="BL36" si="203">SUM(AA36:AD36)</f>
+        <f t="shared" ref="BL36" si="201">SUM(AA36:AD36)</f>
         <v>195.29999999999995</v>
       </c>
       <c r="BM36" s="15">
@@ -8031,47 +8027,47 @@
       </c>
       <c r="BR36" s="2">
         <f>SUM(AY36:BB36)</f>
-        <v>1379.8601987999998</v>
+        <v>1572.9313327999998</v>
       </c>
       <c r="BS36" s="2">
         <f>BS35*0.13</f>
-        <v>1879.8353992080001</v>
+        <v>2038.5849270150009</v>
       </c>
       <c r="BT36" s="2">
-        <f t="shared" ref="BT36:CB36" si="204">BT35*0.13</f>
-        <v>2121.2591774399998</v>
+        <f t="shared" ref="BT36:CB36" si="202">BT35*0.13</f>
+        <v>2250.0412547657202</v>
       </c>
       <c r="BU36" s="2">
-        <f t="shared" si="204"/>
-        <v>2261.9482134855843</v>
+        <f t="shared" si="202"/>
+        <v>2452.384999868038</v>
       </c>
       <c r="BV36" s="2">
-        <f t="shared" si="204"/>
-        <v>2382.5369780219685</v>
+        <f t="shared" si="202"/>
+        <v>2640.3020197117467</v>
       </c>
       <c r="BW36" s="2">
-        <f t="shared" si="204"/>
-        <v>2406.3623478021882</v>
+        <f t="shared" si="202"/>
+        <v>2736.3022399403667</v>
       </c>
       <c r="BX36" s="2">
-        <f t="shared" si="204"/>
-        <v>2430.4259712802104</v>
+        <f t="shared" si="202"/>
+        <v>2799.5078203559942</v>
       </c>
       <c r="BY36" s="2">
-        <f t="shared" si="204"/>
-        <v>2454.7302309930133</v>
+        <f t="shared" si="202"/>
+        <v>2864.062307736101</v>
       </c>
       <c r="BZ36" s="2">
-        <f t="shared" si="204"/>
-        <v>2479.2775333029426</v>
+        <f t="shared" si="202"/>
+        <v>2929.9935281735411</v>
       </c>
       <c r="CA36" s="2">
-        <f t="shared" si="204"/>
-        <v>2504.0703086359722</v>
+        <f t="shared" si="202"/>
+        <v>2997.329872762557</v>
       </c>
       <c r="CB36" s="2">
-        <f t="shared" si="204"/>
-        <v>2529.1110117223316</v>
+        <f t="shared" si="202"/>
+        <v>3066.1003089836081</v>
       </c>
     </row>
     <row r="37" spans="2:150" s="1" customFormat="1">
@@ -8079,212 +8075,212 @@
         <v>37</v>
       </c>
       <c r="C37" s="7">
-        <f t="shared" ref="C37:N37" si="205">C35-C36</f>
+        <f t="shared" ref="C37:N37" si="203">C35-C36</f>
         <v>2.6890000000000098</v>
       </c>
       <c r="D37" s="7">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>29.4710000000001</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>31.822000000000035</v>
       </c>
       <c r="F37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>48.421000000000006</v>
       </c>
       <c r="G37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>53.114999999999888</v>
       </c>
       <c r="H37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>71.018000000000129</v>
       </c>
       <c r="I37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>59.295000000000009</v>
       </c>
       <c r="J37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>83.371000000000066</v>
       </c>
       <c r="K37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>23.696000000000051</v>
       </c>
       <c r="L37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>26.335000000000008</v>
       </c>
       <c r="M37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>29.431999999999967</v>
       </c>
       <c r="N37" s="16">
-        <f t="shared" si="205"/>
+        <f t="shared" si="203"/>
         <v>43.17500000000021</v>
       </c>
       <c r="O37" s="16">
-        <f t="shared" ref="O37" si="206">O35-O36</f>
+        <f t="shared" ref="O37" si="204">O35-O36</f>
         <v>40.596297000000014</v>
       </c>
       <c r="P37" s="16">
-        <f t="shared" ref="P37" si="207">P35-P36</f>
+        <f t="shared" ref="P37" si="205">P35-P36</f>
         <v>41.618063970000001</v>
       </c>
       <c r="Q37" s="16">
-        <f t="shared" ref="Q37" si="208">Q35-Q36</f>
+        <f t="shared" ref="Q37" si="206">Q35-Q36</f>
         <v>43.524226109700052</v>
       </c>
       <c r="R37" s="16">
-        <f t="shared" ref="R37:S37" si="209">R35-R36</f>
+        <f t="shared" ref="R37:S37" si="207">R35-R36</f>
         <v>48.906158370797002</v>
       </c>
       <c r="S37" s="16">
-        <f t="shared" si="209"/>
+        <f t="shared" si="207"/>
         <v>179.4000000000002</v>
       </c>
       <c r="T37" s="16">
-        <f t="shared" ref="T37:V37" si="210">T35-T36</f>
+        <f t="shared" ref="T37:V37" si="208">T35-T36</f>
         <v>66.020000000000138</v>
       </c>
       <c r="U37" s="16">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>101.89199999999984</v>
       </c>
       <c r="V37" s="16">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>211.41200000000003</v>
       </c>
       <c r="W37" s="16">
-        <f t="shared" ref="W37" si="211">W35-W36</f>
+        <f t="shared" ref="W37" si="209">W35-W36</f>
         <v>291.17600000000022</v>
       </c>
       <c r="X37" s="16">
-        <f t="shared" ref="X37" si="212">X35-X36</f>
+        <f t="shared" ref="X37" si="210">X35-X36</f>
         <v>372.59519999999986</v>
       </c>
       <c r="Y37" s="16">
-        <f t="shared" ref="Y37:Z37" si="213">Y35-Y36</f>
+        <f t="shared" ref="Y37:Z37" si="211">Y35-Y36</f>
         <v>402.51252000000011</v>
       </c>
       <c r="Z37" s="16">
-        <f t="shared" si="213"/>
+        <f t="shared" si="211"/>
         <v>145.32960000000111</v>
       </c>
       <c r="AA37" s="16">
-        <f t="shared" ref="AA37" si="214">AA35-AA36</f>
+        <f t="shared" ref="AA37" si="212">AA35-AA36</f>
         <v>191.80000000000024</v>
       </c>
       <c r="AB37" s="16">
-        <f t="shared" ref="AB37" si="215">AB35-AB36</f>
+        <f t="shared" ref="AB37" si="213">AB35-AB36</f>
         <v>270.40000000000003</v>
       </c>
       <c r="AC37" s="16">
-        <f t="shared" ref="AC37:AD37" si="216">AC35-AC36</f>
+        <f t="shared" ref="AC37:AD37" si="214">AC35-AC36</f>
         <v>673.19999999999993</v>
       </c>
       <c r="AD37" s="16">
+        <f t="shared" si="214"/>
+        <v>739.19999999999891</v>
+      </c>
+      <c r="AE37" s="16">
+        <f t="shared" ref="AE37:AH37" si="215">AE35-AE36</f>
+        <v>709.40000000000032</v>
+      </c>
+      <c r="AF37" s="16">
+        <f t="shared" si="215"/>
+        <v>720.1</v>
+      </c>
+      <c r="AG37" s="16">
+        <f t="shared" si="215"/>
+        <v>786.3</v>
+      </c>
+      <c r="AH37" s="16">
+        <f t="shared" si="215"/>
+        <v>541.9</v>
+      </c>
+      <c r="AI37" s="16">
+        <f t="shared" ref="AI37:AM37" si="216">AI35-AI36</f>
+        <v>1707.5000000000002</v>
+      </c>
+      <c r="AJ37" s="16">
         <f t="shared" si="216"/>
-        <v>739.19999999999891</v>
-      </c>
-      <c r="AE37" s="16">
-        <f t="shared" ref="AE37:AH37" si="217">AE35-AE36</f>
-        <v>709.40000000000032</v>
-      </c>
-      <c r="AF37" s="16">
-        <f t="shared" si="217"/>
-        <v>720.1</v>
-      </c>
-      <c r="AG37" s="16">
-        <f t="shared" si="217"/>
-        <v>786.3</v>
-      </c>
-      <c r="AH37" s="16">
-        <f t="shared" si="217"/>
-        <v>541.9</v>
-      </c>
-      <c r="AI37" s="16">
-        <f t="shared" ref="AI37:AM37" si="218">AI35-AI36</f>
-        <v>1707.5000000000002</v>
-      </c>
-      <c r="AJ37" s="16">
+        <v>1353.1000000000001</v>
+      </c>
+      <c r="AK37" s="16">
+        <f t="shared" si="216"/>
+        <v>1449.0999999999992</v>
+      </c>
+      <c r="AL37" s="16">
+        <f t="shared" ref="AL37" si="217">AL35-AL36</f>
+        <v>607.39999999999986</v>
+      </c>
+      <c r="AM37" s="16">
+        <f t="shared" si="216"/>
+        <v>1597.5000000000002</v>
+      </c>
+      <c r="AN37" s="16">
+        <f t="shared" ref="AN37:AO37" si="218">AN35-AN36</f>
+        <v>1440.7000000000003</v>
+      </c>
+      <c r="AO37" s="16">
         <f t="shared" si="218"/>
-        <v>1353.1000000000001</v>
-      </c>
-      <c r="AK37" s="16">
-        <f t="shared" si="218"/>
-        <v>1449.0999999999992</v>
-      </c>
-      <c r="AL37" s="16">
-        <f t="shared" ref="AL37" si="219">AL35-AL36</f>
-        <v>607.39999999999986</v>
-      </c>
-      <c r="AM37" s="16">
-        <f t="shared" si="218"/>
-        <v>1597.5000000000002</v>
-      </c>
-      <c r="AN37" s="16">
-        <f t="shared" ref="AN37:AO37" si="220">AN35-AN36</f>
-        <v>1440.7000000000003</v>
-      </c>
-      <c r="AO37" s="16">
-        <f t="shared" si="220"/>
         <v>1398.3000000000006</v>
       </c>
       <c r="AP37" s="16">
-        <f t="shared" ref="AP37:AR37" si="221">AP35-AP36</f>
+        <f t="shared" ref="AP37:AR37" si="219">AP35-AP36</f>
         <v>55.300000000000637</v>
       </c>
       <c r="AQ37" s="16">
-        <f t="shared" ref="AQ37" si="222">AQ35-AQ36</f>
+        <f t="shared" ref="AQ37" si="220">AQ35-AQ36</f>
         <v>1305.0999999999997</v>
       </c>
       <c r="AR37" s="16">
-        <f t="shared" si="221"/>
+        <f t="shared" si="219"/>
         <v>1487.6000000000004</v>
       </c>
       <c r="AS37" s="16">
-        <f t="shared" ref="AS37" si="223">AS35-AS36</f>
+        <f t="shared" ref="AS37" si="221">AS35-AS36</f>
         <v>1677.4000000000012</v>
       </c>
       <c r="AT37" s="16">
-        <f t="shared" ref="AT37:AU37" si="224">AT35-AT36</f>
+        <f t="shared" ref="AT37:AU37" si="222">AT35-AT36</f>
         <v>937.89999999999941</v>
       </c>
       <c r="AU37" s="16">
+        <f t="shared" si="222"/>
+        <v>2332.1999999999989</v>
+      </c>
+      <c r="AV37" s="16">
+        <f t="shared" ref="AV37:AX37" si="223">AV35-AV36</f>
+        <v>2147.1999999999994</v>
+      </c>
+      <c r="AW37" s="16">
+        <f t="shared" si="223"/>
+        <v>2363.5000000000009</v>
+      </c>
+      <c r="AX37" s="16">
+        <f t="shared" si="223"/>
+        <v>1868.5000000000007</v>
+      </c>
+      <c r="AY37" s="16">
+        <f t="shared" ref="AY37:BB37" si="224">AY35-AY36</f>
+        <v>2890.2999999999993</v>
+      </c>
+      <c r="AZ37" s="16">
         <f t="shared" si="224"/>
-        <v>2332.1999999999989</v>
-      </c>
-      <c r="AV37" s="16">
-        <f t="shared" ref="AV37:AX37" si="225">AV35-AV36</f>
-        <v>2147.1999999999994</v>
-      </c>
-      <c r="AW37" s="16">
-        <f t="shared" si="225"/>
-        <v>2363.5000000000009</v>
-      </c>
-      <c r="AX37" s="16">
-        <f t="shared" si="225"/>
-        <v>1868.5000000000007</v>
-      </c>
-      <c r="AY37" s="16">
-        <f t="shared" ref="AY37:BB37" si="226">AY35-AY36</f>
-        <v>2890.2999999999993</v>
-      </c>
-      <c r="AZ37" s="16">
-        <f t="shared" si="226"/>
-        <v>2825.8155903999996</v>
+        <v>3125.4000000000005</v>
       </c>
       <c r="BA37" s="16">
-        <f t="shared" si="226"/>
-        <v>2734.9586087999992</v>
+        <f t="shared" si="224"/>
+        <v>3002.1735391999996</v>
       </c>
       <c r="BB37" s="16">
-        <f t="shared" si="226"/>
-        <v>2186.6005920000007</v>
+        <f t="shared" si="224"/>
+        <v>2448.1895680000002</v>
       </c>
       <c r="BD37" s="16">
         <f>BD35-BD36</f>
@@ -8307,364 +8303,364 @@
         <v>122.63800000000066</v>
       </c>
       <c r="BI37" s="16">
-        <f t="shared" ref="BI37:BW37" si="227">BI35-BI36</f>
+        <f t="shared" ref="BI37:BW37" si="225">BI35-BI36</f>
         <v>128.6447454504972</v>
       </c>
       <c r="BJ37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>558.72399999999914</v>
       </c>
       <c r="BK37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>1211.6133200000006</v>
       </c>
       <c r="BL37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>1864.5999999999992</v>
       </c>
       <c r="BM37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>2757.7</v>
       </c>
       <c r="BN37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>5117.0999999999976</v>
       </c>
       <c r="BO37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>4491.7999999999975</v>
       </c>
       <c r="BP37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>5408</v>
       </c>
       <c r="BQ37" s="16">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>8711.3999999999924</v>
       </c>
       <c r="BR37" s="16">
-        <f t="shared" si="227"/>
-        <v>10637.674791199997</v>
+        <f t="shared" si="225"/>
+        <v>11466.0631072</v>
       </c>
       <c r="BS37" s="16">
-        <f t="shared" si="227"/>
-        <v>12580.436902392001</v>
+        <f t="shared" si="225"/>
+        <v>13642.837588485005</v>
       </c>
       <c r="BT37" s="16">
-        <f t="shared" si="227"/>
-        <v>14196.119110559997</v>
+        <f t="shared" si="225"/>
+        <v>15057.968397278282</v>
       </c>
       <c r="BU37" s="16">
-        <f t="shared" si="227"/>
-        <v>15137.653428711217</v>
+        <f t="shared" si="225"/>
+        <v>16412.114999116868</v>
       </c>
       <c r="BV37" s="16">
-        <f t="shared" si="227"/>
-        <v>15944.670545223942</v>
+        <f t="shared" si="225"/>
+        <v>17669.713516532458</v>
       </c>
       <c r="BW37" s="16">
-        <f t="shared" si="227"/>
-        <v>16104.117250676183</v>
+        <f t="shared" si="225"/>
+        <v>18312.176528831682</v>
       </c>
       <c r="BX37" s="16">
-        <f t="shared" ref="BX37:CB37" si="228">BX35-BX36</f>
-        <v>16265.158423182946</v>
+        <f t="shared" ref="BX37:CB37" si="226">BX35-BX36</f>
+        <v>18735.167720843961</v>
       </c>
       <c r="BY37" s="16">
-        <f t="shared" si="228"/>
-        <v>16427.810007414781</v>
+        <f t="shared" si="226"/>
+        <v>19167.18621331083</v>
       </c>
       <c r="BZ37" s="16">
-        <f t="shared" si="228"/>
-        <v>16592.088107488922</v>
+        <f t="shared" si="226"/>
+        <v>19608.418227007543</v>
       </c>
       <c r="CA37" s="16">
-        <f t="shared" si="228"/>
-        <v>16758.008988563815</v>
+        <f t="shared" si="226"/>
+        <v>20059.053763872493</v>
       </c>
       <c r="CB37" s="16">
-        <f t="shared" si="228"/>
-        <v>16925.589078449448</v>
+        <f t="shared" si="226"/>
+        <v>20519.286683197992</v>
       </c>
       <c r="CC37" s="1">
         <f>CB37*(1+$CE$46)</f>
-        <v>16756.333187664954</v>
+        <v>20314.09381636601</v>
       </c>
       <c r="CD37" s="1">
-        <f t="shared" ref="CD37:EO37" si="229">CC37*(1+$CE$46)</f>
-        <v>16588.769855788305</v>
+        <f t="shared" ref="CD37:EO37" si="227">CC37*(1+$CE$46)</f>
+        <v>20110.952878202352</v>
       </c>
       <c r="CE37" s="1">
-        <f t="shared" si="229"/>
-        <v>16422.882157230422</v>
+        <f t="shared" si="227"/>
+        <v>19909.843349420327</v>
       </c>
       <c r="CF37" s="1">
-        <f t="shared" si="229"/>
-        <v>16258.653335658119</v>
+        <f t="shared" si="227"/>
+        <v>19710.744915926123</v>
       </c>
       <c r="CG37" s="1">
-        <f t="shared" si="229"/>
-        <v>16096.066802301537</v>
+        <f t="shared" si="227"/>
+        <v>19513.637466766861</v>
       </c>
       <c r="CH37" s="1">
-        <f t="shared" si="229"/>
-        <v>15935.106134278521</v>
+        <f t="shared" si="227"/>
+        <v>19318.501092099192</v>
       </c>
       <c r="CI37" s="1">
-        <f t="shared" si="229"/>
-        <v>15775.755072935735</v>
+        <f t="shared" si="227"/>
+        <v>19125.3160811782</v>
       </c>
       <c r="CJ37" s="1">
-        <f t="shared" si="229"/>
-        <v>15617.997522206379</v>
+        <f t="shared" si="227"/>
+        <v>18934.062920366418</v>
       </c>
       <c r="CK37" s="1">
-        <f t="shared" si="229"/>
-        <v>15461.817546984315</v>
+        <f t="shared" si="227"/>
+        <v>18744.722291162754</v>
       </c>
       <c r="CL37" s="1">
-        <f t="shared" si="229"/>
-        <v>15307.199371514473</v>
+        <f t="shared" si="227"/>
+        <v>18557.275068251125</v>
       </c>
       <c r="CM37" s="1">
-        <f t="shared" si="229"/>
-        <v>15154.127377799328</v>
+        <f t="shared" si="227"/>
+        <v>18371.702317568615</v>
       </c>
       <c r="CN37" s="1">
-        <f t="shared" si="229"/>
-        <v>15002.586104021335</v>
+        <f t="shared" si="227"/>
+        <v>18187.985294392929</v>
       </c>
       <c r="CO37" s="1">
-        <f t="shared" si="229"/>
-        <v>14852.560242981121</v>
+        <f t="shared" si="227"/>
+        <v>18006.105441448999</v>
       </c>
       <c r="CP37" s="1">
-        <f t="shared" si="229"/>
-        <v>14704.03464055131</v>
+        <f t="shared" si="227"/>
+        <v>17826.044387034508</v>
       </c>
       <c r="CQ37" s="1">
-        <f t="shared" si="229"/>
-        <v>14556.994294145798</v>
+        <f t="shared" si="227"/>
+        <v>17647.783943164162</v>
       </c>
       <c r="CR37" s="1">
-        <f t="shared" si="229"/>
-        <v>14411.424351204339</v>
+        <f t="shared" si="227"/>
+        <v>17471.306103732521</v>
       </c>
       <c r="CS37" s="1">
-        <f t="shared" si="229"/>
-        <v>14267.310107692296</v>
+        <f t="shared" si="227"/>
+        <v>17296.593042695196</v>
       </c>
       <c r="CT37" s="1">
-        <f t="shared" si="229"/>
-        <v>14124.637006615372</v>
+        <f t="shared" si="227"/>
+        <v>17123.627112268245</v>
       </c>
       <c r="CU37" s="1">
-        <f t="shared" si="229"/>
-        <v>13983.390636549218</v>
+        <f t="shared" si="227"/>
+        <v>16952.390841145563</v>
       </c>
       <c r="CV37" s="1">
-        <f t="shared" si="229"/>
-        <v>13843.556730183725</v>
+        <f t="shared" si="227"/>
+        <v>16782.866932734109</v>
       </c>
       <c r="CW37" s="1">
-        <f t="shared" si="229"/>
-        <v>13705.121162881887</v>
+        <f t="shared" si="227"/>
+        <v>16615.038263406768</v>
       </c>
       <c r="CX37" s="1">
-        <f t="shared" si="229"/>
-        <v>13568.069951253068</v>
+        <f t="shared" si="227"/>
+        <v>16448.887880772701</v>
       </c>
       <c r="CY37" s="1">
-        <f t="shared" si="229"/>
-        <v>13432.389251740537</v>
+        <f t="shared" si="227"/>
+        <v>16284.399001964974</v>
       </c>
       <c r="CZ37" s="1">
-        <f t="shared" si="229"/>
-        <v>13298.065359223132</v>
+        <f t="shared" si="227"/>
+        <v>16121.555011945324</v>
       </c>
       <c r="DA37" s="1">
-        <f t="shared" si="229"/>
-        <v>13165.084705630901</v>
+        <f t="shared" si="227"/>
+        <v>15960.33946182587</v>
       </c>
       <c r="DB37" s="1">
-        <f t="shared" si="229"/>
-        <v>13033.433858574592</v>
+        <f t="shared" si="227"/>
+        <v>15800.73606720761</v>
       </c>
       <c r="DC37" s="1">
-        <f t="shared" si="229"/>
-        <v>12903.099519988846</v>
+        <f t="shared" si="227"/>
+        <v>15642.728706535534</v>
       </c>
       <c r="DD37" s="1">
-        <f t="shared" si="229"/>
-        <v>12774.068524788958</v>
+        <f t="shared" si="227"/>
+        <v>15486.301419470179</v>
       </c>
       <c r="DE37" s="1">
-        <f t="shared" si="229"/>
-        <v>12646.327839541069</v>
+        <f t="shared" si="227"/>
+        <v>15331.438405275478</v>
       </c>
       <c r="DF37" s="1">
-        <f t="shared" si="229"/>
-        <v>12519.864561145658</v>
+        <f t="shared" si="227"/>
+        <v>15178.124021222722</v>
       </c>
       <c r="DG37" s="1">
-        <f t="shared" si="229"/>
-        <v>12394.6659155342</v>
+        <f t="shared" si="227"/>
+        <v>15026.342781010495</v>
       </c>
       <c r="DH37" s="1">
-        <f t="shared" si="229"/>
-        <v>12270.719256378858</v>
+        <f t="shared" si="227"/>
+        <v>14876.07935320039</v>
       </c>
       <c r="DI37" s="1">
-        <f t="shared" si="229"/>
-        <v>12148.012063815069</v>
+        <f t="shared" si="227"/>
+        <v>14727.318559668385</v>
       </c>
       <c r="DJ37" s="1">
-        <f t="shared" si="229"/>
-        <v>12026.531943176919</v>
+        <f t="shared" si="227"/>
+        <v>14580.045374071702</v>
       </c>
       <c r="DK37" s="1">
-        <f t="shared" si="229"/>
-        <v>11906.266623745149</v>
+        <f t="shared" si="227"/>
+        <v>14434.244920330984</v>
       </c>
       <c r="DL37" s="1">
-        <f t="shared" si="229"/>
-        <v>11787.203957507698</v>
+        <f t="shared" si="227"/>
+        <v>14289.902471127674</v>
       </c>
       <c r="DM37" s="1">
-        <f t="shared" si="229"/>
-        <v>11669.331917932621</v>
+        <f t="shared" si="227"/>
+        <v>14147.003446416398</v>
       </c>
       <c r="DN37" s="1">
-        <f t="shared" si="229"/>
-        <v>11552.638598753294</v>
+        <f t="shared" si="227"/>
+        <v>14005.533411952234</v>
       </c>
       <c r="DO37" s="1">
-        <f t="shared" si="229"/>
-        <v>11437.112212765762</v>
+        <f t="shared" si="227"/>
+        <v>13865.478077832711</v>
       </c>
       <c r="DP37" s="1">
-        <f t="shared" si="229"/>
-        <v>11322.741090638105</v>
+        <f t="shared" si="227"/>
+        <v>13726.823297054383</v>
       </c>
       <c r="DQ37" s="1">
-        <f t="shared" si="229"/>
-        <v>11209.513679731723</v>
+        <f t="shared" si="227"/>
+        <v>13589.555064083839</v>
       </c>
       <c r="DR37" s="1">
-        <f t="shared" si="229"/>
-        <v>11097.418542934405</v>
+        <f t="shared" si="227"/>
+        <v>13453.659513443001</v>
       </c>
       <c r="DS37" s="1">
-        <f t="shared" si="229"/>
-        <v>10986.444357505061</v>
+        <f t="shared" si="227"/>
+        <v>13319.122918308571</v>
       </c>
       <c r="DT37" s="1">
-        <f t="shared" si="229"/>
-        <v>10876.579913930011</v>
+        <f t="shared" si="227"/>
+        <v>13185.931689125486</v>
       </c>
       <c r="DU37" s="1">
-        <f t="shared" si="229"/>
-        <v>10767.81411479071</v>
+        <f t="shared" si="227"/>
+        <v>13054.07237223423</v>
       </c>
       <c r="DV37" s="1">
-        <f t="shared" si="229"/>
-        <v>10660.135973642802</v>
+        <f t="shared" si="227"/>
+        <v>12923.531648511887</v>
       </c>
       <c r="DW37" s="1">
-        <f t="shared" si="229"/>
-        <v>10553.534613906373</v>
+        <f t="shared" si="227"/>
+        <v>12794.296332026768</v>
       </c>
       <c r="DX37" s="1">
-        <f t="shared" si="229"/>
-        <v>10447.999267767309</v>
+        <f t="shared" si="227"/>
+        <v>12666.353368706501</v>
       </c>
       <c r="DY37" s="1">
-        <f t="shared" si="229"/>
-        <v>10343.519275089635</v>
+        <f t="shared" si="227"/>
+        <v>12539.689835019435</v>
       </c>
       <c r="DZ37" s="1">
-        <f t="shared" si="229"/>
-        <v>10240.084082338739</v>
+        <f t="shared" si="227"/>
+        <v>12414.292936669241</v>
       </c>
       <c r="EA37" s="1">
-        <f t="shared" si="229"/>
-        <v>10137.683241515351</v>
+        <f t="shared" si="227"/>
+        <v>12290.150007302547</v>
       </c>
       <c r="EB37" s="1">
-        <f t="shared" si="229"/>
-        <v>10036.306409100198</v>
+        <f t="shared" si="227"/>
+        <v>12167.248507229522</v>
       </c>
       <c r="EC37" s="1">
-        <f t="shared" si="229"/>
-        <v>9935.9433450091965</v>
+        <f t="shared" si="227"/>
+        <v>12045.576022157227</v>
       </c>
       <c r="ED37" s="1">
-        <f t="shared" si="229"/>
-        <v>9836.5839115591043</v>
+        <f t="shared" si="227"/>
+        <v>11925.120261935655</v>
       </c>
       <c r="EE37" s="1">
-        <f t="shared" si="229"/>
-        <v>9738.2180724435129</v>
+        <f t="shared" si="227"/>
+        <v>11805.869059316299</v>
       </c>
       <c r="EF37" s="1">
-        <f t="shared" si="229"/>
-        <v>9640.8358917190781</v>
+        <f t="shared" si="227"/>
+        <v>11687.810368723136</v>
       </c>
       <c r="EG37" s="1">
-        <f t="shared" si="229"/>
-        <v>9544.4275328018866</v>
+        <f t="shared" si="227"/>
+        <v>11570.932265035904</v>
       </c>
       <c r="EH37" s="1">
-        <f t="shared" si="229"/>
-        <v>9448.9832574738684</v>
+        <f t="shared" si="227"/>
+        <v>11455.222942385546</v>
       </c>
       <c r="EI37" s="1">
-        <f t="shared" si="229"/>
-        <v>9354.4934248991303</v>
+        <f t="shared" si="227"/>
+        <v>11340.67071296169</v>
       </c>
       <c r="EJ37" s="1">
-        <f t="shared" si="229"/>
-        <v>9260.9484906501384</v>
+        <f t="shared" si="227"/>
+        <v>11227.264005832072</v>
       </c>
       <c r="EK37" s="1">
-        <f t="shared" si="229"/>
-        <v>9168.3390057436372</v>
+        <f t="shared" si="227"/>
+        <v>11114.991365773751</v>
       </c>
       <c r="EL37" s="1">
-        <f t="shared" si="229"/>
-        <v>9076.6556156862007</v>
+        <f t="shared" si="227"/>
+        <v>11003.841452116014</v>
       </c>
       <c r="EM37" s="1">
-        <f t="shared" si="229"/>
-        <v>8985.8890595293378</v>
+        <f t="shared" si="227"/>
+        <v>10893.803037594853</v>
       </c>
       <c r="EN37" s="1">
-        <f t="shared" si="229"/>
-        <v>8896.0301689340449</v>
+        <f t="shared" si="227"/>
+        <v>10784.865007218905</v>
       </c>
       <c r="EO37" s="1">
-        <f t="shared" si="229"/>
-        <v>8807.0698672447052</v>
+        <f t="shared" si="227"/>
+        <v>10677.016357146716</v>
       </c>
       <c r="EP37" s="1">
-        <f t="shared" ref="EP37:ET37" si="230">EO37*(1+$CE$46)</f>
-        <v>8718.999168572258</v>
+        <f t="shared" ref="EP37:ET37" si="228">EO37*(1+$CE$46)</f>
+        <v>10570.246193575249</v>
       </c>
       <c r="EQ37" s="1">
-        <f t="shared" si="230"/>
-        <v>8631.8091768865361</v>
+        <f t="shared" si="228"/>
+        <v>10464.543731639496</v>
       </c>
       <c r="ER37" s="1">
-        <f t="shared" si="230"/>
-        <v>8545.4910851176701</v>
+        <f t="shared" si="228"/>
+        <v>10359.898294323102</v>
       </c>
       <c r="ES37" s="1">
-        <f t="shared" si="230"/>
-        <v>8460.0361742664936</v>
+        <f t="shared" si="228"/>
+        <v>10256.299311379871</v>
       </c>
       <c r="ET37" s="1">
-        <f t="shared" si="230"/>
-        <v>8375.4358125238286</v>
+        <f t="shared" si="228"/>
+        <v>10153.736318266072</v>
       </c>
     </row>
     <row r="38" spans="2:150">
@@ -8820,13 +8816,16 @@
         <v>425.7</v>
       </c>
       <c r="AZ38" s="2">
-        <v>425.7</v>
+        <f>425.2</f>
+        <v>425.2</v>
       </c>
       <c r="BA38" s="2">
-        <v>425.7</v>
+        <f>425.2</f>
+        <v>425.2</v>
       </c>
       <c r="BB38" s="2">
-        <v>425.7</v>
+        <f>425.2</f>
+        <v>425.2</v>
       </c>
       <c r="BD38" s="2">
         <v>428</v>
@@ -8872,41 +8871,52 @@
         <v>435.9</v>
       </c>
       <c r="BQ38" s="2">
-        <f t="shared" ref="BQ38" si="231">427.7</f>
+        <f t="shared" ref="BQ38" si="229">427.7</f>
         <v>427.7</v>
       </c>
       <c r="BR38" s="2">
-        <v>425.7</v>
+        <f t="shared" ref="BR38:CB38" si="230">425.2</f>
+        <v>425.2</v>
       </c>
       <c r="BS38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BT38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BU38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BV38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BW38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BX38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BY38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="BZ38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="CA38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
       <c r="CB38" s="2">
-        <v>425.7</v>
+        <f t="shared" si="230"/>
+        <v>425.2</v>
       </c>
     </row>
     <row r="39" spans="2:150" s="1" customFormat="1">
@@ -8914,312 +8924,312 @@
         <v>38</v>
       </c>
       <c r="C39" s="8">
-        <f t="shared" ref="C39:N39" si="232">C37/C38</f>
+        <f t="shared" ref="C39:N39" si="231">C37/C38</f>
         <v>6.2827102803738547E-3</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>6.8857476635514253E-2</v>
       </c>
       <c r="E39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>7.435046728971971E-2</v>
       </c>
       <c r="F39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.11313317757009347</v>
       </c>
       <c r="G39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.12410046728971937</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.16592990654205639</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.13853971962616823</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.19479205607476652</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>5.5364485981308532E-2</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>6.1530373831775717E-2</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>6.8766355140186836E-2</v>
       </c>
       <c r="N39" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.10087616822429955</v>
       </c>
       <c r="O39" s="8">
-        <f t="shared" ref="O39" si="233">O37/O38</f>
+        <f t="shared" ref="O39" si="232">O37/O38</f>
         <v>9.4851161214953308E-2</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" ref="P39" si="234">P37/P38</f>
+        <f t="shared" ref="P39" si="233">P37/P38</f>
         <v>9.7238467219626173E-2</v>
       </c>
       <c r="Q39" s="8">
-        <f t="shared" ref="Q39" si="235">Q37/Q38</f>
+        <f t="shared" ref="Q39" si="234">Q37/Q38</f>
         <v>0.10169211707873844</v>
       </c>
       <c r="R39" s="8">
-        <f t="shared" ref="R39:S39" si="236">R37/R38</f>
+        <f t="shared" ref="R39:S39" si="235">R37/R38</f>
         <v>0.11426672516541356</v>
       </c>
       <c r="S39" s="8">
+        <f t="shared" si="235"/>
+        <v>0.40680272108843585</v>
+      </c>
+      <c r="T39" s="8">
+        <f t="shared" ref="T39:V39" si="236">T37/T38</f>
+        <v>0.14970521541950144</v>
+      </c>
+      <c r="U39" s="8">
         <f t="shared" si="236"/>
-        <v>0.40680272108843585</v>
-      </c>
-      <c r="T39" s="8">
-        <f t="shared" ref="T39:V39" si="237">T37/T38</f>
-        <v>0.14970521541950144</v>
-      </c>
-      <c r="U39" s="8">
-        <f t="shared" si="237"/>
         <v>0.2310476190476187</v>
       </c>
       <c r="V39" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="236"/>
         <v>0.4793922902494332</v>
       </c>
       <c r="W39" s="8">
-        <f t="shared" ref="W39" si="238">W37/W38</f>
+        <f t="shared" ref="W39" si="237">W37/W38</f>
         <v>0.66026303854875334</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" ref="X39" si="239">X37/X38</f>
+        <f t="shared" ref="X39" si="238">X37/X38</f>
         <v>0.84488707482993164</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" ref="Y39:Z39" si="240">Y37/Y38</f>
+        <f t="shared" ref="Y39:Z39" si="239">Y37/Y38</f>
         <v>0.91272680272108864</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="240"/>
+        <f t="shared" si="239"/>
         <v>0.32954557823129504</v>
       </c>
       <c r="AA39" s="8">
-        <f t="shared" ref="AA39" si="241">AA37/AA38</f>
+        <f t="shared" ref="AA39" si="240">AA37/AA38</f>
         <v>0.43492063492063548</v>
       </c>
       <c r="AB39" s="8">
-        <f t="shared" ref="AB39" si="242">AB37/AB38</f>
+        <f t="shared" ref="AB39" si="241">AB37/AB38</f>
         <v>0.6131519274376418</v>
       </c>
       <c r="AC39" s="8">
-        <f t="shared" ref="AC39:AD39" si="243">AC37/AC38</f>
+        <f t="shared" ref="AC39:AD39" si="242">AC37/AC38</f>
         <v>1.5265306122448978</v>
       </c>
       <c r="AD39" s="8">
+        <f t="shared" si="242"/>
+        <v>1.6761904761904738</v>
+      </c>
+      <c r="AE39" s="8">
+        <f t="shared" ref="AE39:AF39" si="243">AE37/AE38</f>
+        <v>1.6086167800453521</v>
+      </c>
+      <c r="AF39" s="8">
         <f t="shared" si="243"/>
-        <v>1.6761904761904738</v>
-      </c>
-      <c r="AE39" s="8">
-        <f t="shared" ref="AE39:AF39" si="244">AE37/AE38</f>
-        <v>1.6086167800453521</v>
-      </c>
-      <c r="AF39" s="8">
+        <v>1.6328798185941045</v>
+      </c>
+      <c r="AG39" s="8">
+        <f t="shared" ref="AG39:AH39" si="244">AG37/AG38</f>
+        <v>1.7789592760180994</v>
+      </c>
+      <c r="AH39" s="8">
         <f t="shared" si="244"/>
-        <v>1.6328798185941045</v>
-      </c>
-      <c r="AG39" s="8">
-        <f t="shared" ref="AG39:AH39" si="245">AG37/AG38</f>
-        <v>1.7789592760180994</v>
-      </c>
-      <c r="AH39" s="8">
+        <v>1.2260180995475112</v>
+      </c>
+      <c r="AI39" s="8">
+        <f t="shared" ref="AI39:AM39" si="245">AI37/AI38</f>
+        <v>3.8631221719457018</v>
+      </c>
+      <c r="AJ39" s="8">
         <f t="shared" si="245"/>
-        <v>1.2260180995475112</v>
-      </c>
-      <c r="AI39" s="8">
-        <f t="shared" ref="AI39:AM39" si="246">AI37/AI38</f>
-        <v>3.8631221719457018</v>
-      </c>
-      <c r="AJ39" s="8">
-        <f t="shared" si="246"/>
         <v>3.0530234657039714</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="246"/>
+        <f t="shared" si="245"/>
         <v>3.2725835591689232</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" ref="AL39" si="247">AL37/AL38</f>
+        <f t="shared" ref="AL39" si="246">AL37/AL38</f>
         <v>1.3695603156708001</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="246"/>
+        <f t="shared" si="245"/>
         <v>3.5971628011709078</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" ref="AN39:AO39" si="248">AN37/AN38</f>
+        <f t="shared" ref="AN39:AO39" si="247">AN37/AN38</f>
         <v>3.2404408457040041</v>
       </c>
       <c r="AO39" s="8">
+        <f t="shared" si="247"/>
+        <v>3.1429534726904937</v>
+      </c>
+      <c r="AP39" s="8">
+        <f t="shared" ref="AP39:AR39" si="248">AP37/AP38</f>
+        <v>0.12421383647798885</v>
+      </c>
+      <c r="AQ39" s="8">
+        <f t="shared" ref="AQ39" si="249">AQ37/AQ38</f>
+        <v>2.9314914645103318</v>
+      </c>
+      <c r="AR39" s="8">
         <f t="shared" si="248"/>
-        <v>3.1429534726904937</v>
-      </c>
-      <c r="AP39" s="8">
-        <f t="shared" ref="AP39:AR39" si="249">AP37/AP38</f>
-        <v>0.12421383647798885</v>
-      </c>
-      <c r="AQ39" s="8">
-        <f t="shared" ref="AQ39" si="250">AQ37/AQ38</f>
-        <v>2.9314914645103318</v>
-      </c>
-      <c r="AR39" s="8">
-        <f t="shared" si="249"/>
         <v>3.3512052264023438</v>
       </c>
       <c r="AS39" s="8">
-        <f t="shared" ref="AS39" si="251">AS37/AS38</f>
+        <f t="shared" ref="AS39" si="250">AS37/AS38</f>
         <v>3.7993204983012485</v>
       </c>
       <c r="AT39" s="8">
-        <f t="shared" ref="AT39:AU39" si="252">AT37/AT38</f>
+        <f t="shared" ref="AT39:AU39" si="251">AT37/AT38</f>
         <v>2.1516402844689138</v>
       </c>
       <c r="AU39" s="8">
+        <f t="shared" si="251"/>
+        <v>5.3973617218236489</v>
+      </c>
+      <c r="AV39" s="8">
+        <f t="shared" ref="AV39:AX39" si="252">AV37/AV38</f>
+        <v>4.9692200879426043</v>
+      </c>
+      <c r="AW39" s="8">
         <f t="shared" si="252"/>
-        <v>5.3973617218236489</v>
-      </c>
-      <c r="AV39" s="8">
-        <f t="shared" ref="AV39:AX39" si="253">AV37/AV38</f>
-        <v>4.9692200879426043</v>
-      </c>
-      <c r="AW39" s="8">
+        <v>5.5286549707602362</v>
+      </c>
+      <c r="AX39" s="8">
+        <f t="shared" si="252"/>
+        <v>4.3687163899929873</v>
+      </c>
+      <c r="AY39" s="8">
+        <f t="shared" ref="AY39:BB39" si="253">AY37/AY38</f>
+        <v>6.7895231383603463</v>
+      </c>
+      <c r="AZ39" s="8">
         <f t="shared" si="253"/>
-        <v>5.5286549707602362</v>
-      </c>
-      <c r="AX39" s="8">
+        <v>7.3504233301975557</v>
+      </c>
+      <c r="BA39" s="8">
         <f t="shared" si="253"/>
-        <v>4.3687163899929873</v>
-      </c>
-      <c r="AY39" s="8">
-        <f t="shared" ref="AY39:BB39" si="254">AY37/AY38</f>
-        <v>6.7895231383603463</v>
-      </c>
-      <c r="AZ39" s="8">
+        <v>7.0606150968955781</v>
+      </c>
+      <c r="BB39" s="8">
+        <f t="shared" si="253"/>
+        <v>5.7577365192850429</v>
+      </c>
+      <c r="BD39" s="8">
+        <f t="shared" ref="BD39:BX39" si="254">BD37/BD38</f>
+        <v>0.52833177570093515</v>
+      </c>
+      <c r="BE39" s="8">
         <f t="shared" si="254"/>
-        <v>6.6380446098191204</v>
-      </c>
-      <c r="BA39" s="8">
+        <v>4.0074766355140665E-2</v>
+      </c>
+      <c r="BF39" s="8">
         <f t="shared" si="254"/>
-        <v>6.4246150077519362</v>
-      </c>
-      <c r="BB39" s="8">
+        <v>0.2626238317757007</v>
+      </c>
+      <c r="BG39" s="8">
         <f t="shared" si="254"/>
-        <v>5.136482480620157</v>
-      </c>
-      <c r="BD39" s="8">
-        <f t="shared" ref="BD39:BX39" si="255">BD37/BD38</f>
-        <v>0.52833177570093515</v>
-      </c>
-      <c r="BE39" s="8">
+        <v>0.62336214953271085</v>
+      </c>
+      <c r="BH39" s="8">
+        <f t="shared" si="254"/>
+        <v>0.28653738317757166</v>
+      </c>
+      <c r="BI39" s="8">
+        <f t="shared" si="254"/>
+        <v>0.30057183516471309</v>
+      </c>
+      <c r="BJ39" s="8">
+        <f t="shared" si="254"/>
+        <v>1.305429906542054</v>
+      </c>
+      <c r="BK39" s="8">
+        <f t="shared" si="254"/>
+        <v>2.8308722429906554</v>
+      </c>
+      <c r="BL39" s="8">
+        <f t="shared" si="254"/>
+        <v>4.3565420560747645</v>
+      </c>
+      <c r="BM39" s="8">
+        <f t="shared" si="254"/>
+        <v>6.2391402714932118</v>
+      </c>
+      <c r="BN39" s="8">
+        <f t="shared" si="254"/>
+        <v>11.537993235625699</v>
+      </c>
+      <c r="BO39" s="8">
+        <f t="shared" si="254"/>
+        <v>10.089398023360282</v>
+      </c>
+      <c r="BP39" s="8">
+        <f t="shared" si="254"/>
+        <v>12.406515255792614</v>
+      </c>
+      <c r="BQ39" s="8">
+        <f t="shared" si="254"/>
+        <v>20.368014963759627</v>
+      </c>
+      <c r="BR39" s="8">
+        <f t="shared" si="254"/>
+        <v>26.966282001881467</v>
+      </c>
+      <c r="BS39" s="8">
+        <f t="shared" si="254"/>
+        <v>32.085695175176397</v>
+      </c>
+      <c r="BT39" s="8">
+        <f t="shared" si="254"/>
+        <v>35.413848535461625</v>
+      </c>
+      <c r="BU39" s="8">
+        <f t="shared" si="254"/>
+        <v>38.598577138092352</v>
+      </c>
+      <c r="BV39" s="8">
+        <f t="shared" si="254"/>
+        <v>41.556240631543879</v>
+      </c>
+      <c r="BW39" s="8">
+        <f t="shared" si="254"/>
+        <v>43.067207264420702</v>
+      </c>
+      <c r="BX39" s="8">
+        <f t="shared" si="254"/>
+        <v>44.06201251374403</v>
+      </c>
+      <c r="BY39" s="8">
+        <f t="shared" ref="BY39:CB39" si="255">BY37/BY38</f>
+        <v>45.078048479094143</v>
+      </c>
+      <c r="BZ39" s="8">
         <f t="shared" si="255"/>
-        <v>4.0074766355140665E-2</v>
-      </c>
-      <c r="BF39" s="8">
+        <v>46.115753120902035</v>
+      </c>
+      <c r="CA39" s="8">
         <f t="shared" si="255"/>
-        <v>0.2626238317757007</v>
-      </c>
-      <c r="BG39" s="8">
+        <v>47.175573292268325</v>
+      </c>
+      <c r="CB39" s="8">
         <f t="shared" si="255"/>
-        <v>0.62336214953271085</v>
-      </c>
-      <c r="BH39" s="8">
-        <f t="shared" si="255"/>
-        <v>0.28653738317757166</v>
-      </c>
-      <c r="BI39" s="8">
-        <f t="shared" si="255"/>
-        <v>0.30057183516471309</v>
-      </c>
-      <c r="BJ39" s="8">
-        <f t="shared" si="255"/>
-        <v>1.305429906542054</v>
-      </c>
-      <c r="BK39" s="8">
-        <f t="shared" si="255"/>
-        <v>2.8308722429906554</v>
-      </c>
-      <c r="BL39" s="8">
-        <f t="shared" si="255"/>
-        <v>4.3565420560747645</v>
-      </c>
-      <c r="BM39" s="8">
-        <f t="shared" si="255"/>
-        <v>6.2391402714932118</v>
-      </c>
-      <c r="BN39" s="8">
-        <f t="shared" si="255"/>
-        <v>11.537993235625699</v>
-      </c>
-      <c r="BO39" s="8">
-        <f t="shared" si="255"/>
-        <v>10.089398023360282</v>
-      </c>
-      <c r="BP39" s="8">
-        <f t="shared" si="255"/>
-        <v>12.406515255792614</v>
-      </c>
-      <c r="BQ39" s="8">
-        <f t="shared" si="255"/>
-        <v>20.368014963759627</v>
-      </c>
-      <c r="BR39" s="8">
-        <f t="shared" si="255"/>
-        <v>24.988665236551558</v>
-      </c>
-      <c r="BS39" s="8">
-        <f t="shared" si="255"/>
-        <v>29.552353540972518</v>
-      </c>
-      <c r="BT39" s="8">
-        <f t="shared" si="255"/>
-        <v>33.347707565327688</v>
-      </c>
-      <c r="BU39" s="8">
-        <f t="shared" si="255"/>
-        <v>35.559439578837718</v>
-      </c>
-      <c r="BV39" s="8">
-        <f t="shared" si="255"/>
-        <v>37.455180984787276</v>
-      </c>
-      <c r="BW39" s="8">
-        <f t="shared" si="255"/>
-        <v>37.829732794635149</v>
-      </c>
-      <c r="BX39" s="8">
-        <f t="shared" si="255"/>
-        <v>38.208030122581505</v>
-      </c>
-      <c r="BY39" s="8">
-        <f t="shared" ref="BY39:CB39" si="256">BY37/BY38</f>
-        <v>38.590110423807332</v>
-      </c>
-      <c r="BZ39" s="8">
-        <f t="shared" si="256"/>
-        <v>38.97601152804539</v>
-      </c>
-      <c r="CA39" s="8">
-        <f t="shared" si="256"/>
-        <v>39.36577164332585</v>
-      </c>
-      <c r="CB39" s="8">
-        <f t="shared" si="256"/>
-        <v>39.759429359759096</v>
+        <v>48.257964918151437</v>
       </c>
     </row>
     <row r="41" spans="2:150">
@@ -9231,308 +9241,308 @@
         <v>0.28029290178043892</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" ref="D41:R41" si="257">D28/D26</f>
+        <f t="shared" ref="D41:R41" si="256">D28/D26</f>
         <v>0.28867223005651921</v>
       </c>
       <c r="E41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.27766661633509621</v>
+      </c>
+      <c r="F41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.30168818018600613</v>
+      </c>
+      <c r="G41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.31564953322168754</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.3174849131644345</v>
+      </c>
+      <c r="I41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.32285204252493205</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.3168230140470174</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.33482823086981423</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.31795701814440863</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.32467303859108176</v>
+      </c>
+      <c r="N41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.31478780891916075</v>
+      </c>
+      <c r="O41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.33</v>
+      </c>
+      <c r="P41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.33</v>
+      </c>
+      <c r="Q41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.33</v>
+      </c>
+      <c r="R41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.33</v>
+      </c>
+      <c r="S41" s="10">
+        <f t="shared" ref="S41:AH41" si="257">S28/S26</f>
+        <v>0.37182500568655702</v>
+      </c>
+      <c r="T41" s="10">
         <f t="shared" si="257"/>
-        <v>0.27766661633509621</v>
-      </c>
-      <c r="F41" s="10">
+        <v>0.31717350103376984</v>
+      </c>
+      <c r="U41" s="10">
         <f t="shared" si="257"/>
-        <v>0.30168818018600613</v>
-      </c>
-      <c r="G41" s="10">
+        <v>0.33208038360637715</v>
+      </c>
+      <c r="V41" s="10">
         <f t="shared" si="257"/>
-        <v>0.31564953322168754</v>
-      </c>
-      <c r="H41" s="10">
+        <v>0.24481995255885089</v>
+      </c>
+      <c r="W41" s="10">
         <f t="shared" si="257"/>
-        <v>0.3174849131644345</v>
-      </c>
-      <c r="I41" s="10">
+        <v>0.4067602480472064</v>
+      </c>
+      <c r="X41" s="10">
         <f t="shared" si="257"/>
-        <v>0.32285204252493205</v>
-      </c>
-      <c r="J41" s="10">
+        <v>0.41403239268033593</v>
+      </c>
+      <c r="Y41" s="10">
         <f t="shared" si="257"/>
-        <v>0.3168230140470174</v>
-      </c>
-      <c r="K41" s="10">
+        <v>0.39677608211139082</v>
+      </c>
+      <c r="Z41" s="10">
         <f t="shared" si="257"/>
-        <v>0.33482823086981423</v>
-      </c>
-      <c r="L41" s="10">
+        <v>0.2667817442510263</v>
+      </c>
+      <c r="AA41" s="10">
         <f t="shared" si="257"/>
-        <v>0.31795701814440863</v>
-      </c>
-      <c r="M41" s="10">
+        <v>0.36505197965051983</v>
+      </c>
+      <c r="AB41" s="10">
         <f t="shared" si="257"/>
-        <v>0.32467303859108176</v>
-      </c>
-      <c r="N41" s="10">
+        <v>0.38945764777574654</v>
+      </c>
+      <c r="AC41" s="10">
         <f t="shared" si="257"/>
-        <v>0.31478780891916075</v>
-      </c>
-      <c r="O41" s="10">
+        <v>0.41026080335046639</v>
+      </c>
+      <c r="AD41" s="10">
         <f t="shared" si="257"/>
+        <v>0.36601426742271786</v>
+      </c>
+      <c r="AE41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.3759188626907074</v>
+      </c>
+      <c r="AF41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.40733571893298637</v>
+      </c>
+      <c r="AG41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.39866293532338304</v>
+      </c>
+      <c r="AH41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.37311860325105356</v>
+      </c>
+      <c r="AI41" s="10">
+        <f t="shared" ref="AI41:AT41" si="258">AI28/AI26</f>
+        <v>0.46000837520938026</v>
+      </c>
+      <c r="AJ41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.45272276553433766</v>
+      </c>
+      <c r="AK41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.43788334335538182</v>
+      </c>
+      <c r="AL41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.3203533394731039</v>
+      </c>
+      <c r="AM41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.45541320318259237</v>
+      </c>
+      <c r="AN41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.41145029547935408</v>
+      </c>
+      <c r="AO41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.39579337841929951</v>
+      </c>
+      <c r="AP41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.31175099654869404</v>
+      </c>
+      <c r="AQ41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.41143172210990619</v>
+      </c>
+      <c r="AR41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.42917689592417524</v>
+      </c>
+      <c r="AS41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.42273786248639034</v>
+      </c>
+      <c r="AT41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.39911466352685443</v>
+      </c>
+      <c r="AU41" s="10">
+        <f t="shared" ref="AU41:AX41" si="259">AU28/AU26</f>
+        <v>0.46884871510287707</v>
+      </c>
+      <c r="AV41" s="10">
+        <f t="shared" si="259"/>
+        <v>0.45873651836431528</v>
+      </c>
+      <c r="AW41" s="10">
+        <f t="shared" si="259"/>
+        <v>0.47887467301800574</v>
+      </c>
+      <c r="AX41" s="10">
+        <f t="shared" si="259"/>
+        <v>0.43713463133752994</v>
+      </c>
+      <c r="AY41" s="10">
+        <f t="shared" ref="AY41:BB41" si="260">AY28/AY26</f>
+        <v>0.50078726713965926</v>
+      </c>
+      <c r="AZ41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.51934255180879485</v>
+      </c>
+      <c r="BA41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.51</v>
+      </c>
+      <c r="BB41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.47</v>
+      </c>
+      <c r="BD41" s="10">
+        <f t="shared" ref="BD41:BW41" si="261">BD28/BD26</f>
+        <v>0.36344141520082063</v>
+      </c>
+      <c r="BE41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.27246859624712066</v>
+      </c>
+      <c r="BF41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.28742511821754951</v>
+      </c>
+      <c r="BG41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.31825712633087339</v>
+      </c>
+      <c r="BH41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.32274156646401203</v>
+      </c>
+      <c r="BI41" s="10">
+        <f t="shared" si="261"/>
         <v>0.33</v>
       </c>
-      <c r="P41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.33</v>
-      </c>
-      <c r="Q41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.33</v>
-      </c>
-      <c r="R41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.33</v>
-      </c>
-      <c r="S41" s="10">
-        <f t="shared" ref="S41:AH41" si="258">S28/S26</f>
-        <v>0.37182500568655702</v>
-      </c>
-      <c r="T41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.31717350103376984</v>
-      </c>
-      <c r="U41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.33208038360637715</v>
-      </c>
-      <c r="V41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.24481995255885089</v>
-      </c>
-      <c r="W41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.4067602480472064</v>
-      </c>
-      <c r="X41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.41403239268033593</v>
-      </c>
-      <c r="Y41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.39677608211139082</v>
-      </c>
-      <c r="Z41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.2667817442510263</v>
-      </c>
-      <c r="AA41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.36505197965051983</v>
-      </c>
-      <c r="AB41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.38945764777574654</v>
-      </c>
-      <c r="AC41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.41026080335046639</v>
-      </c>
-      <c r="AD41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.36601426742271786</v>
-      </c>
-      <c r="AE41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.3759188626907074</v>
-      </c>
-      <c r="AF41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.40733571893298637</v>
-      </c>
-      <c r="AG41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.39866293532338304</v>
-      </c>
-      <c r="AH41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.37311860325105356</v>
-      </c>
-      <c r="AI41" s="10">
-        <f t="shared" ref="AI41:AT41" si="259">AI28/AI26</f>
-        <v>0.46000837520938026</v>
-      </c>
-      <c r="AJ41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.45272276553433766</v>
-      </c>
-      <c r="AK41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.43788334335538182</v>
-      </c>
-      <c r="AL41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.3203533394731039</v>
-      </c>
-      <c r="AM41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.45541320318259237</v>
-      </c>
-      <c r="AN41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.41145029547935408</v>
-      </c>
-      <c r="AO41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.39579337841929951</v>
-      </c>
-      <c r="AP41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.31175099654869404</v>
-      </c>
-      <c r="AQ41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.41143172210990619</v>
-      </c>
-      <c r="AR41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.42917689592417524</v>
-      </c>
-      <c r="AS41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.42273786248639034</v>
-      </c>
-      <c r="AT41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.39911466352685443</v>
-      </c>
-      <c r="AU41" s="10">
-        <f t="shared" ref="AU41:AX41" si="260">AU28/AU26</f>
-        <v>0.46884871510287707</v>
-      </c>
-      <c r="AV41" s="10">
-        <f t="shared" si="260"/>
-        <v>0.45873651836431528</v>
-      </c>
-      <c r="AW41" s="10">
-        <f t="shared" si="260"/>
-        <v>0.47887467301800574</v>
-      </c>
-      <c r="AX41" s="10">
-        <f t="shared" si="260"/>
-        <v>0.43713463133752994</v>
-      </c>
-      <c r="AY41" s="10">
-        <f t="shared" ref="AY41:BB41" si="261">AY28/AY26</f>
-        <v>0.50078726713965926</v>
-      </c>
-      <c r="AZ41" s="10">
+      <c r="BJ41" s="10">
         <f t="shared" si="261"/>
-        <v>0.48</v>
-      </c>
-      <c r="BA41" s="10">
+        <v>0.31297981513657785</v>
+      </c>
+      <c r="BK41" s="10">
         <f t="shared" si="261"/>
-        <v>0.48</v>
-      </c>
-      <c r="BB41" s="10">
+        <v>0.36893441507553748</v>
+      </c>
+      <c r="BL41" s="10">
         <f t="shared" si="261"/>
-        <v>0.46000000000000008</v>
-      </c>
-      <c r="BD41" s="10">
-        <f t="shared" ref="BD41:BW41" si="262">BD28/BD26</f>
-        <v>0.36344141520082063</v>
-      </c>
-      <c r="BE41" s="10">
+        <v>0.38274287982534483</v>
+      </c>
+      <c r="BM41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.38875640204865552</v>
+      </c>
+      <c r="BN41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.4163798966954671</v>
+      </c>
+      <c r="BO41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.39370437379015416</v>
+      </c>
+      <c r="BP41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.4153774986433712</v>
+      </c>
+      <c r="BQ41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.46056373058057626</v>
+      </c>
+      <c r="BR41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.49975874904589912</v>
+      </c>
+      <c r="BS41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.52</v>
+      </c>
+      <c r="BT41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.53</v>
+      </c>
+      <c r="BU41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.54</v>
+      </c>
+      <c r="BV41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BW41" s="10">
+        <f t="shared" si="261"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BX41" s="10">
+        <f t="shared" ref="BX41:CB41" si="262">BX28/BX26</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BY41" s="10">
         <f t="shared" si="262"/>
-        <v>0.27246859624712066</v>
-      </c>
-      <c r="BF41" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BZ41" s="10">
         <f t="shared" si="262"/>
-        <v>0.28742511821754951</v>
-      </c>
-      <c r="BG41" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="CA41" s="10">
         <f t="shared" si="262"/>
-        <v>0.31825712633087339</v>
-      </c>
-      <c r="BH41" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="CB41" s="10">
         <f t="shared" si="262"/>
-        <v>0.32274156646401203</v>
-      </c>
-      <c r="BI41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.33</v>
-      </c>
-      <c r="BJ41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.31297981513657785</v>
-      </c>
-      <c r="BK41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.36893441507553748</v>
-      </c>
-      <c r="BL41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.38274287982534483</v>
-      </c>
-      <c r="BM41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.38875640204865552</v>
-      </c>
-      <c r="BN41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.4163798966954671</v>
-      </c>
-      <c r="BO41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.39370437379015416</v>
-      </c>
-      <c r="BP41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.4153774986433712</v>
-      </c>
-      <c r="BQ41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.46056373058057626</v>
-      </c>
-      <c r="BR41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.48004427593398824</v>
-      </c>
-      <c r="BS41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.5</v>
-      </c>
-      <c r="BT41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.52</v>
-      </c>
-      <c r="BU41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.53</v>
-      </c>
-      <c r="BV41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.54</v>
-      </c>
-      <c r="BW41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.54</v>
-      </c>
-      <c r="BX41" s="10">
-        <f t="shared" ref="BX41:CB41" si="263">BX28/BX26</f>
-        <v>0.54</v>
-      </c>
-      <c r="BY41" s="10">
-        <f t="shared" si="263"/>
-        <v>0.54</v>
-      </c>
-      <c r="BZ41" s="10">
-        <f t="shared" si="263"/>
-        <v>0.54</v>
-      </c>
-      <c r="CA41" s="10">
-        <f t="shared" si="263"/>
-        <v>0.54</v>
-      </c>
-      <c r="CB41" s="10">
-        <f t="shared" si="263"/>
-        <v>0.54</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="42" spans="2:150" s="1" customFormat="1">
@@ -9544,308 +9554,308 @@
         <v>3.1077355485218686E-2</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" ref="D42:R42" si="264">D32/D26</f>
+        <f t="shared" ref="D42:R42" si="263">D32/D26</f>
         <v>5.3411722020026794E-2</v>
       </c>
       <c r="E42" s="10">
+        <f t="shared" si="263"/>
+        <v>5.1645616316108811E-2</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="263"/>
+        <v>7.0018634650238679E-2</v>
+      </c>
+      <c r="G42" s="10">
+        <f t="shared" si="263"/>
+        <v>7.6841071767411492E-2</v>
+      </c>
+      <c r="H42" s="10">
+        <f t="shared" si="263"/>
+        <v>9.6687051022562642E-2</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="263"/>
+        <v>7.8334392861805324E-2</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="263"/>
+        <v>4.3810044668114348E-2</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="263"/>
+        <v>6.1950418560715641E-2</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="263"/>
+        <v>4.5500865206536907E-2</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="263"/>
+        <v>4.2362463363352115E-2</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="263"/>
+        <v>3.2846989551552137E-2</v>
+      </c>
+      <c r="O42" s="10">
+        <f t="shared" si="263"/>
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="P42" s="10">
+        <f t="shared" si="263"/>
+        <v>0.05</v>
+      </c>
+      <c r="Q42" s="10">
+        <f t="shared" si="263"/>
+        <v>5.0000000000000037E-2</v>
+      </c>
+      <c r="R42" s="10">
+        <f t="shared" si="263"/>
+        <v>0.05</v>
+      </c>
+      <c r="S42" s="10">
+        <f t="shared" ref="S42:AH42" si="264">S32/S26</f>
+        <v>9.7846690423838117E-2</v>
+      </c>
+      <c r="T42" s="10">
         <f t="shared" si="264"/>
-        <v>5.1645616316108811E-2</v>
-      </c>
-      <c r="F42" s="10">
+        <v>4.6060188375832804E-2</v>
+      </c>
+      <c r="U42" s="10">
         <f t="shared" si="264"/>
-        <v>7.0018634650238679E-2</v>
-      </c>
-      <c r="G42" s="10">
+        <v>6.9604395869555552E-2</v>
+      </c>
+      <c r="V42" s="10">
         <f t="shared" si="264"/>
-        <v>7.6841071767411492E-2</v>
-      </c>
-      <c r="H42" s="10">
+        <v>7.4404428490017396E-2</v>
+      </c>
+      <c r="W42" s="10">
         <f t="shared" si="264"/>
-        <v>9.6687051022562642E-2</v>
-      </c>
-      <c r="I42" s="10">
+        <v>0.12090518429034365</v>
+      </c>
+      <c r="X42" s="10">
         <f t="shared" si="264"/>
-        <v>7.8334392861805324E-2</v>
-      </c>
-      <c r="J42" s="10">
+        <v>0.11816980148290565</v>
+      </c>
+      <c r="Y42" s="10">
         <f t="shared" si="264"/>
-        <v>4.3810044668114348E-2</v>
-      </c>
-      <c r="K42" s="10">
+        <v>0.12013278718117143</v>
+      </c>
+      <c r="Z42" s="10">
         <f t="shared" si="264"/>
-        <v>6.1950418560715641E-2</v>
-      </c>
-      <c r="L42" s="10">
+        <v>5.156073336732684E-2</v>
+      </c>
+      <c r="AA42" s="10">
         <f t="shared" si="264"/>
-        <v>4.5500865206536907E-2</v>
-      </c>
-      <c r="M42" s="10">
+        <v>0.10152621101526216</v>
+      </c>
+      <c r="AB42" s="10">
         <f t="shared" si="264"/>
-        <v>4.2362463363352115E-2</v>
-      </c>
-      <c r="N42" s="10">
+        <v>0.14344911639244365</v>
+      </c>
+      <c r="AC42" s="10">
         <f t="shared" si="264"/>
-        <v>3.2846989551552137E-2</v>
-      </c>
-      <c r="O42" s="10">
+        <v>0.18814011041309728</v>
+      </c>
+      <c r="AD42" s="10">
         <f t="shared" si="264"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="P42" s="10">
+        <v>8.384854582037661E-2</v>
+      </c>
+      <c r="AE42" s="10">
         <f t="shared" si="264"/>
-        <v>0.05</v>
-      </c>
-      <c r="Q42" s="10">
+        <v>0.1661927877947296</v>
+      </c>
+      <c r="AF42" s="10">
         <f t="shared" si="264"/>
-        <v>5.0000000000000037E-2</v>
-      </c>
-      <c r="R42" s="10">
+        <v>0.22086857514638908</v>
+      </c>
+      <c r="AG42" s="10">
         <f t="shared" si="264"/>
-        <v>0.05</v>
-      </c>
-      <c r="S42" s="10">
-        <f t="shared" ref="S42:AH42" si="265">S32/S26</f>
-        <v>9.7846690423838117E-2</v>
-      </c>
-      <c r="T42" s="10">
+        <v>0.20385572139303479</v>
+      </c>
+      <c r="AH42" s="10">
+        <f t="shared" si="264"/>
+        <v>0.14358819987959059</v>
+      </c>
+      <c r="AI42" s="10">
+        <f t="shared" ref="AI42:AT42" si="265">AI32/AI26</f>
+        <v>0.27367392518146288</v>
+      </c>
+      <c r="AJ42" s="10">
         <f t="shared" si="265"/>
-        <v>4.6060188375832804E-2</v>
-      </c>
-      <c r="U42" s="10">
+        <v>0.25166852815385871</v>
+      </c>
+      <c r="AK42" s="10">
         <f t="shared" si="265"/>
-        <v>6.9604395869555552E-2</v>
-      </c>
-      <c r="V42" s="10">
+        <v>0.23455602325115246</v>
+      </c>
+      <c r="AL42" s="10">
         <f t="shared" si="265"/>
-        <v>7.4404428490017396E-2</v>
-      </c>
-      <c r="W42" s="10">
+        <v>8.1939994552034531E-2</v>
+      </c>
+      <c r="AM42" s="10">
         <f t="shared" si="265"/>
-        <v>0.12090518429034365</v>
-      </c>
-      <c r="X42" s="10">
+        <v>0.25060372658176366</v>
+      </c>
+      <c r="AN42" s="10">
         <f t="shared" si="265"/>
-        <v>0.11816980148290565</v>
-      </c>
-      <c r="Y42" s="10">
+        <v>0.19801508136660773</v>
+      </c>
+      <c r="AO42" s="10">
         <f t="shared" si="265"/>
-        <v>0.12013278718117143</v>
-      </c>
-      <c r="Z42" s="10">
+        <v>0.19342384172807112</v>
+      </c>
+      <c r="AP42" s="10">
         <f t="shared" si="265"/>
-        <v>5.156073336732684E-2</v>
-      </c>
-      <c r="AA42" s="10">
+        <v>7.0032220679818222E-2</v>
+      </c>
+      <c r="AQ42" s="10">
         <f t="shared" si="265"/>
-        <v>0.10152621101526216</v>
-      </c>
-      <c r="AB42" s="10">
+        <v>0.21004717270109657</v>
+      </c>
+      <c r="AR42" s="10">
         <f t="shared" si="265"/>
-        <v>0.14344911639244365</v>
-      </c>
-      <c r="AC42" s="10">
+        <v>0.22316270321107085</v>
+      </c>
+      <c r="AS42" s="10">
         <f t="shared" si="265"/>
-        <v>0.18814011041309728</v>
-      </c>
-      <c r="AD42" s="10">
+        <v>0.2243581488462485</v>
+      </c>
+      <c r="AT42" s="10">
         <f t="shared" si="265"/>
-        <v>8.384854582037661E-2</v>
-      </c>
-      <c r="AE42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.1661927877947296</v>
-      </c>
-      <c r="AF42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.22086857514638908</v>
-      </c>
-      <c r="AG42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.20385572139303479</v>
-      </c>
-      <c r="AH42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.14358819987959059</v>
-      </c>
-      <c r="AI42" s="10">
-        <f t="shared" ref="AI42:AT42" si="266">AI32/AI26</f>
-        <v>0.27367392518146288</v>
-      </c>
-      <c r="AJ42" s="10">
+        <v>0.16938003804003257</v>
+      </c>
+      <c r="AU42" s="10">
+        <f t="shared" ref="AU42:AX42" si="266">AU32/AU26</f>
+        <v>0.28093784683684786</v>
+      </c>
+      <c r="AV42" s="10">
         <f t="shared" si="266"/>
-        <v>0.25166852815385871</v>
-      </c>
-      <c r="AK42" s="10">
+        <v>0.27227935099850403</v>
+      </c>
+      <c r="AW42" s="10">
         <f t="shared" si="266"/>
-        <v>0.23455602325115246</v>
-      </c>
-      <c r="AL42" s="10">
+        <v>0.29613117957800245</v>
+      </c>
+      <c r="AX42" s="10">
         <f t="shared" si="266"/>
-        <v>8.1939994552034531E-2</v>
-      </c>
-      <c r="AM42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.25060372658176366</v>
-      </c>
-      <c r="AN42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.19801508136660773</v>
-      </c>
-      <c r="AO42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.19342384172807112</v>
-      </c>
-      <c r="AP42" s="10">
-        <f t="shared" si="266"/>
-        <v>7.0032220679818222E-2</v>
-      </c>
-      <c r="AQ42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.21004717270109657</v>
-      </c>
-      <c r="AR42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.22316270321107085</v>
-      </c>
-      <c r="AS42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.2243581488462485</v>
-      </c>
-      <c r="AT42" s="10">
-        <f t="shared" si="266"/>
-        <v>0.16938003804003257</v>
-      </c>
-      <c r="AU42" s="10">
-        <f t="shared" ref="AU42:AX42" si="267">AU32/AU26</f>
-        <v>0.28093784683684786</v>
-      </c>
-      <c r="AV42" s="10">
+        <v>0.22180256673010304</v>
+      </c>
+      <c r="AY42" s="10">
+        <f t="shared" ref="AY42:BB42" si="267">AY32/AY26</f>
+        <v>0.31746784535417527</v>
+      </c>
+      <c r="AZ42" s="10">
         <f t="shared" si="267"/>
-        <v>0.27227935099850403</v>
-      </c>
-      <c r="AW42" s="10">
+        <v>0.34070149469275762</v>
+      </c>
+      <c r="BA42" s="10">
         <f t="shared" si="267"/>
-        <v>0.29613117957800245</v>
-      </c>
-      <c r="AX42" s="10">
+        <v>0.32645333222361445</v>
+      </c>
+      <c r="BB42" s="10">
         <f t="shared" si="267"/>
-        <v>0.22180256673010304</v>
-      </c>
-      <c r="AY42" s="10">
-        <f t="shared" ref="AY42:BB42" si="268">AY32/AY26</f>
-        <v>0.31746784535417527</v>
-      </c>
-      <c r="AZ42" s="10">
+        <v>0.25485083756822885</v>
+      </c>
+      <c r="BD42" s="10">
+        <f t="shared" ref="BD42:BW42" si="268">BD32/BD26</f>
+        <v>0.11735339796796899</v>
+      </c>
+      <c r="BE42" s="10">
         <f t="shared" si="268"/>
-        <v>0.29785257685510802</v>
-      </c>
-      <c r="BA42" s="10">
+        <v>1.3850954289523567E-2</v>
+      </c>
+      <c r="BF42" s="10">
         <f t="shared" si="268"/>
-        <v>0.29910188525200743</v>
-      </c>
-      <c r="BB42" s="10">
+        <v>5.2198825848164897E-2</v>
+      </c>
+      <c r="BG42" s="10">
         <f t="shared" si="268"/>
-        <v>0.24190758188023714</v>
-      </c>
-      <c r="BD42" s="10">
-        <f t="shared" ref="BD42:BW42" si="269">BD32/BD26</f>
-        <v>0.11735339796796899</v>
-      </c>
-      <c r="BE42" s="10">
+        <v>7.3146805177289956E-2</v>
+      </c>
+      <c r="BH42" s="10">
+        <f t="shared" si="268"/>
+        <v>4.5109890669105875E-2</v>
+      </c>
+      <c r="BI42" s="10">
+        <f t="shared" si="268"/>
+        <v>5.0000000000000031E-2</v>
+      </c>
+      <c r="BJ42" s="10">
+        <f t="shared" si="268"/>
+        <v>7.1714541702031079E-2</v>
+      </c>
+      <c r="BK42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.10165511000233846</v>
+      </c>
+      <c r="BL42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.12910092289371833</v>
+      </c>
+      <c r="BM42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.18332666453265045</v>
+      </c>
+      <c r="BN42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.20860579286565689</v>
+      </c>
+      <c r="BO42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.17816520958008064</v>
+      </c>
+      <c r="BP42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.206204612241388</v>
+      </c>
+      <c r="BQ42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.26710665651305471</v>
+      </c>
+      <c r="BR42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.3092906611677817</v>
+      </c>
+      <c r="BS42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.33873121213942453</v>
+      </c>
+      <c r="BT42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.35153364983198732</v>
+      </c>
+      <c r="BU42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.36394114561274515</v>
+      </c>
+      <c r="BV42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.37598073896634615</v>
+      </c>
+      <c r="BW42" s="10">
+        <f t="shared" si="268"/>
+        <v>0.37800053044272786</v>
+      </c>
+      <c r="BX42" s="10">
+        <f t="shared" ref="BX42:CB42" si="269">BX32/BX26</f>
+        <v>0.37900052524230898</v>
+      </c>
+      <c r="BY42" s="10">
         <f t="shared" si="269"/>
-        <v>1.3850954289523567E-2</v>
-      </c>
-      <c r="BF42" s="10">
+        <v>0.37999071617130592</v>
+      </c>
+      <c r="BZ42" s="10">
         <f t="shared" si="269"/>
-        <v>5.2198825848164897E-2</v>
-      </c>
-      <c r="BG42" s="10">
+        <v>0.38097119934609702</v>
+      </c>
+      <c r="CA42" s="10">
         <f t="shared" si="269"/>
-        <v>7.3146805177289956E-2</v>
-      </c>
-      <c r="BH42" s="10">
+        <v>0.38194206994074315</v>
+      </c>
+      <c r="CB42" s="10">
         <f t="shared" si="269"/>
-        <v>4.5109890669105875E-2</v>
-      </c>
-      <c r="BI42" s="10">
-        <f t="shared" si="269"/>
-        <v>5.0000000000000031E-2</v>
-      </c>
-      <c r="BJ42" s="10">
-        <f t="shared" si="269"/>
-        <v>7.1714541702031079E-2</v>
-      </c>
-      <c r="BK42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.10165511000233846</v>
-      </c>
-      <c r="BL42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.12910092289371833</v>
-      </c>
-      <c r="BM42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.18332666453265045</v>
-      </c>
-      <c r="BN42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.20860579286565689</v>
-      </c>
-      <c r="BO42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.17816520958008064</v>
-      </c>
-      <c r="BP42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.206204612241388</v>
-      </c>
-      <c r="BQ42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.26710665651305471</v>
-      </c>
-      <c r="BR42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.28897616616518085</v>
-      </c>
-      <c r="BS42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.31957598617272048</v>
-      </c>
-      <c r="BT42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.34204213267724726</v>
-      </c>
-      <c r="BU42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.35344957662654064</v>
-      </c>
-      <c r="BV42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.36449418862039806</v>
-      </c>
-      <c r="BW42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.36449418862039806</v>
-      </c>
-      <c r="BX42" s="10">
-        <f t="shared" ref="BX42:CB42" si="270">BX32/BX26</f>
-        <v>0.36449418862039806</v>
-      </c>
-      <c r="BY42" s="10">
-        <f t="shared" si="270"/>
-        <v>0.36449418862039817</v>
-      </c>
-      <c r="BZ42" s="10">
-        <f t="shared" si="270"/>
-        <v>0.36449418862039806</v>
-      </c>
-      <c r="CA42" s="10">
-        <f t="shared" si="270"/>
-        <v>0.36449418862039812</v>
-      </c>
-      <c r="CB42" s="10">
-        <f t="shared" si="270"/>
-        <v>0.36449418862039806</v>
+        <v>0.38290342219622603</v>
       </c>
     </row>
     <row r="43" spans="2:150" s="1" customFormat="1">
@@ -9857,307 +9867,307 @@
         <v>0.1162993512448228</v>
       </c>
       <c r="D43" s="9">
-        <f t="shared" ref="D43:R43" si="271">D29/D$26</f>
+        <f t="shared" ref="D43:R43" si="270">D29/D$26</f>
         <v>0.10717598740195179</v>
       </c>
       <c r="E43" s="9">
+        <f t="shared" si="270"/>
+        <v>9.7855423015753173E-2</v>
+      </c>
+      <c r="F43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.1089293159636837</v>
+      </c>
+      <c r="G43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.10794361654970637</v>
+      </c>
+      <c r="H43" s="9">
+        <f t="shared" si="270"/>
+        <v>9.0094277335167602E-2</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.10334233932534524</v>
+      </c>
+      <c r="J43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.13717731463271385</v>
+      </c>
+      <c r="K43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.12375145331374603</v>
+      </c>
+      <c r="L43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.11986424222378143</v>
+      </c>
+      <c r="M43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.11971202659986022</v>
+      </c>
+      <c r="N43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.12294517786931952</v>
+      </c>
+      <c r="O43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.12</v>
+      </c>
+      <c r="P43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.12</v>
+      </c>
+      <c r="R43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.12</v>
+      </c>
+      <c r="S43" s="9">
+        <f t="shared" ref="S43:AH43" si="271">S29/S$26</f>
+        <v>0.10285086056562287</v>
+      </c>
+      <c r="T43" s="9">
         <f t="shared" si="271"/>
-        <v>9.7855423015753173E-2</v>
-      </c>
-      <c r="F43" s="9">
+        <v>9.845939581897542E-2</v>
+      </c>
+      <c r="U43" s="9">
         <f t="shared" si="271"/>
-        <v>0.1089293159636837</v>
-      </c>
-      <c r="G43" s="9">
+        <v>0.1047289915318651</v>
+      </c>
+      <c r="V43" s="9">
         <f t="shared" si="271"/>
-        <v>0.10794361654970637</v>
-      </c>
-      <c r="H43" s="9">
+        <v>0.17601689177670515</v>
+      </c>
+      <c r="W43" s="9">
         <f t="shared" si="271"/>
-        <v>9.0094277335167602E-2</v>
-      </c>
-      <c r="I43" s="9">
+        <v>0.12944787993979268</v>
+      </c>
+      <c r="X43" s="9">
         <f t="shared" si="271"/>
-        <v>0.10334233932534524</v>
-      </c>
-      <c r="J43" s="9">
+        <v>0.13505991665283143</v>
+      </c>
+      <c r="Y43" s="9">
         <f t="shared" si="271"/>
-        <v>0.13717731463271385</v>
-      </c>
-      <c r="K43" s="9">
+        <v>0.10885187226170524</v>
+      </c>
+      <c r="Z43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12375145331374603</v>
-      </c>
-      <c r="L43" s="9">
+        <v>0.2215039641373806</v>
+      </c>
+      <c r="AA43" s="9">
         <f t="shared" si="271"/>
-        <v>0.11986424222378143</v>
-      </c>
-      <c r="M43" s="9">
+        <v>0.13638575536385755</v>
+      </c>
+      <c r="AB43" s="9">
         <f t="shared" si="271"/>
-        <v>0.11971202659986022</v>
-      </c>
-      <c r="N43" s="9">
+        <v>0.1225269144830388</v>
+      </c>
+      <c r="AC43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12294517786931952</v>
-      </c>
-      <c r="O43" s="9">
+        <v>0.10542547115933751</v>
+      </c>
+      <c r="AD43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12</v>
-      </c>
-      <c r="P43" s="9">
+        <v>0.16076458752515085</v>
+      </c>
+      <c r="AE43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12</v>
-      </c>
-      <c r="Q43" s="9">
+        <v>8.7343966712898749E-2</v>
+      </c>
+      <c r="AF43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12</v>
-      </c>
-      <c r="R43" s="9">
+        <v>7.065712426805465E-2</v>
+      </c>
+      <c r="AG43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12</v>
-      </c>
-      <c r="S43" s="9">
-        <f t="shared" ref="S43:AH43" si="272">S29/S$26</f>
-        <v>0.10285086056562287</v>
-      </c>
-      <c r="T43" s="9">
+        <v>8.2027363184079605E-2</v>
+      </c>
+      <c r="AH43" s="9">
+        <f t="shared" si="271"/>
+        <v>0.11478025285972306</v>
+      </c>
+      <c r="AI43" s="9">
+        <f t="shared" ref="AI43:AT43" si="272">AI29/AI$26</f>
+        <v>7.1538246789503074E-2</v>
+      </c>
+      <c r="AJ43" s="9">
         <f t="shared" si="272"/>
-        <v>9.845939581897542E-2</v>
-      </c>
-      <c r="U43" s="9">
+        <v>8.2268653463728234E-2</v>
+      </c>
+      <c r="AK43" s="9">
         <f t="shared" si="272"/>
-        <v>0.1047289915318651</v>
-      </c>
-      <c r="V43" s="9">
+        <v>8.497360860559898E-2</v>
+      </c>
+      <c r="AL43" s="9">
         <f t="shared" si="272"/>
-        <v>0.17601689177670515</v>
-      </c>
-      <c r="W43" s="9">
+        <v>0.10282386208864619</v>
+      </c>
+      <c r="AM43" s="9">
         <f t="shared" si="272"/>
-        <v>0.12944787993979268</v>
-      </c>
-      <c r="X43" s="9">
+        <v>7.0667785149597095E-2</v>
+      </c>
+      <c r="AN43" s="9">
         <f t="shared" si="272"/>
-        <v>0.13505991665283143</v>
-      </c>
-      <c r="Y43" s="9">
+        <v>7.2144640594220891E-2</v>
+      </c>
+      <c r="AO43" s="9">
         <f t="shared" si="272"/>
-        <v>0.10885187226170524</v>
-      </c>
-      <c r="Z43" s="9">
+        <v>7.1666498435449685E-2</v>
+      </c>
+      <c r="AP43" s="9">
         <f t="shared" si="272"/>
-        <v>0.2215039641373806</v>
-      </c>
-      <c r="AA43" s="9">
+        <v>0.1059079736630965</v>
+      </c>
+      <c r="AQ43" s="9">
         <f t="shared" si="272"/>
-        <v>0.13638575536385755</v>
-      </c>
-      <c r="AB43" s="9">
+        <v>6.8051216075476317E-2</v>
+      </c>
+      <c r="AR43" s="9">
         <f t="shared" si="272"/>
-        <v>0.1225269144830388</v>
-      </c>
-      <c r="AC43" s="9">
+        <v>7.6606451455302732E-2</v>
+      </c>
+      <c r="AS43" s="9">
         <f t="shared" si="272"/>
-        <v>0.10542547115933751</v>
-      </c>
-      <c r="AD43" s="9">
+        <v>6.5408525235023468E-2</v>
+      </c>
+      <c r="AT43" s="9">
         <f t="shared" si="272"/>
-        <v>0.16076458752515085</v>
-      </c>
-      <c r="AE43" s="9">
-        <f t="shared" si="272"/>
-        <v>8.7343966712898749E-2</v>
-      </c>
-      <c r="AF43" s="9">
-        <f t="shared" si="272"/>
-        <v>7.065712426805465E-2</v>
-      </c>
-      <c r="AG43" s="9">
-        <f t="shared" si="272"/>
-        <v>8.2027363184079605E-2</v>
-      </c>
-      <c r="AH43" s="9">
-        <f t="shared" si="272"/>
-        <v>0.11478025285972306</v>
-      </c>
-      <c r="AI43" s="9">
-        <f t="shared" ref="AI43:AT43" si="273">AI29/AI$26</f>
-        <v>7.1538246789503074E-2</v>
-      </c>
-      <c r="AJ43" s="9">
+        <v>0.10377230323340278</v>
+      </c>
+      <c r="AU43" s="9">
+        <f t="shared" ref="AU43:AX43" si="273">AU29/AU$26</f>
+        <v>6.982626141893622E-2</v>
+      </c>
+      <c r="AV43" s="9">
         <f t="shared" si="273"/>
-        <v>8.2268653463728234E-2</v>
-      </c>
-      <c r="AK43" s="9">
+        <v>6.7379410626301095E-2</v>
+      </c>
+      <c r="AW43" s="9">
         <f t="shared" si="273"/>
-        <v>8.497360860559898E-2</v>
-      </c>
-      <c r="AL43" s="9">
+        <v>6.5437112583590334E-2</v>
+      </c>
+      <c r="AX43" s="9">
         <f t="shared" si="273"/>
-        <v>0.10282386208864619</v>
-      </c>
-      <c r="AM43" s="9">
-        <f t="shared" si="273"/>
-        <v>7.0667785149597095E-2</v>
-      </c>
-      <c r="AN43" s="9">
-        <f t="shared" si="273"/>
-        <v>7.2144640594220891E-2</v>
-      </c>
-      <c r="AO43" s="9">
-        <f t="shared" si="273"/>
-        <v>7.1666498435449685E-2</v>
-      </c>
-      <c r="AP43" s="9">
-        <f t="shared" si="273"/>
-        <v>0.1059079736630965</v>
-      </c>
-      <c r="AQ43" s="9">
-        <f t="shared" si="273"/>
-        <v>6.8051216075476317E-2</v>
-      </c>
-      <c r="AR43" s="9">
-        <f t="shared" si="273"/>
-        <v>7.6606451455302732E-2</v>
-      </c>
-      <c r="AS43" s="9">
-        <f t="shared" si="273"/>
-        <v>6.5408525235023468E-2</v>
-      </c>
-      <c r="AT43" s="9">
-        <f t="shared" si="273"/>
-        <v>0.10377230323340278</v>
-      </c>
-      <c r="AU43" s="9">
-        <f t="shared" ref="AU43:AX43" si="274">AU29/AU$26</f>
-        <v>6.982626141893622E-2</v>
-      </c>
-      <c r="AV43" s="9">
+        <v>9.5271556141121358E-2</v>
+      </c>
+      <c r="AY43" s="9">
+        <f t="shared" ref="AY43:BB43" si="274">AY29/AY$26</f>
+        <v>6.5295746860416587E-2</v>
+      </c>
+      <c r="AZ43" s="9">
         <f t="shared" si="274"/>
-        <v>6.7379410626301095E-2</v>
-      </c>
-      <c r="AW43" s="9">
+        <v>6.4381904830673686E-2</v>
+      </c>
+      <c r="BA43" s="9">
         <f t="shared" si="274"/>
-        <v>6.5437112583590334E-2</v>
-      </c>
-      <c r="AX43" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BB43" s="9">
         <f t="shared" si="274"/>
-        <v>9.5271556141121358E-2</v>
-      </c>
-      <c r="AY43" s="9">
-        <f t="shared" ref="AY43:BB43" si="275">AY29/AY$26</f>
-        <v>6.5295746860416587E-2</v>
-      </c>
-      <c r="AZ43" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="BD43" s="9">
+        <f t="shared" ref="BD43:BW43" si="275">BD29/BD$26</f>
+        <v>0.12564466386671314</v>
+      </c>
+      <c r="BE43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.13430067254373584</v>
+      </c>
+      <c r="BF43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.10742606916989633</v>
+      </c>
+      <c r="BG43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.11030407713034202</v>
+      </c>
+      <c r="BH43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.12155581722634566</v>
+      </c>
+      <c r="BI43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="BJ43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.12283917484368646</v>
+      </c>
+      <c r="BK43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.15001855063742303</v>
+      </c>
+      <c r="BL43" s="9">
+        <f t="shared" si="275"/>
+        <v>0.13161159075121565</v>
+      </c>
+      <c r="BM43" s="9">
+        <f t="shared" si="275"/>
+        <v>8.9164532650448144E-2</v>
+      </c>
+      <c r="BN43" s="9">
+        <f t="shared" si="275"/>
+        <v>8.5697642313105685E-2</v>
+      </c>
+      <c r="BO43" s="9">
+        <f t="shared" si="275"/>
+        <v>8.0042763698933442E-2</v>
+      </c>
+      <c r="BP43" s="9">
+        <f t="shared" si="275"/>
+        <v>7.8814943970489243E-2</v>
+      </c>
+      <c r="BQ43" s="9">
+        <f t="shared" si="275"/>
+        <v>7.4805966016168873E-2</v>
+      </c>
+      <c r="BR43" s="9">
+        <f t="shared" si="275"/>
+        <v>7.5258878898866732E-2</v>
+      </c>
+      <c r="BS43" s="9">
         <f t="shared" si="275"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BA43" s="9">
+      <c r="BT43" s="9">
         <f t="shared" si="275"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BB43" s="9">
+      <c r="BU43" s="9">
         <f t="shared" si="275"/>
-        <v>0.1</v>
-      </c>
-      <c r="BD43" s="9">
-        <f t="shared" ref="BD43:BW43" si="276">BD29/BD$26</f>
-        <v>0.12564466386671314</v>
-      </c>
-      <c r="BE43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.13430067254373584</v>
-      </c>
-      <c r="BF43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.10742606916989633</v>
-      </c>
-      <c r="BG43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.11030407713034202</v>
-      </c>
-      <c r="BH43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.12155581722634566</v>
-      </c>
-      <c r="BI43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="BJ43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.12283917484368646</v>
-      </c>
-      <c r="BK43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.15001855063742303</v>
-      </c>
-      <c r="BL43" s="9">
-        <f t="shared" si="276"/>
-        <v>0.13161159075121565</v>
-      </c>
-      <c r="BM43" s="9">
-        <f t="shared" si="276"/>
-        <v>8.9164532650448144E-2</v>
-      </c>
-      <c r="BN43" s="9">
-        <f t="shared" si="276"/>
-        <v>8.5697642313105685E-2</v>
-      </c>
-      <c r="BO43" s="9">
-        <f t="shared" si="276"/>
-        <v>8.0042763698933442E-2</v>
-      </c>
-      <c r="BP43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.8814943970489243E-2</v>
-      </c>
-      <c r="BQ43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.4805966016168873E-2</v>
-      </c>
-      <c r="BR43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.6336599082977546E-2</v>
-      </c>
-      <c r="BS43" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BV43" s="9">
+        <f t="shared" si="275"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BW43" s="9">
+        <f t="shared" si="275"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BX43" s="9">
+        <f t="shared" ref="BX43:CB43" si="276">BX29/BX$26</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BY43" s="9">
         <f t="shared" si="276"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BT43" s="9">
+      <c r="BZ43" s="9">
         <f t="shared" si="276"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BU43" s="9">
+      <c r="CA43" s="9">
         <f t="shared" si="276"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BV43" s="9">
+      <c r="CB43" s="9">
         <f t="shared" si="276"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BW43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BX43" s="9">
-        <f t="shared" ref="BX43:CB43" si="277">BX29/BX$26</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BY43" s="9">
-        <f t="shared" si="277"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BZ43" s="9">
-        <f t="shared" si="277"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="CA43" s="9">
-        <f t="shared" si="277"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="CB43" s="9">
-        <f t="shared" si="277"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -10174,192 +10184,192 @@
         <v>0.19934764881761358</v>
       </c>
       <c r="H44" s="9">
-        <f t="shared" ref="H44:AL44" si="278">H30/D30-1</f>
+        <f t="shared" ref="H44:AL44" si="277">H30/D30-1</f>
         <v>0.23684040976741194</v>
       </c>
       <c r="I44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.2659933012350848</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.28277352030001635</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.29730758770737009</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.34622597280825129</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.42007225947268778</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.43681082970542451</v>
       </c>
       <c r="O44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.32458457367266225</v>
       </c>
       <c r="P44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.24590322518234764</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.16067581886563964</v>
       </c>
       <c r="R44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.19134689815326755</v>
       </c>
       <c r="S44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.35632741775517518</v>
       </c>
       <c r="T44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.38256958139871955</v>
       </c>
       <c r="U44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.28009630818619558</v>
       </c>
       <c r="V44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>-0.19105941977193741</v>
       </c>
       <c r="W44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.16958381952547641</v>
       </c>
       <c r="X44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.18757019842755507</v>
       </c>
       <c r="Y44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.2813479623824453</v>
       </c>
       <c r="Z44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.58864027538726327</v>
       </c>
       <c r="AA44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.23977386099102094</v>
       </c>
       <c r="AB44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.20807061790668357</v>
       </c>
       <c r="AC44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.16146788990825689</v>
       </c>
       <c r="AD44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.47778981581798519</v>
       </c>
       <c r="AE44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.21727467811158796</v>
       </c>
       <c r="AF44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.1351774530271399</v>
       </c>
       <c r="AG44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.19483938915218535</v>
       </c>
       <c r="AH44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.18988269794721413</v>
       </c>
       <c r="AI44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.15733803437637728</v>
       </c>
       <c r="AJ44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.23517241379310327</v>
       </c>
       <c r="AK44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.24261789334508577</v>
       </c>
       <c r="AL44" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v>0.32984185664407484</v>
       </c>
       <c r="AM44" s="9">
-        <f t="shared" ref="AM44:AM45" si="279">AM30/AI30-1</f>
+        <f t="shared" ref="AM44:AM45" si="278">AM30/AI30-1</f>
         <v>0.25190403655750182</v>
       </c>
       <c r="AN44" s="9">
-        <f t="shared" ref="AN44:AN45" si="280">AN30/AJ30-1</f>
+        <f t="shared" ref="AN44:AN45" si="279">AN30/AJ30-1</f>
         <v>0.3340777963893542</v>
       </c>
       <c r="AO44" s="9">
-        <f t="shared" ref="AO44:AO45" si="281">AO30/AK30-1</f>
+        <f t="shared" ref="AO44:AO45" si="280">AO30/AK30-1</f>
         <v>0.17520837027841818</v>
       </c>
       <c r="AP44" s="9">
-        <f t="shared" ref="AP44:AP45" si="282">AP30/AL30-1</f>
+        <f t="shared" ref="AP44:AP45" si="281">AP30/AL30-1</f>
         <v>4.0772200772200673E-2</v>
       </c>
       <c r="AQ44" s="9">
-        <f t="shared" ref="AQ44:AQ45" si="283">AQ30/AM30-1</f>
+        <f t="shared" ref="AQ44:AQ45" si="282">AQ30/AM30-1</f>
         <v>4.5323193916349647E-2</v>
       </c>
       <c r="AR44" s="9">
-        <f t="shared" ref="AR44:AR45" si="284">AR30/AN30-1</f>
+        <f t="shared" ref="AR44:AR45" si="283">AR30/AN30-1</f>
         <v>-8.2031249999999889E-2</v>
       </c>
       <c r="AS44" s="9">
-        <f t="shared" ref="AS44:AS45" si="285">AS30/AO30-1</f>
+        <f t="shared" ref="AS44:AS45" si="284">AS30/AO30-1</f>
         <v>-8.2993813188471099E-3</v>
       </c>
       <c r="AT44" s="9">
-        <f t="shared" ref="AT44:AT45" si="286">AT30/AP30-1</f>
+        <f t="shared" ref="AT44:AT45" si="285">AT30/AP30-1</f>
         <v>-8.9033981302866216E-4</v>
       </c>
       <c r="AU44" s="9">
-        <f t="shared" ref="AU44:AU45" si="287">AU30/AQ30-1</f>
+        <f t="shared" ref="AU44:AU45" si="286">AU30/AQ30-1</f>
         <v>2.2115524516223006E-2</v>
       </c>
       <c r="AV44" s="9">
-        <f t="shared" ref="AV44:AV45" si="288">AV30/AR30-1</f>
+        <f t="shared" ref="AV44:AV45" si="287">AV30/AR30-1</f>
         <v>8.1003039513677821E-2</v>
       </c>
       <c r="AW44" s="9">
-        <f t="shared" ref="AW44:AW45" si="289">AW30/AS30-1</f>
+        <f t="shared" ref="AW44:AW45" si="288">AW30/AS30-1</f>
         <v>0.11853317102860617</v>
       </c>
       <c r="AX44" s="9">
-        <f t="shared" ref="AX44:AX45" si="290">AX30/AT30-1</f>
+        <f t="shared" ref="AX44:AX45" si="289">AX30/AT30-1</f>
         <v>0.15327491459973275</v>
       </c>
       <c r="AY44" s="9">
-        <f t="shared" ref="AY44:AY45" si="291">AY30/AU30-1</f>
+        <f t="shared" ref="AY44:AY45" si="290">AY30/AU30-1</f>
         <v>0.17124555160142352</v>
       </c>
       <c r="AZ44" s="9">
-        <f t="shared" ref="AZ44:AZ45" si="292">AZ30/AV30-1</f>
+        <f t="shared" ref="AZ44:AZ45" si="291">AZ30/AV30-1</f>
+        <v>0.15942640236187278</v>
+      </c>
+      <c r="BA44" s="9">
+        <f t="shared" ref="BA44:BA45" si="292">BA30/AW30-1</f>
         <v>0.12999999999999989</v>
       </c>
-      <c r="BA44" s="9">
-        <f t="shared" ref="BA44:BA45" si="293">BA30/AW30-1</f>
-        <v>9.000000000000008E-2</v>
-      </c>
       <c r="BB44" s="9">
-        <f t="shared" ref="BB44:BB45" si="294">BB30/AX30-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="BB44:BB45" si="293">BB30/AX30-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="BD44" s="9"/>
       <c r="BE44" s="9">
@@ -10367,95 +10377,95 @@
         <v>0.27013932587739764</v>
       </c>
       <c r="BF44" s="9">
-        <f t="shared" ref="BF44:BW44" si="295">BF30/BE30-1</f>
+        <f t="shared" ref="BF44:BW44" si="294">BF30/BE30-1</f>
         <v>0.15124556241793519</v>
       </c>
       <c r="BG44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.24698958996116382</v>
       </c>
       <c r="BH44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.37785319729590672</v>
       </c>
       <c r="BI44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.22554929477910646</v>
       </c>
       <c r="BJ44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.19575111525701705</v>
       </c>
       <c r="BK44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.28111565481807688</v>
       </c>
       <c r="BL44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.2645277459486004</v>
       </c>
       <c r="BM44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.18414239482200645</v>
       </c>
       <c r="BN44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.24290789833287785</v>
       </c>
       <c r="BO44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>0.19218083468930036</v>
       </c>
       <c r="BP44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>-1.2947729536316288E-2</v>
       </c>
       <c r="BQ44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v>9.3280514238732293E-2</v>
       </c>
       <c r="BR44" s="9">
-        <f t="shared" si="295"/>
-        <v>0.10861865044096541</v>
+        <f t="shared" si="294"/>
+        <v>0.13909653380734266</v>
       </c>
       <c r="BS44" s="9">
-        <f t="shared" si="295"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="294"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="BT44" s="9">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BU44" s="9">
+        <f t="shared" si="294"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BU44" s="9">
-        <f t="shared" si="295"/>
+      <c r="BV44" s="9">
+        <f t="shared" si="294"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BV44" s="9">
-        <f t="shared" si="295"/>
+      <c r="BW44" s="9">
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BW44" s="9">
-        <f t="shared" si="295"/>
+      <c r="BX44" s="9">
+        <f t="shared" ref="BX44" si="295">BX30/BW30-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BX44" s="9">
-        <f t="shared" ref="BX44" si="296">BX30/BW30-1</f>
+      <c r="BY44" s="9">
+        <f t="shared" ref="BY44:BY45" si="296">BY30/BX30-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BY44" s="9">
-        <f t="shared" ref="BY44:BY45" si="297">BY30/BX30-1</f>
+      <c r="BZ44" s="9">
+        <f t="shared" ref="BZ44:BZ45" si="297">BZ30/BY30-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BZ44" s="9">
-        <f t="shared" ref="BZ44:BZ45" si="298">BZ30/BY30-1</f>
+      <c r="CA44" s="9">
+        <f t="shared" ref="CA44:CA45" si="298">CA30/BZ30-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="CA44" s="9">
-        <f t="shared" ref="CA44:CA45" si="299">CA30/BZ30-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="CB44" s="9">
-        <f t="shared" ref="CB44:CB45" si="300">CB30/CA30-1</f>
+        <f t="shared" ref="CB44:CB45" si="299">CB30/CA30-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -10468,292 +10478,292 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9">
-        <f t="shared" ref="G45:AL45" si="301">G31/C31-1</f>
+        <f t="shared" ref="G45:AL45" si="300">G31/C31-1</f>
         <v>0.26682681412319265</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.3688075905483077</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.68842916188786218</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.64360364267129233</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.63665474060822902</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.5980604525610691</v>
       </c>
       <c r="M45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.42125499846201153</v>
       </c>
       <c r="N45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.43849188026859109</v>
       </c>
       <c r="O45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.24313961241242099</v>
       </c>
       <c r="P45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.20862719746418357</v>
       </c>
       <c r="Q45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>7.8671139487068498E-2</v>
       </c>
       <c r="R45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.1856000440197354</v>
       </c>
       <c r="S45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.70837817496324762</v>
       </c>
       <c r="T45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.84532405753891249</v>
       </c>
       <c r="U45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.80159844836811156</v>
       </c>
       <c r="V45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-2.4905608128700303</v>
       </c>
       <c r="W45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.43232115285640749</v>
       </c>
       <c r="X45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.45488546049555856</v>
       </c>
       <c r="Y45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.59628770301624123</v>
       </c>
       <c r="Z45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.57343020238713027</v>
       </c>
       <c r="AA45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-0.27416457060725841</v>
       </c>
       <c r="AB45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-0.27795629820051415</v>
       </c>
       <c r="AC45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-0.32209302325581401</v>
       </c>
       <c r="AD45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-1.8393799472295516</v>
       </c>
       <c r="AE45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.24801980198019802</v>
       </c>
       <c r="AF45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.23275478415665329</v>
       </c>
       <c r="AG45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.1646655231560894</v>
       </c>
       <c r="AH45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>8.2514734774066456E-2</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.17889726299087672</v>
       </c>
       <c r="AJ45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.20866425992779791</v>
       </c>
       <c r="AK45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.18483063328424154</v>
       </c>
       <c r="AL45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.44392014519056255</v>
       </c>
       <c r="AM45" s="9">
+        <f t="shared" si="278"/>
+        <v>0.338829071332436</v>
+      </c>
+      <c r="AN45" s="9">
         <f t="shared" si="279"/>
-        <v>0.338829071332436</v>
-      </c>
-      <c r="AN45" s="9">
+        <v>0.22252090800477897</v>
+      </c>
+      <c r="AO45" s="9">
         <f t="shared" si="280"/>
-        <v>0.22252090800477897</v>
-      </c>
-      <c r="AO45" s="9">
+        <v>0.15972653822249838</v>
+      </c>
+      <c r="AP45" s="9">
         <f t="shared" si="281"/>
-        <v>0.15972653822249838</v>
-      </c>
-      <c r="AP45" s="9">
+        <v>-1.3323278029160446E-2</v>
+      </c>
+      <c r="AQ45" s="9">
         <f t="shared" si="282"/>
-        <v>-1.3323278029160446E-2</v>
-      </c>
-      <c r="AQ45" s="9">
+        <v>7.5395828097510886E-3</v>
+      </c>
+      <c r="AR45" s="9">
         <f t="shared" si="283"/>
-        <v>7.5395828097510886E-3</v>
-      </c>
-      <c r="AR45" s="9">
+        <v>-1.9056926459809498E-2</v>
+      </c>
+      <c r="AS45" s="9">
         <f t="shared" si="284"/>
-        <v>-1.9056926459809498E-2</v>
-      </c>
-      <c r="AS45" s="9">
+        <v>0.282422293676313</v>
+      </c>
+      <c r="AT45" s="9">
         <f t="shared" si="285"/>
-        <v>0.282422293676313</v>
-      </c>
-      <c r="AT45" s="9">
+        <v>0.11923566878980885</v>
+      </c>
+      <c r="AU45" s="9">
         <f t="shared" si="286"/>
-        <v>0.11923566878980885</v>
-      </c>
-      <c r="AU45" s="9">
+        <v>7.7326016462959668E-3</v>
+      </c>
+      <c r="AV45" s="9">
         <f t="shared" si="287"/>
-        <v>7.7326016462959668E-3</v>
-      </c>
-      <c r="AV45" s="9">
+        <v>6.3511830635118338E-2</v>
+      </c>
+      <c r="AW45" s="9">
         <f t="shared" si="288"/>
-        <v>6.3511830635118338E-2</v>
-      </c>
-      <c r="AW45" s="9">
+        <v>-0.1278729628081906</v>
+      </c>
+      <c r="AX45" s="9">
         <f t="shared" si="289"/>
-        <v>-0.1278729628081906</v>
-      </c>
-      <c r="AX45" s="9">
+        <v>3.2779421807420883E-2</v>
+      </c>
+      <c r="AY45" s="9">
         <f t="shared" si="290"/>
-        <v>3.2779421807420883E-2</v>
-      </c>
-      <c r="AY45" s="9">
+        <v>4.3316831683168244E-2</v>
+      </c>
+      <c r="AZ45" s="9">
         <f t="shared" si="291"/>
-        <v>4.3316831683168244E-2</v>
-      </c>
-      <c r="AZ45" s="9">
+        <v>3.3255269320842995E-2</v>
+      </c>
+      <c r="BA45" s="9">
         <f t="shared" si="292"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA45" s="9">
+      <c r="BB45" s="9">
         <f t="shared" si="293"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB45" s="9">
-        <f t="shared" si="294"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="BD45" s="9"/>
       <c r="BE45" s="9">
-        <f t="shared" ref="BE45:BW45" si="302">BE31/BD31-1</f>
+        <f t="shared" ref="BE45:BW45" si="301">BE31/BD31-1</f>
         <v>-5.7114946784625475E-2</v>
       </c>
       <c r="BF45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.50643762480469889</v>
       </c>
       <c r="BG45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.49605936739119594</v>
       </c>
       <c r="BH45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.51007447885193602</v>
       </c>
       <c r="BI45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.17483508417028948</v>
       </c>
       <c r="BJ45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>-9.9352118633088016E-2</v>
       </c>
       <c r="BK45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.46241299303944294</v>
       </c>
       <c r="BL45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.45073774393146149</v>
       </c>
       <c r="BM45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.17694663167104108</v>
       </c>
       <c r="BN45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.25590039026203293</v>
       </c>
       <c r="BO45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>0.16373187333530637</v>
       </c>
       <c r="BP45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>9.3712251255642309E-2</v>
       </c>
       <c r="BQ45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>-1.0579550078474553E-2</v>
       </c>
       <c r="BR45" s="9">
-        <f t="shared" si="302"/>
-        <v>3.3160801363022019E-2</v>
+        <f t="shared" si="301"/>
+        <v>3.3977439633394058E-2</v>
       </c>
       <c r="BS45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BT45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BU45" s="9">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BV45" s="9">
+        <f t="shared" si="301"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BW45" s="9">
+        <f t="shared" si="301"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BV45" s="9">
-        <f t="shared" si="302"/>
+      <c r="BX45" s="9">
+        <f t="shared" ref="BX45" si="302">BX31/BW31-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BW45" s="9">
-        <f t="shared" si="302"/>
+      <c r="BY45" s="9">
+        <f t="shared" si="296"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BX45" s="9">
-        <f t="shared" ref="BX45" si="303">BX31/BW31-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BY45" s="9">
+      <c r="BZ45" s="9">
         <f t="shared" si="297"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BZ45" s="9">
+      <c r="CA45" s="9">
         <f t="shared" si="298"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="CA45" s="9">
+      <c r="CB45" s="9">
         <f t="shared" si="299"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="CB45" s="9">
-        <f t="shared" si="300"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -10770,196 +10780,196 @@
         <v>65</v>
       </c>
       <c r="G47" s="10">
-        <f t="shared" ref="G47:R47" si="304">G26/C26-1</f>
+        <f t="shared" ref="G47:R47" si="303">G26/C26-1</f>
         <v>0.24036852966079758</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.25345249361307398</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.27435196596018629</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.2633510036333313</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.2385974526194623</v>
       </c>
       <c r="L47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.22701090042054384</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.23337273454838536</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.22805860736781414</v>
       </c>
       <c r="O47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.20496157657763581</v>
       </c>
       <c r="P47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.17463187681112702</v>
       </c>
       <c r="Q47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.14683134342524973</v>
       </c>
       <c r="R47" s="10">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v>0.18172050854122612</v>
       </c>
       <c r="S47" s="10">
-        <f t="shared" ref="S47" si="305">S26/O26-1</f>
+        <f t="shared" ref="S47" si="304">S26/O26-1</f>
         <v>0.39156766338179749</v>
       </c>
       <c r="T47" s="10">
-        <f t="shared" ref="T47" si="306">T26/P26-1</f>
+        <f t="shared" ref="T47" si="305">T26/P26-1</f>
         <v>0.44205475410345207</v>
       </c>
       <c r="U47" s="10">
-        <f t="shared" ref="U47" si="307">U26/Q26-1</f>
+        <f t="shared" ref="U47" si="306">U26/Q26-1</f>
         <v>0.49673555377207057</v>
       </c>
       <c r="V47" s="10">
-        <f t="shared" ref="V47" si="308">V26/R26-1</f>
+        <f t="shared" ref="V47" si="307">V26/R26-1</f>
         <v>0.52455457216186252</v>
       </c>
       <c r="W47" s="10">
-        <f t="shared" ref="W47" si="309">W26/S26-1</f>
+        <f t="shared" ref="W47" si="308">W26/S26-1</f>
         <v>0.40339525362044126</v>
       </c>
       <c r="X47" s="10">
-        <f t="shared" ref="X47" si="310">X26/T26-1</f>
+        <f t="shared" ref="X47" si="309">X26/T26-1</f>
         <v>0.40273058810016082</v>
       </c>
       <c r="Y47" s="10">
-        <f t="shared" ref="Y47" si="311">Y26/U26-1</f>
+        <f t="shared" ref="Y47" si="310">Y26/U26-1</f>
         <v>0.34020015469728815</v>
       </c>
       <c r="Z47" s="10">
-        <f t="shared" ref="Z47" si="312">Z26/V26-1</f>
+        <f t="shared" ref="Z47" si="311">Z26/V26-1</f>
         <v>0.27428972222086934</v>
       </c>
       <c r="AA47" s="10">
-        <f t="shared" ref="AA47" si="313">AA26/W26-1</f>
+        <f t="shared" ref="AA47" si="312">AA26/W26-1</f>
         <v>0.22127267363898739</v>
       </c>
       <c r="AB47" s="10">
-        <f t="shared" ref="AB47" si="314">AB26/X26-1</f>
+        <f t="shared" ref="AB47" si="313">AB26/X26-1</f>
         <v>0.25975742645299182</v>
       </c>
       <c r="AC47" s="10">
-        <f t="shared" ref="AC47" si="315">AC26/Y26-1</f>
+        <f t="shared" ref="AC47" si="314">AC26/Y26-1</f>
         <v>0.31357428208301785</v>
       </c>
       <c r="AD47" s="10">
-        <f t="shared" ref="AD47" si="316">AD26/Z26-1</f>
+        <f t="shared" ref="AD47" si="315">AD26/Z26-1</f>
         <v>0.30604203185834744</v>
       </c>
       <c r="AE47" s="10">
-        <f t="shared" ref="AE47" si="317">AE26/AA26-1</f>
+        <f t="shared" ref="AE47" si="316">AE26/AA26-1</f>
         <v>0.27582393275823924</v>
       </c>
       <c r="AF47" s="10">
-        <f t="shared" ref="AF47" si="318">AF26/AB26-1</f>
+        <f t="shared" ref="AF47" si="317">AF26/AB26-1</f>
         <v>0.24883201300020308</v>
       </c>
       <c r="AG47" s="10">
-        <f t="shared" ref="AG47" si="319">AG26/AC26-1</f>
+        <f t="shared" ref="AG47" si="318">AG26/AC26-1</f>
         <v>0.22444317532838376</v>
       </c>
       <c r="AH47" s="10">
-        <f t="shared" ref="AH47" si="320">AH26/AD26-1</f>
+        <f t="shared" ref="AH47" si="319">AH26/AD26-1</f>
         <v>0.21529175050301808</v>
       </c>
       <c r="AI47" s="10">
-        <f t="shared" ref="AI47" si="321">AI26/AE26-1</f>
+        <f t="shared" ref="AI47" si="320">AI26/AE26-1</f>
         <v>0.24202496532593609</v>
       </c>
       <c r="AJ47" s="10">
-        <f t="shared" ref="AJ47" si="322">AJ26/AF26-1</f>
+        <f t="shared" ref="AJ47" si="321">AJ26/AF26-1</f>
         <v>0.19417696811971386</v>
       </c>
       <c r="AK47" s="10">
-        <f t="shared" ref="AK47" si="323">AK26/AG26-1</f>
+        <f t="shared" ref="AK47" si="322">AK26/AG26-1</f>
         <v>0.16347947761194037</v>
       </c>
       <c r="AL47" s="10">
-        <f t="shared" ref="AL47" si="324">AL26/AH26-1</f>
+        <f t="shared" ref="AL47" si="323">AL26/AH26-1</f>
         <v>0.16034015653220957</v>
       </c>
       <c r="AM47" s="10">
-        <f t="shared" ref="AM47" si="325">AM26/AI26-1</f>
+        <f t="shared" ref="AM47" si="324">AM26/AI26-1</f>
         <v>9.8241206030150741E-2</v>
       </c>
       <c r="AN47" s="10">
-        <f t="shared" ref="AN47" si="326">AN26/AJ26-1</f>
+        <f t="shared" ref="AN47" si="325">AN26/AJ26-1</f>
         <v>8.5578468495464355E-2</v>
       </c>
       <c r="AO47" s="10">
-        <f t="shared" ref="AO47" si="327">AO26/AK26-1</f>
+        <f t="shared" ref="AO47" si="326">AO26/AK26-1</f>
         <v>5.9076635264248001E-2</v>
       </c>
       <c r="AP47" s="10">
-        <f t="shared" ref="AP47" si="328">AP26/AL26-1</f>
+        <f t="shared" ref="AP47" si="327">AP26/AL26-1</f>
         <v>1.8523082510733868E-2</v>
       </c>
       <c r="AQ47" s="10">
-        <f t="shared" ref="AQ47" si="329">AQ26/AM26-1</f>
+        <f t="shared" ref="AQ47" si="328">AQ26/AM26-1</f>
         <v>3.7329367802943603E-2</v>
       </c>
       <c r="AR47" s="10">
-        <f t="shared" ref="AR47" si="330">AR26/AN26-1</f>
+        <f t="shared" ref="AR47" si="329">AR26/AN26-1</f>
         <v>2.7251853803590853E-2</v>
       </c>
       <c r="AS47" s="10">
-        <f t="shared" ref="AS47" si="331">AS26/AO26-1</f>
+        <f t="shared" ref="AS47" si="330">AS26/AO26-1</f>
         <v>7.7735439588169974E-2</v>
       </c>
       <c r="AT47" s="10">
-        <f t="shared" ref="AT47" si="332">AT26/AP26-1</f>
+        <f t="shared" ref="AT47" si="331">AT26/AP26-1</f>
         <v>0.12489652449663136</v>
       </c>
       <c r="AU47" s="10">
-        <f t="shared" ref="AU47" si="333">AU26/AQ26-1</f>
+        <f t="shared" ref="AU47" si="332">AU26/AQ26-1</f>
         <v>0.14812228144336204</v>
       </c>
       <c r="AV47" s="10">
-        <f t="shared" ref="AV47" si="334">AV26/AR26-1</f>
+        <f t="shared" ref="AV47" si="333">AV26/AR26-1</f>
         <v>0.16757661255847456</v>
       </c>
       <c r="AW47" s="10">
-        <f t="shared" ref="AW47" si="335">AW26/AS26-1</f>
+        <f t="shared" ref="AW47" si="334">AW26/AS26-1</f>
         <v>0.15020429188569029</v>
       </c>
       <c r="AX47" s="10">
-        <f t="shared" ref="AX47" si="336">AX26/AT26-1</f>
+        <f t="shared" ref="AX47" si="335">AX26/AT26-1</f>
         <v>0.16005117290100546</v>
       </c>
       <c r="AY47" s="10">
-        <f t="shared" ref="AY47" si="337">AY26/AU26-1</f>
+        <f t="shared" ref="AY47" si="336">AY26/AU26-1</f>
         <v>0.12511739093315111</v>
       </c>
       <c r="AZ47" s="10">
-        <f t="shared" ref="AZ47" si="338">AZ26/AV26-1</f>
-        <v>0.15999999999999992</v>
+        <f t="shared" ref="AZ47" si="337">AZ26/AV26-1</f>
+        <v>0.15899699768811537</v>
       </c>
       <c r="BA47" s="10">
-        <f t="shared" ref="BA47" si="339">BA26/AW26-1</f>
+        <f t="shared" ref="BA47" si="338">BA26/AW26-1</f>
         <v>0.12999999999999989</v>
       </c>
       <c r="BB47" s="10">
-        <f t="shared" ref="BB47" si="340">BB26/AX26-1</f>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" ref="BB47" si="339">BB26/AX26-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="BC47" s="10"/>
       <c r="BD47" s="10">
@@ -10967,15 +10977,15 @@
         <v>-0.51767354003612276</v>
       </c>
       <c r="BE47" s="10">
-        <f t="shared" ref="BE47:BG47" si="341">BE26/BD26-1</f>
+        <f t="shared" ref="BE47:BG47" si="340">BE26/BD26-1</f>
         <v>0.12628967879380015</v>
       </c>
       <c r="BF47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.21203109094828276</v>
       </c>
       <c r="BG47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.25833306283006174</v>
       </c>
       <c r="BH47" s="10">
@@ -10983,84 +10993,84 @@
         <v>0.23159576184233854</v>
       </c>
       <c r="BI47" s="10">
-        <f t="shared" ref="BI47:BX47" si="342">BI26/BH26-1</f>
+        <f t="shared" ref="BI47:BX47" si="341">BI26/BH26-1</f>
         <v>0.17644768184607984</v>
       </c>
       <c r="BJ47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>0.46601117890001431</v>
       </c>
       <c r="BK47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>0.3508386486955255</v>
       </c>
       <c r="BL47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>0.27599656870505318</v>
       </c>
       <c r="BM47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>0.24005160265952163</v>
       </c>
       <c r="BN47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>0.18832426376440448</v>
       </c>
       <c r="BO47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>6.4548497235559887E-2</v>
       </c>
       <c r="BP47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>6.6666455800301172E-2</v>
       </c>
       <c r="BQ47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v>0.15649713995961223</v>
       </c>
       <c r="BR47" s="10">
-        <f t="shared" si="342"/>
-        <v>0.11778930742623905</v>
+        <f t="shared" si="341"/>
+        <v>0.13330694932681064</v>
       </c>
       <c r="BS47" s="10">
-        <f t="shared" si="342"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="341"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="BT47" s="10">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="BU47" s="10">
+        <f t="shared" si="341"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BU47" s="10">
-        <f t="shared" si="342"/>
+      <c r="BV47" s="10">
+        <f t="shared" si="341"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BW47" s="10">
+        <f t="shared" si="341"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BV47" s="10">
-        <f t="shared" si="342"/>
+      <c r="BX47" s="10">
+        <f t="shared" si="341"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BW47" s="10">
-        <f t="shared" si="342"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BX47" s="10">
-        <f t="shared" si="342"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BY47" s="10">
-        <f t="shared" ref="BY47" si="343">BY26/BX26-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BY47" si="342">BY26/BX26-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BZ47" s="10">
-        <f t="shared" ref="BZ47" si="344">BZ26/BY26-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BZ47" si="343">BZ26/BY26-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="CA47" s="10">
-        <f t="shared" ref="CA47" si="345">CA26/BZ26-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="CA47" si="344">CA26/BZ26-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="CB47" s="10">
-        <f t="shared" ref="CB47" si="346">CB26/CA26-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="CB47" si="345">CB26/CA26-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="CD47" t="s">
         <v>85</v>
@@ -11078,211 +11088,211 @@
         <v>4.4348368736699895E-2</v>
       </c>
       <c r="E48" s="10">
-        <f t="shared" ref="E48:R48" si="347">E26/D26-1</f>
+        <f t="shared" ref="E48:R48" si="346">E26/D26-1</f>
         <v>3.4250943544435364E-2</v>
       </c>
       <c r="F48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>6.2595897464645001E-2</v>
       </c>
       <c r="G48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>8.07152642461475E-2</v>
       </c>
       <c r="H48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>5.5364624053904965E-2</v>
       </c>
       <c r="I48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>5.1495553216299061E-2</v>
       </c>
       <c r="J48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>5.3422939169821548E-2</v>
       </c>
       <c r="K48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>5.9540198608768691E-2</v>
       </c>
       <c r="L48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>4.5492137008471545E-2</v>
       </c>
       <c r="M48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>5.6947371365129396E-2</v>
       </c>
       <c r="N48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>4.8884146218695301E-2</v>
       </c>
       <c r="O48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>3.9612621501393219E-2</v>
       </c>
       <c r="P48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>1.9176391145624416E-2</v>
       </c>
       <c r="Q48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>3.1932129343499538E-2</v>
       </c>
       <c r="R48" s="10">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v>8.0793539325842545E-2</v>
       </c>
       <c r="S48" s="10">
-        <f t="shared" ref="S48" si="348">S26/R26-1</f>
+        <f t="shared" ref="S48" si="347">S26/R26-1</f>
         <v>0.22422459123670935</v>
       </c>
       <c r="T48" s="10">
-        <f t="shared" ref="T48" si="349">T26/S26-1</f>
+        <f t="shared" ref="T48" si="348">T26/S26-1</f>
         <v>5.6152854651603468E-2</v>
       </c>
       <c r="U48" s="10">
-        <f t="shared" ref="U48" si="350">U26/T26-1</f>
+        <f t="shared" ref="U48" si="349">U26/T26-1</f>
         <v>7.1061624167240822E-2</v>
       </c>
       <c r="V48" s="10">
-        <f t="shared" ref="V48" si="351">V26/U26-1</f>
+        <f t="shared" ref="V48" si="350">V26/U26-1</f>
         <v>0.10088166729895054</v>
       </c>
       <c r="W48" s="10">
-        <f t="shared" ref="W48" si="352">W26/V26-1</f>
+        <f t="shared" ref="W48" si="351">W26/V26-1</f>
         <v>0.12693308070353182</v>
       </c>
       <c r="X48" s="10">
-        <f t="shared" ref="X48" si="353">X26/W26-1</f>
+        <f t="shared" ref="X48" si="352">X26/W26-1</f>
         <v>5.5652647468472649E-2</v>
       </c>
       <c r="Y48" s="10">
-        <f t="shared" ref="Y48" si="354">Y26/X26-1</f>
+        <f t="shared" ref="Y48" si="353">Y26/X26-1</f>
         <v>2.3316213802253571E-2</v>
       </c>
       <c r="Z48" s="10">
-        <f t="shared" ref="Z48" si="355">Z26/Y26-1</f>
+        <f t="shared" ref="Z48" si="354">Z26/Y26-1</f>
         <v>4.6740808903493969E-2</v>
       </c>
       <c r="AA48" s="10">
-        <f t="shared" ref="AA48" si="356">AA26/Z26-1</f>
+        <f t="shared" ref="AA48" si="355">AA26/Z26-1</f>
         <v>8.0046831174609201E-2</v>
       </c>
       <c r="AB48" s="10">
-        <f t="shared" ref="AB48" si="357">AB26/AA26-1</f>
+        <f t="shared" ref="AB48" si="356">AB26/AA26-1</f>
         <v>8.8918380889183801E-2</v>
       </c>
       <c r="AC48" s="10">
-        <f t="shared" ref="AC48" si="358">AC26/AB26-1</f>
+        <f t="shared" ref="AC48" si="357">AC26/AB26-1</f>
         <v>6.7032297379646666E-2</v>
       </c>
       <c r="AD48" s="10">
-        <f t="shared" ref="AD48" si="359">AD26/AC26-1</f>
+        <f t="shared" ref="AD48" si="358">AD26/AC26-1</f>
         <v>4.073862554730634E-2</v>
       </c>
       <c r="AE48" s="10">
-        <f t="shared" ref="AE48" si="360">AE26/AD26-1</f>
+        <f t="shared" ref="AE48" si="359">AE26/AD26-1</f>
         <v>5.5057618437900135E-2</v>
       </c>
       <c r="AF48" s="10">
-        <f t="shared" ref="AF48" si="361">AF26/AE26-1</f>
+        <f t="shared" ref="AF48" si="360">AF26/AE26-1</f>
         <v>6.5880721220527017E-2</v>
       </c>
       <c r="AG48" s="10">
-        <f t="shared" ref="AG48" si="362">AG26/AF26-1</f>
+        <f t="shared" ref="AG48" si="361">AG26/AF26-1</f>
         <v>4.6193884189980494E-2</v>
       </c>
       <c r="AH48" s="10">
-        <f t="shared" ref="AH48" si="363">AH26/AG26-1</f>
+        <f t="shared" ref="AH48" si="362">AH26/AG26-1</f>
         <v>3.2960199004975044E-2</v>
       </c>
       <c r="AI48" s="10">
-        <f t="shared" ref="AI48" si="364">AI26/AH26-1</f>
+        <f t="shared" ref="AI48" si="363">AI26/AH26-1</f>
         <v>7.8266104756171018E-2</v>
       </c>
       <c r="AJ48" s="10">
-        <f t="shared" ref="AJ48" si="365">AJ26/AI26-1</f>
+        <f t="shared" ref="AJ48" si="364">AJ26/AI26-1</f>
         <v>2.4818537130094853E-2</v>
       </c>
       <c r="AK48" s="10">
-        <f t="shared" ref="AK48" si="366">AK26/AJ26-1</f>
+        <f t="shared" ref="AK48" si="365">AK26/AJ26-1</f>
         <v>1.9300444032798403E-2</v>
       </c>
       <c r="AL48" s="10">
-        <f t="shared" ref="AL48" si="367">AL26/AK26-1</f>
+        <f t="shared" ref="AL48" si="366">AL26/AK26-1</f>
         <v>3.0173047370882555E-2</v>
       </c>
       <c r="AM48" s="10">
-        <f t="shared" ref="AM48" si="368">AM26/AL26-1</f>
+        <f t="shared" ref="AM48" si="367">AM26/AL26-1</f>
         <v>2.0559583879210752E-2</v>
       </c>
       <c r="AN48" s="10">
-        <f t="shared" ref="AN48" si="369">AN26/AM26-1</f>
+        <f t="shared" ref="AN48" si="368">AN26/AM26-1</f>
         <v>1.3002364066193817E-2</v>
       </c>
       <c r="AO48" s="10">
-        <f t="shared" ref="AO48" si="370">AO26/AN26-1</f>
+        <f t="shared" ref="AO48" si="369">AO26/AN26-1</f>
         <v>-5.5833678372918527E-3</v>
       </c>
       <c r="AP48" s="10">
-        <f t="shared" ref="AP48" si="371">AP26/AO26-1</f>
+        <f t="shared" ref="AP48" si="370">AP26/AO26-1</f>
         <v>-9.2737458362773806E-3</v>
       </c>
       <c r="AQ48" s="10">
-        <f t="shared" ref="AQ48" si="372">AQ26/AP26-1</f>
+        <f t="shared" ref="AQ48" si="371">AQ26/AP26-1</f>
         <v>3.9403471682734503E-2</v>
       </c>
       <c r="AR48" s="10">
-        <f t="shared" ref="AR48" si="373">AR26/AQ26-1</f>
+        <f t="shared" ref="AR48" si="372">AR26/AQ26-1</f>
         <v>3.1611836059548537E-3</v>
       </c>
       <c r="AS48" s="10">
-        <f t="shared" ref="AS48" si="374">AS26/AR26-1</f>
+        <f t="shared" ref="AS48" si="373">AS26/AR26-1</f>
         <v>4.3286553564667374E-2</v>
       </c>
       <c r="AT48" s="10">
-        <f t="shared" ref="AT48" si="375">AT26/AS26-1</f>
+        <f t="shared" ref="AT48" si="374">AT26/AS26-1</f>
         <v>3.407986700539678E-2</v>
       </c>
       <c r="AU48" s="10">
-        <f t="shared" ref="AU48" si="376">AU26/AT26-1</f>
+        <f t="shared" ref="AU48" si="375">AU26/AT26-1</f>
         <v>6.0864052169187666E-2</v>
       </c>
       <c r="AV48" s="10">
-        <f t="shared" ref="AV48" si="377">AV26/AU26-1</f>
+        <f t="shared" ref="AV48" si="376">AV26/AU26-1</f>
         <v>2.0159224792964947E-2</v>
       </c>
       <c r="AW48" s="10">
-        <f t="shared" ref="AW48" si="378">AW26/AV26-1</f>
+        <f t="shared" ref="AW48" si="377">AW26/AV26-1</f>
         <v>2.7763539171278495E-2</v>
       </c>
       <c r="AX48" s="10">
-        <f t="shared" ref="AX48" si="379">AX26/AW26-1</f>
+        <f t="shared" ref="AX48" si="378">AX26/AW26-1</f>
         <v>4.2932608629270952E-2</v>
       </c>
       <c r="AY48" s="10">
-        <f t="shared" ref="AY48" si="380">AY26/AX26-1</f>
+        <f t="shared" ref="AY48" si="379">AY26/AX26-1</f>
         <v>2.8917191236031758E-2</v>
       </c>
       <c r="AZ48" s="10">
-        <f t="shared" ref="AZ48" si="381">AZ26/AY26-1</f>
-        <v>5.1787760367264735E-2</v>
+        <f t="shared" ref="AZ48" si="380">AZ26/AY26-1</f>
+        <v>5.0878324543764508E-2</v>
       </c>
       <c r="BA48" s="10">
-        <f t="shared" ref="BA48" si="382">BA26/AZ26-1</f>
-        <v>1.1834476409866568E-3</v>
+        <f t="shared" ref="BA48" si="381">BA26/AZ26-1</f>
+        <v>2.0498772474546456E-3</v>
       </c>
       <c r="BB48" s="10">
-        <f t="shared" ref="BB48" si="383">BB26/BA26-1</f>
-        <v>-2.1673836153073056E-2</v>
+        <f t="shared" ref="BB48" si="382">BB26/BA26-1</f>
+        <v>3.3703116517507903E-2</v>
       </c>
       <c r="CD48" t="s">
         <v>86</v>
       </c>
       <c r="CE48" s="2">
         <f>NPV(CE47,BQ37:ET37)</f>
-        <v>237154.54970478042</v>
+        <v>276530.74098197947</v>
       </c>
     </row>
     <row r="49" spans="2:83">
@@ -11294,308 +11304,308 @@
         <v>-1.8913978494623451</v>
       </c>
       <c r="D49" s="9">
-        <f t="shared" ref="D49:BW49" si="384">D36/D35</f>
+        <f t="shared" ref="D49:BW49" si="383">D36/D35</f>
         <v>0.36823940491757517</v>
       </c>
       <c r="E49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.3570144066597965</v>
+      </c>
+      <c r="F49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.34569752986325059</v>
+      </c>
+      <c r="G49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.40282649757150618</v>
+      </c>
+      <c r="H49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.39493235183859821</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.39207685288659683</v>
+      </c>
+      <c r="J49" s="9">
+        <f t="shared" si="383"/>
+        <v>-0.83168556112136249</v>
+      </c>
+      <c r="K49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.38333420080154013</v>
+      </c>
+      <c r="L49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.34959249197332665</v>
+      </c>
+      <c r="M49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.30318670391590535</v>
+      </c>
+      <c r="N49" s="9">
+        <f t="shared" si="383"/>
+        <v>-1.0829313006561061</v>
+      </c>
+      <c r="O49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.3</v>
+      </c>
+      <c r="P49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.3</v>
+      </c>
+      <c r="R49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.3</v>
+      </c>
+      <c r="S49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.2026666666666665</v>
+      </c>
+      <c r="T49" s="9">
+        <f t="shared" si="383"/>
+        <v>-3.5783633841885929</v>
+      </c>
+      <c r="U49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.11622662457065554</v>
+      </c>
+      <c r="V49" s="9">
+        <f t="shared" si="383"/>
+        <v>-0.62110848694905363</v>
+      </c>
+      <c r="W49" s="9">
+        <f t="shared" si="383"/>
+        <v>3.1595471537468882E-2</v>
+      </c>
+      <c r="X49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.12984732196904594</v>
+      </c>
+      <c r="Y49" s="9">
+        <f t="shared" si="383"/>
+        <v>-6.3406092881683265E-2</v>
+      </c>
+      <c r="Z49" s="9">
+        <f t="shared" si="383"/>
+        <v>-0.21686416097851588</v>
+      </c>
+      <c r="AA49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.22473726758286156</v>
+      </c>
+      <c r="AB49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.45995606151388052</v>
+      </c>
+      <c r="AC49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.34019406057042051</v>
+      </c>
+      <c r="AD49" s="9">
+        <f t="shared" si="383"/>
+        <v>-1.4517412935323439</v>
+      </c>
+      <c r="AE49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.10901783471489572</v>
+      </c>
+      <c r="AF49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.30458715596330271</v>
+      </c>
+      <c r="AG49" s="9">
+        <f t="shared" si="383"/>
+        <v>8.3352762881790637E-2</v>
+      </c>
+      <c r="AH49" s="9">
+        <f t="shared" si="383"/>
+        <v>-7.0525483998419611E-2</v>
+      </c>
+      <c r="AI49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.16105733798457228</v>
+      </c>
+      <c r="AJ49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.15107597716293369</v>
+      </c>
+      <c r="AK49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.12757375075255875</v>
+      </c>
+      <c r="AL49" s="9">
+        <f t="shared" si="383"/>
+        <v>-0.10275962236746554</v>
+      </c>
+      <c r="AM49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.19305955447795117</v>
+      </c>
+      <c r="AN49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.1122681619323433</v>
+      </c>
+      <c r="AO49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.13786300018496819</v>
+      </c>
+      <c r="AP49" s="9">
+        <f t="shared" si="383"/>
+        <v>-0.40712468193383566</v>
+      </c>
+      <c r="AQ49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.1115120157941317</v>
+      </c>
+      <c r="AR49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.11415470731852555</v>
+      </c>
+      <c r="AS49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.12132006286013612</v>
+      </c>
+      <c r="AT49" s="9">
+        <f t="shared" si="383"/>
+        <v>0.18315624455669755</v>
+      </c>
+      <c r="AU49" s="9">
+        <f t="shared" ref="AU49:AX49" si="384">AU36/AU35</f>
+        <v>0.10800887325021039</v>
+      </c>
+      <c r="AV49" s="9">
         <f t="shared" si="384"/>
-        <v>0.3570144066597965</v>
-      </c>
-      <c r="F49" s="9">
+        <v>0.14583499085050527</v>
+      </c>
+      <c r="AW49" s="9">
         <f t="shared" si="384"/>
-        <v>0.34569752986325059</v>
-      </c>
-      <c r="G49" s="9">
+        <v>0.12556883347515627</v>
+      </c>
+      <c r="AX49" s="9">
         <f t="shared" si="384"/>
-        <v>0.40282649757150618</v>
-      </c>
-      <c r="H49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.39493235183859821</v>
-      </c>
-      <c r="I49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.39207685288659683</v>
-      </c>
-      <c r="J49" s="9">
-        <f t="shared" si="384"/>
-        <v>-0.83168556112136249</v>
-      </c>
-      <c r="K49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.38333420080154013</v>
-      </c>
-      <c r="L49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.34959249197332665</v>
-      </c>
-      <c r="M49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.30318670391590535</v>
-      </c>
-      <c r="N49" s="9">
-        <f t="shared" si="384"/>
-        <v>-1.0829313006561061</v>
-      </c>
-      <c r="O49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.3</v>
-      </c>
-      <c r="P49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.3</v>
-      </c>
-      <c r="Q49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.3</v>
-      </c>
-      <c r="R49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.3</v>
-      </c>
-      <c r="S49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.2026666666666665</v>
-      </c>
-      <c r="T49" s="9">
-        <f t="shared" si="384"/>
-        <v>-3.5783633841885929</v>
-      </c>
-      <c r="U49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.11622662457065554</v>
-      </c>
-      <c r="V49" s="9">
-        <f t="shared" si="384"/>
-        <v>-0.62110848694905363</v>
-      </c>
-      <c r="W49" s="9">
-        <f t="shared" si="384"/>
-        <v>3.1595471537468882E-2</v>
-      </c>
-      <c r="X49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.12984732196904594</v>
-      </c>
-      <c r="Y49" s="9">
-        <f t="shared" si="384"/>
-        <v>-6.3406092881683265E-2</v>
-      </c>
-      <c r="Z49" s="9">
-        <f t="shared" si="384"/>
-        <v>-0.21686416097851588</v>
-      </c>
-      <c r="AA49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.22473726758286156</v>
-      </c>
-      <c r="AB49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.45995606151388052</v>
-      </c>
-      <c r="AC49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.34019406057042051</v>
-      </c>
-      <c r="AD49" s="9">
-        <f t="shared" si="384"/>
-        <v>-1.4517412935323439</v>
-      </c>
-      <c r="AE49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.10901783471489572</v>
-      </c>
-      <c r="AF49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.30458715596330271</v>
-      </c>
-      <c r="AG49" s="9">
-        <f t="shared" si="384"/>
-        <v>8.3352762881790637E-2</v>
-      </c>
-      <c r="AH49" s="9">
-        <f t="shared" si="384"/>
-        <v>-7.0525483998419611E-2</v>
-      </c>
-      <c r="AI49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.16105733798457228</v>
-      </c>
-      <c r="AJ49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.15107597716293369</v>
-      </c>
-      <c r="AK49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.12757375075255875</v>
-      </c>
-      <c r="AL49" s="9">
-        <f t="shared" si="384"/>
-        <v>-0.10275962236746554</v>
-      </c>
-      <c r="AM49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.19305955447795117</v>
-      </c>
-      <c r="AN49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.1122681619323433</v>
-      </c>
-      <c r="AO49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.13786300018496819</v>
-      </c>
-      <c r="AP49" s="9">
-        <f t="shared" si="384"/>
-        <v>-0.40712468193383566</v>
-      </c>
-      <c r="AQ49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.1115120157941317</v>
-      </c>
-      <c r="AR49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.11415470731852555</v>
-      </c>
-      <c r="AS49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.12132006286013612</v>
-      </c>
-      <c r="AT49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.18315624455669755</v>
-      </c>
-      <c r="AU49" s="9">
-        <f t="shared" ref="AU49:AX49" si="385">AU36/AU35</f>
-        <v>0.10800887325021039</v>
-      </c>
-      <c r="AV49" s="9">
+        <v>0.12449629837878357</v>
+      </c>
+      <c r="AY49" s="9">
+        <f t="shared" ref="AY49:BB49" si="385">AY36/AY35</f>
+        <v>0.10063167065998695</v>
+      </c>
+      <c r="AZ49" s="9">
         <f t="shared" si="385"/>
-        <v>0.14583499085050527</v>
-      </c>
-      <c r="AW49" s="9">
+        <v>0.13941129498581928</v>
+      </c>
+      <c r="BA49" s="9">
         <f t="shared" si="385"/>
-        <v>0.12556883347515627</v>
-      </c>
-      <c r="AX49" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="BB49" s="9">
         <f t="shared" si="385"/>
-        <v>0.12449629837878357</v>
-      </c>
-      <c r="AY49" s="9">
-        <f t="shared" ref="AY49:BB49" si="386">AY36/AY35</f>
-        <v>0.10063167065998695</v>
-      </c>
-      <c r="AZ49" s="9">
-        <f t="shared" si="386"/>
-        <v>0.12</v>
-      </c>
-      <c r="BA49" s="9">
-        <f t="shared" si="386"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="BB49" s="9">
-        <f t="shared" si="386"/>
         <v>0.12</v>
       </c>
       <c r="BC49" s="9"/>
       <c r="BD49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.37103709925957218</v>
       </c>
       <c r="BE49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.43727034120734615</v>
       </c>
       <c r="BF49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.34295684908285323</v>
       </c>
       <c r="BG49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.23634037364505703</v>
       </c>
       <c r="BH49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.13563383656841535</v>
       </c>
       <c r="BI49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.36781576933181465</v>
       </c>
       <c r="BJ49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>-0.1517137886396058</v>
       </c>
       <c r="BK49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>1.2389823090606799E-2</v>
       </c>
       <c r="BL49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>9.4810427690664612E-2</v>
       </c>
       <c r="BM49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.1370591732640736</v>
       </c>
       <c r="BN49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.12393425783256297</v>
       </c>
       <c r="BO49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.14666210722291886</v>
       </c>
       <c r="BP49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.12850098301479357</v>
       </c>
       <c r="BQ49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.12584416236014256</v>
       </c>
       <c r="BR49" s="9">
-        <f t="shared" si="384"/>
-        <v>0.1148205684400508</v>
+        <f t="shared" si="383"/>
+        <v>0.12063287088877692</v>
       </c>
       <c r="BS49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.13</v>
       </c>
       <c r="BT49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.13</v>
       </c>
       <c r="BU49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.13</v>
       </c>
       <c r="BV49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.13</v>
       </c>
       <c r="BW49" s="9">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v>0.13</v>
       </c>
       <c r="BX49" s="9">
-        <f t="shared" ref="BX49:CB49" si="387">BX36/BX35</f>
+        <f t="shared" ref="BX49:CB49" si="386">BX36/BX35</f>
         <v>0.13</v>
       </c>
       <c r="BY49" s="9">
-        <f t="shared" si="387"/>
+        <f t="shared" si="386"/>
         <v>0.13</v>
       </c>
       <c r="BZ49" s="9">
-        <f t="shared" si="387"/>
+        <f t="shared" si="386"/>
         <v>0.13</v>
       </c>
       <c r="CA49" s="9">
-        <f t="shared" si="387"/>
+        <f t="shared" si="386"/>
         <v>0.13</v>
       </c>
       <c r="CB49" s="9">
-        <f t="shared" si="387"/>
+        <f t="shared" si="386"/>
         <v>0.13</v>
       </c>
       <c r="CD49" t="s">
@@ -11603,7 +11613,7 @@
       </c>
       <c r="CE49" s="2">
         <f>Main!D8</f>
-        <v>-6646</v>
+        <v>-7851.1</v>
       </c>
     </row>
     <row r="50" spans="2:83" s="1" customFormat="1">
@@ -11615,315 +11625,315 @@
         <v>2.6260765790884709E-3</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" ref="D50:BW50" si="388">D37/D26</f>
+        <f t="shared" ref="D50:BW50" si="387">D37/D26</f>
         <v>2.7559165566332481E-2</v>
       </c>
       <c r="E50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.8772177913361615E-2</v>
+      </c>
+      <c r="F50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.1201296767441269E-2</v>
+      </c>
+      <c r="G50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.1819903959486218E-2</v>
+      </c>
+      <c r="H50" s="10">
+        <f t="shared" si="387"/>
+        <v>5.2982415042595363E-2</v>
+      </c>
+      <c r="I50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.2070138892830594E-2</v>
+      </c>
+      <c r="J50" s="10">
+        <f t="shared" si="387"/>
+        <v>5.6152372690486112E-2</v>
+      </c>
+      <c r="K50" s="10">
+        <f t="shared" si="387"/>
+        <v>1.5062973220886558E-2</v>
+      </c>
+      <c r="L50" s="10">
+        <f t="shared" si="387"/>
+        <v>1.6012097083104825E-2</v>
+      </c>
+      <c r="M50" s="10">
+        <f t="shared" si="387"/>
+        <v>1.6930949086924114E-2</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.3679163378274956E-2</v>
+      </c>
+      <c r="O50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.1416519128911782E-2</v>
+      </c>
+      <c r="P50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.1542444508284551E-2</v>
+      </c>
+      <c r="Q50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.1831975376053397E-2</v>
+      </c>
+      <c r="R50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.2697748783246163E-2</v>
+      </c>
+      <c r="S50" s="10">
+        <f t="shared" si="387"/>
+        <v>6.8011221472439223E-2</v>
+      </c>
+      <c r="T50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.3697737192740688E-2</v>
+      </c>
+      <c r="U50" s="10">
+        <f t="shared" si="387"/>
+        <v>3.4147348496527299E-2</v>
+      </c>
+      <c r="V50" s="10">
+        <f t="shared" si="387"/>
+        <v>6.4358497274812854E-2</v>
+      </c>
+      <c r="W50" s="10">
+        <f t="shared" si="387"/>
+        <v>7.865633532835789E-2</v>
+      </c>
+      <c r="X50" s="10">
+        <f t="shared" si="387"/>
+        <v>9.5344214962571117E-2</v>
+      </c>
+      <c r="Y50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.10065297820072844</v>
+      </c>
+      <c r="Z50" s="10">
+        <f t="shared" si="387"/>
+        <v>3.4718596318485888E-2</v>
+      </c>
+      <c r="AA50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.2424242424242475E-2</v>
+      </c>
+      <c r="AB50" s="10">
+        <f t="shared" si="387"/>
+        <v>5.4925858216534638E-2</v>
+      </c>
+      <c r="AC50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.12815533980582522</v>
+      </c>
+      <c r="AD50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.13521126760563359</v>
+      </c>
+      <c r="AE50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.12298890429958396</v>
+      </c>
+      <c r="AF50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.11712752114508784</v>
+      </c>
+      <c r="AG50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.1222481343283582</v>
+      </c>
+      <c r="AH50" s="10">
+        <f t="shared" si="387"/>
+        <v>8.1562311860325101E-2</v>
+      </c>
+      <c r="AI50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.23834450027917367</v>
+      </c>
+      <c r="AJ50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.18430085265193824</v>
+      </c>
+      <c r="AK50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.1936393398810716</v>
+      </c>
+      <c r="AL50" s="10">
+        <f t="shared" si="387"/>
+        <v>7.8787957402098749E-2</v>
+      </c>
+      <c r="AM50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.2030427819720888</v>
+      </c>
+      <c r="AN50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.18076310209407664</v>
+      </c>
+      <c r="AO50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.17642828303219954</v>
+      </c>
+      <c r="AP50" s="10">
+        <f t="shared" si="387"/>
+        <v>7.0427019523440397E-3</v>
+      </c>
+      <c r="AQ50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.15990933039269739</v>
+      </c>
+      <c r="AR50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.18169604143001972</v>
+      </c>
+      <c r="AS50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.19637777023309191</v>
+      </c>
+      <c r="AT50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.10618376958608816</v>
+      </c>
+      <c r="AU50" s="10">
+        <f t="shared" ref="AU50:AX50" si="388">AU37/AU26</f>
+        <v>0.24889012208657038</v>
+      </c>
+      <c r="AV50" s="10">
         <f t="shared" si="388"/>
-        <v>2.8772177913361615E-2</v>
-      </c>
-      <c r="F50" s="10">
+        <v>0.22461895745504373</v>
+      </c>
+      <c r="AW50" s="10">
         <f t="shared" si="388"/>
-        <v>4.1201296767441269E-2</v>
-      </c>
-      <c r="G50" s="10">
+        <v>0.24056714199924686</v>
+      </c>
+      <c r="AX50" s="10">
         <f t="shared" si="388"/>
-        <v>4.1819903959486218E-2</v>
-      </c>
-      <c r="H50" s="10">
-        <f t="shared" si="388"/>
-        <v>5.2982415042595363E-2</v>
-      </c>
-      <c r="I50" s="10">
-        <f t="shared" si="388"/>
-        <v>4.2070138892830594E-2</v>
-      </c>
-      <c r="J50" s="10">
-        <f t="shared" si="388"/>
-        <v>5.6152372690486112E-2</v>
-      </c>
-      <c r="K50" s="10">
-        <f t="shared" si="388"/>
-        <v>1.5062973220886558E-2</v>
-      </c>
-      <c r="L50" s="10">
-        <f t="shared" si="388"/>
-        <v>1.6012097083104825E-2</v>
-      </c>
-      <c r="M50" s="10">
-        <f t="shared" si="388"/>
-        <v>1.6930949086924114E-2</v>
-      </c>
-      <c r="N50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.3679163378274956E-2</v>
-      </c>
-      <c r="O50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.1416519128911782E-2</v>
-      </c>
-      <c r="P50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.1542444508284551E-2</v>
-      </c>
-      <c r="Q50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.1831975376053397E-2</v>
-      </c>
-      <c r="R50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.2697748783246163E-2</v>
-      </c>
-      <c r="S50" s="10">
-        <f t="shared" si="388"/>
-        <v>6.8011221472439223E-2</v>
-      </c>
-      <c r="T50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.3697737192740688E-2</v>
-      </c>
-      <c r="U50" s="10">
-        <f t="shared" si="388"/>
-        <v>3.4147348496527299E-2</v>
-      </c>
-      <c r="V50" s="10">
-        <f t="shared" si="388"/>
-        <v>6.4358497274812854E-2</v>
-      </c>
-      <c r="W50" s="10">
-        <f t="shared" si="388"/>
-        <v>7.865633532835789E-2</v>
-      </c>
-      <c r="X50" s="10">
-        <f t="shared" si="388"/>
-        <v>9.5344214962571117E-2</v>
-      </c>
-      <c r="Y50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.10065297820072844</v>
-      </c>
-      <c r="Z50" s="10">
-        <f t="shared" si="388"/>
-        <v>3.4718596318485888E-2</v>
-      </c>
-      <c r="AA50" s="10">
-        <f t="shared" si="388"/>
-        <v>4.2424242424242475E-2</v>
-      </c>
-      <c r="AB50" s="10">
-        <f t="shared" si="388"/>
-        <v>5.4925858216534638E-2</v>
-      </c>
-      <c r="AC50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.12815533980582522</v>
-      </c>
-      <c r="AD50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.13521126760563359</v>
-      </c>
-      <c r="AE50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.12298890429958396</v>
-      </c>
-      <c r="AF50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.11712752114508784</v>
-      </c>
-      <c r="AG50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.1222481343283582</v>
-      </c>
-      <c r="AH50" s="10">
-        <f t="shared" si="388"/>
-        <v>8.1562311860325101E-2</v>
-      </c>
-      <c r="AI50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.23834450027917367</v>
-      </c>
-      <c r="AJ50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.18430085265193824</v>
-      </c>
-      <c r="AK50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.1936393398810716</v>
-      </c>
-      <c r="AL50" s="10">
-        <f t="shared" si="388"/>
-        <v>7.8787957402098749E-2</v>
-      </c>
-      <c r="AM50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.2030427819720888</v>
-      </c>
-      <c r="AN50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.18076310209407664</v>
-      </c>
-      <c r="AO50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.17642828303219954</v>
-      </c>
-      <c r="AP50" s="10">
-        <f t="shared" si="388"/>
-        <v>7.0427019523440397E-3</v>
-      </c>
-      <c r="AQ50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.15990933039269739</v>
-      </c>
-      <c r="AR50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.18169604143001972</v>
-      </c>
-      <c r="AS50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.19637777023309191</v>
-      </c>
-      <c r="AT50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.10618376958608816</v>
-      </c>
-      <c r="AU50" s="10">
-        <f t="shared" ref="AU50:AX50" si="389">AU37/AU26</f>
-        <v>0.24889012208657038</v>
-      </c>
-      <c r="AV50" s="10">
+        <v>0.18235495047089256</v>
+      </c>
+      <c r="AY50" s="10">
+        <f t="shared" ref="AY50:BB50" si="389">AY37/AY26</f>
+        <v>0.27414918238039226</v>
+      </c>
+      <c r="AZ50" s="10">
         <f t="shared" si="389"/>
-        <v>0.22461895745504373</v>
-      </c>
-      <c r="AW50" s="10">
+        <v>0.28209618022961952</v>
+      </c>
+      <c r="BA50" s="10">
         <f t="shared" si="389"/>
-        <v>0.24056714199924686</v>
-      </c>
-      <c r="AX50" s="10">
+        <v>0.27041952860187762</v>
+      </c>
+      <c r="BB50" s="10">
         <f t="shared" si="389"/>
-        <v>0.18235495047089256</v>
-      </c>
-      <c r="AY50" s="10">
-        <f t="shared" ref="AY50:BB50" si="390">AY37/AY26</f>
-        <v>0.27414918238039226</v>
-      </c>
-      <c r="AZ50" s="10">
+        <v>0.2133297753239782</v>
+      </c>
+      <c r="BD50" s="10">
+        <f t="shared" si="387"/>
+        <v>7.056344721939907E-2</v>
+      </c>
+      <c r="BE50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.7521917101518256E-3</v>
+      </c>
+      <c r="BF50" s="10">
+        <f t="shared" si="387"/>
+        <v>2.569468669091898E-2</v>
+      </c>
+      <c r="BG50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.8467878828395504E-2</v>
+      </c>
+      <c r="BH50" s="10">
+        <f t="shared" si="387"/>
+        <v>1.8089505275528082E-2</v>
+      </c>
+      <c r="BI50" s="10">
+        <f t="shared" si="387"/>
+        <v>1.6129505907978094E-2</v>
+      </c>
+      <c r="BJ50" s="10">
+        <f t="shared" si="387"/>
+        <v>4.7784721245814774E-2</v>
+      </c>
+      <c r="BK50" s="10">
+        <f t="shared" si="387"/>
+        <v>7.6710054526016591E-2</v>
+      </c>
+      <c r="BL50" s="10">
+        <f t="shared" si="387"/>
+        <v>9.2517614369355919E-2</v>
+      </c>
+      <c r="BM50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.11034330985915493</v>
+      </c>
+      <c r="BN50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.17230105122800393</v>
+      </c>
+      <c r="BO50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.14207543111628429</v>
+      </c>
+      <c r="BP50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.16036390270228595</v>
+      </c>
+      <c r="BQ50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.22336407621362567</v>
+      </c>
+      <c r="BR50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.25941324529228976</v>
+      </c>
+      <c r="BS50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.28317573096514848</v>
+      </c>
+      <c r="BT50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.29485726796504369</v>
+      </c>
+      <c r="BU50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.30606996100435202</v>
+      </c>
+      <c r="BV50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.31684898902040992</v>
+      </c>
+      <c r="BW50" s="10">
+        <f t="shared" si="387"/>
+        <v>0.31880531933069328</v>
+      </c>
+      <c r="BX50" s="10">
+        <f t="shared" ref="BX50:CB50" si="390">BX37/BX26</f>
+        <v>0.31977389463137285</v>
+      </c>
+      <c r="BY50" s="10">
         <f t="shared" si="390"/>
-        <v>0.25483538781695531</v>
-      </c>
-      <c r="BA50" s="10">
+        <v>0.32073297409577106</v>
+      </c>
+      <c r="BZ50" s="10">
         <f t="shared" si="390"/>
-        <v>0.24635025526686344</v>
-      </c>
-      <c r="BB50" s="10">
+        <v>0.32168265082032232</v>
+      </c>
+      <c r="CA50" s="10">
         <f t="shared" si="390"/>
-        <v>0.20132052380518342</v>
-      </c>
-      <c r="BD50" s="10">
-        <f t="shared" si="388"/>
-        <v>7.056344721939907E-2</v>
-      </c>
-      <c r="BE50" s="10">
-        <f t="shared" si="388"/>
-        <v>4.7521917101518256E-3</v>
-      </c>
-      <c r="BF50" s="10">
-        <f t="shared" si="388"/>
-        <v>2.569468669091898E-2</v>
-      </c>
-      <c r="BG50" s="10">
-        <f t="shared" si="388"/>
-        <v>4.8467878828395504E-2</v>
-      </c>
-      <c r="BH50" s="10">
-        <f t="shared" si="388"/>
-        <v>1.8089505275528082E-2</v>
-      </c>
-      <c r="BI50" s="10">
-        <f t="shared" si="388"/>
-        <v>1.6129505907978094E-2</v>
-      </c>
-      <c r="BJ50" s="10">
-        <f t="shared" si="388"/>
-        <v>4.7784721245814774E-2</v>
-      </c>
-      <c r="BK50" s="10">
-        <f t="shared" si="388"/>
-        <v>7.6710054526016591E-2</v>
-      </c>
-      <c r="BL50" s="10">
-        <f t="shared" si="388"/>
-        <v>9.2517614369355919E-2</v>
-      </c>
-      <c r="BM50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.11034330985915493</v>
-      </c>
-      <c r="BN50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.17230105122800393</v>
-      </c>
-      <c r="BO50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.14207543111628429</v>
-      </c>
-      <c r="BP50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.16036390270228595</v>
-      </c>
-      <c r="BQ50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.22336407621362567</v>
-      </c>
-      <c r="BR50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.24401253074536036</v>
-      </c>
-      <c r="BS50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.26720057499074029</v>
-      </c>
-      <c r="BT50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.28715871418223199</v>
-      </c>
-      <c r="BU50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.29728548053941767</v>
-      </c>
-      <c r="BV50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.30699444641648216</v>
-      </c>
-      <c r="BW50" s="10">
-        <f t="shared" si="388"/>
-        <v>0.30699444641648221</v>
-      </c>
-      <c r="BX50" s="10">
-        <f t="shared" ref="BX50:CB50" si="391">BX37/BX26</f>
-        <v>0.30699444641648221</v>
-      </c>
-      <c r="BY50" s="10">
-        <f t="shared" si="391"/>
-        <v>0.30699444641648233</v>
-      </c>
-      <c r="BZ50" s="10">
-        <f t="shared" si="391"/>
-        <v>0.30699444641648221</v>
-      </c>
-      <c r="CA50" s="10">
-        <f t="shared" si="391"/>
-        <v>0.30699444641648227</v>
+        <v>0.32262301698875051</v>
       </c>
       <c r="CB50" s="10">
-        <f t="shared" si="391"/>
-        <v>0.30699444641648216</v>
+        <f t="shared" si="390"/>
+        <v>0.32355416388101771</v>
       </c>
       <c r="CD50" t="s">
         <v>87</v>
       </c>
       <c r="CE50" s="2">
         <f>CE48+CE49</f>
-        <v>230508.54970478042</v>
+        <v>268679.64098197949</v>
       </c>
     </row>
     <row r="51" spans="2:83">
@@ -11932,7 +11942,7 @@
       </c>
       <c r="CE51" s="17">
         <f>CE50/BW38</f>
-        <v>541.48120672957577</v>
+        <v>631.89003053146632</v>
       </c>
     </row>
     <row r="52" spans="2:83" s="1" customFormat="1">
@@ -11944,19 +11954,19 @@
         <v>397.81099999999992</v>
       </c>
       <c r="BE52" s="7">
-        <f t="shared" ref="BE52:BH52" si="392">BE54-BE67</f>
+        <f t="shared" ref="BE52:BH52" si="391">BE54-BE67</f>
         <v>348.07799999999997</v>
       </c>
       <c r="BF52" s="7">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>700.40499999999997</v>
       </c>
       <c r="BG52" s="7">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>722.75099999999986</v>
       </c>
       <c r="BH52" s="7">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>-60.690000000000055</v>
       </c>
       <c r="CD52" t="s">
@@ -11964,7 +11974,7 @@
       </c>
       <c r="CE52" s="17">
         <f>Main!D3</f>
-        <v>1194.18</v>
+        <v>1230.08</v>
       </c>
     </row>
     <row r="53" spans="2:83">
@@ -11973,7 +11983,7 @@
       </c>
       <c r="CE53" s="10">
         <f>CE51/CE52-1</f>
-        <v>-0.5465665086255207</v>
+        <v>-0.48630167913349831</v>
       </c>
     </row>
     <row r="54" spans="2:83">
@@ -12014,7 +12024,7 @@
         <v>91</v>
       </c>
       <c r="CE54" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="2:83">
@@ -12551,27 +12561,27 @@
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
       <c r="G74" s="7">
-        <f t="shared" ref="G74:L74" si="393">G37</f>
+        <f t="shared" ref="G74:L74" si="392">G37</f>
         <v>53.114999999999888</v>
       </c>
       <c r="H74" s="7">
-        <f t="shared" si="393"/>
+        <f t="shared" si="392"/>
         <v>71.018000000000129</v>
       </c>
       <c r="I74" s="7">
-        <f t="shared" si="393"/>
+        <f t="shared" si="392"/>
         <v>59.295000000000009</v>
       </c>
       <c r="J74" s="16">
-        <f t="shared" si="393"/>
+        <f t="shared" si="392"/>
         <v>83.371000000000066</v>
       </c>
       <c r="K74" s="16">
-        <f t="shared" si="393"/>
+        <f t="shared" si="392"/>
         <v>23.696000000000051</v>
       </c>
       <c r="L74" s="16">
-        <f t="shared" si="393"/>
+        <f t="shared" si="392"/>
         <v>26.335000000000008</v>
       </c>
       <c r="M74" s="16">

--- a/Financial Analysis/NFLX.xlsx
+++ b/Financial Analysis/NFLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC87849C-6BE5-4A09-9270-ACBC788B334B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E43167-0901-42CE-BC2C-24B02051E76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="639" xr2:uid="{0F574E5A-2072-44A4-9588-9F3B274273C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="639" activeTab="1" xr2:uid="{0F574E5A-2072-44A4-9588-9F3B274273C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -665,13 +665,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>52</xdr:col>
+      <xdr:col>53</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>52</xdr:col>
+      <xdr:col>53</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -689,7 +689,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="32948880" y="0"/>
+          <a:off x="33558480" y="0"/>
           <a:ext cx="0" cy="10896600"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1088,17 +1088,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="17">
-        <v>1230.08</v>
+        <v>1094.69</v>
       </c>
       <c r="E3" s="4">
-        <v>45887</v>
+        <v>45956</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45956</v>
       </c>
       <c r="G3" s="4">
-        <v>45945</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -1106,8 +1106,8 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>425.2</f>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>139</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>523030.01599999995</v>
+        <v>463820.15299999999</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>530881.11599999992</v>
+        <v>471671.25299999997</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -5153,8 +5153,7 @@
         <v>11079.2</v>
       </c>
       <c r="BA26" s="16">
-        <f>AW26*1.13</f>
-        <v>11101.911</v>
+        <v>11510.3</v>
       </c>
       <c r="BB26" s="16">
         <f>AX26*1.12</f>
@@ -5216,47 +5215,47 @@
       </c>
       <c r="BR26" s="16">
         <f>SUM(AY26:BB26)</f>
-        <v>44199.991000000002</v>
+        <v>44608.380000000005</v>
       </c>
       <c r="BS26" s="16">
         <f>BR26*1.09</f>
-        <v>48177.990190000004</v>
+        <v>48623.134200000008</v>
       </c>
       <c r="BT26" s="16">
         <f>BS26*1.06</f>
-        <v>51068.669601400004</v>
+        <v>51540.52225200001</v>
       </c>
       <c r="BU26" s="16">
         <f>BT26*1.05</f>
-        <v>53622.103081470006</v>
+        <v>54117.548364600014</v>
       </c>
       <c r="BV26" s="16">
         <f>BU26*1.04</f>
-        <v>55766.987204728808</v>
+        <v>56282.250299184016</v>
       </c>
       <c r="BW26" s="16">
         <f>BV26*1.03</f>
-        <v>57439.99682087067</v>
+        <v>57970.717808159541</v>
       </c>
       <c r="BX26" s="16">
         <f t="shared" ref="BX26:CB26" si="118">BW26*1.02</f>
-        <v>58588.796757288088</v>
+        <v>59130.132164322735</v>
       </c>
       <c r="BY26" s="16">
         <f t="shared" si="118"/>
-        <v>59760.572692433852</v>
+        <v>60312.734807609188</v>
       </c>
       <c r="BZ26" s="16">
         <f t="shared" si="118"/>
-        <v>60955.784146282531</v>
+        <v>61518.989503761375</v>
       </c>
       <c r="CA26" s="16">
         <f t="shared" si="118"/>
-        <v>62174.899829208181</v>
+        <v>62749.3692938366</v>
       </c>
       <c r="CB26" s="16">
         <f t="shared" si="118"/>
-        <v>63418.397825792345</v>
+        <v>64004.356679713332</v>
       </c>
     </row>
     <row r="27" spans="2:80">
@@ -5421,12 +5420,11 @@
         <v>5325.3</v>
       </c>
       <c r="BA27" s="2">
-        <f t="shared" ref="BA27:BB27" si="120">BA26-BA28</f>
-        <v>5439.9363899999998</v>
+        <v>6164.3</v>
       </c>
       <c r="BB27" s="2">
-        <f t="shared" si="120"/>
-        <v>6082.3224000000009</v>
+        <f t="shared" ref="BA27:BB27" si="120">BB26-BB28</f>
+        <v>6311.844000000001</v>
       </c>
       <c r="BD27" s="2">
         <v>2039.9010000000001</v>
@@ -5484,47 +5482,47 @@
       </c>
       <c r="BR27" s="2">
         <f>SUM(AY27:BB27)</f>
-        <v>22110.658790000001</v>
+        <v>23064.544000000002</v>
       </c>
       <c r="BS27" s="2">
         <f t="shared" ref="BS27:BW27" si="124">BS26-BS28</f>
-        <v>23125.435291199999</v>
+        <v>24311.567100000004</v>
       </c>
       <c r="BT27" s="2">
         <f t="shared" si="124"/>
-        <v>24002.274712658</v>
+        <v>25254.855903480006</v>
       </c>
       <c r="BU27" s="2">
         <f t="shared" si="124"/>
-        <v>24666.167417476201</v>
+        <v>25976.423215008006</v>
       </c>
       <c r="BV27" s="2">
         <f t="shared" si="124"/>
-        <v>25095.144242127961</v>
+        <v>26452.657640616486</v>
       </c>
       <c r="BW27" s="2">
         <f t="shared" si="124"/>
-        <v>25847.998569391799</v>
+        <v>26666.530191753387</v>
       </c>
       <c r="BX27" s="2">
         <f t="shared" ref="BX27:CB27" si="125">BX26-BX28</f>
-        <v>26364.958540779637</v>
+        <v>26608.559473945228</v>
       </c>
       <c r="BY27" s="2">
         <f t="shared" si="125"/>
-        <v>26892.25771159523</v>
+        <v>27140.730663424132</v>
       </c>
       <c r="BZ27" s="2">
         <f t="shared" si="125"/>
-        <v>27430.102865827139</v>
+        <v>27683.545276692617</v>
       </c>
       <c r="CA27" s="2">
         <f t="shared" si="125"/>
-        <v>27978.704923143676</v>
+        <v>28237.216182226468</v>
       </c>
       <c r="CB27" s="2">
         <f t="shared" si="125"/>
-        <v>28538.279021606555</v>
+        <v>28801.960505870993</v>
       </c>
     </row>
     <row r="28" spans="2:80" s="1" customFormat="1">
@@ -5704,7 +5702,7 @@
         <v>3610.9000000000005</v>
       </c>
       <c r="AT28" s="16">
-        <f t="shared" ref="AT28:AZ28" si="135">AT26-AT27</f>
+        <f t="shared" ref="AT28:BA28" si="135">AT26-AT27</f>
         <v>3525.2999999999993</v>
       </c>
       <c r="AU28" s="16">
@@ -5732,12 +5730,12 @@
         <v>5753.9000000000005</v>
       </c>
       <c r="BA28" s="16">
-        <f>BA26*0.51</f>
-        <v>5661.9746100000002</v>
+        <f t="shared" si="135"/>
+        <v>5345.9999999999991</v>
       </c>
       <c r="BB28" s="16">
-        <f>BB26*0.47</f>
-        <v>5393.7576000000008</v>
+        <f>BB26*0.45</f>
+        <v>5164.2360000000008</v>
       </c>
       <c r="BD28" s="16">
         <f>BD26-BD27</f>
@@ -5797,47 +5795,47 @@
       </c>
       <c r="BR28" s="16">
         <f t="shared" si="136"/>
-        <v>22089.33221</v>
+        <v>21543.836000000003</v>
       </c>
       <c r="BS28" s="16">
-        <f>BS26*0.52</f>
-        <v>25052.554898800005</v>
+        <f>BS26*0.5</f>
+        <v>24311.567100000004</v>
       </c>
       <c r="BT28" s="16">
-        <f>BT26*0.53</f>
-        <v>27066.394888742005</v>
+        <f>BT26*0.51</f>
+        <v>26285.666348520004</v>
       </c>
       <c r="BU28" s="16">
-        <f>BU26*0.54</f>
-        <v>28955.935663993805</v>
+        <f>BU26*0.52</f>
+        <v>28141.125149592008</v>
       </c>
       <c r="BV28" s="16">
-        <f>BV26*0.55</f>
-        <v>30671.842962600847</v>
+        <f>BV26*0.53</f>
+        <v>29829.59265856753</v>
       </c>
       <c r="BW28" s="16">
-        <f t="shared" ref="BW28:CB28" si="137">BW26*0.55</f>
-        <v>31591.998251478872</v>
+        <f>BW26*0.54</f>
+        <v>31304.187616406154</v>
       </c>
       <c r="BX28" s="16">
-        <f t="shared" si="137"/>
-        <v>32223.838216508451</v>
+        <f t="shared" ref="BW28:CB28" si="137">BX26*0.55</f>
+        <v>32521.572690377507</v>
       </c>
       <c r="BY28" s="16">
         <f t="shared" si="137"/>
-        <v>32868.314980838622</v>
+        <v>33172.004144185055</v>
       </c>
       <c r="BZ28" s="16">
         <f t="shared" si="137"/>
-        <v>33525.681280455392</v>
+        <v>33835.444227068758</v>
       </c>
       <c r="CA28" s="16">
         <f t="shared" si="137"/>
-        <v>34196.194906064506</v>
+        <v>34512.153111610132</v>
       </c>
       <c r="CB28" s="16">
         <f t="shared" si="137"/>
-        <v>34880.118804185789</v>
+        <v>35202.396173842339</v>
       </c>
     </row>
     <row r="29" spans="2:80">
@@ -6002,8 +6000,7 @@
         <v>713.3</v>
       </c>
       <c r="BA29" s="2">
-        <f t="shared" ref="BA29" si="139">BA26*0.07</f>
-        <v>777.13377000000003</v>
+        <v>786.3</v>
       </c>
       <c r="BB29" s="2">
         <f>BB26*0.1</f>
@@ -6032,15 +6029,15 @@
         <v>957.08879999999988</v>
       </c>
       <c r="BJ29" s="15">
-        <f t="shared" ref="BJ29:BJ31" si="140">SUM(S29:V29)</f>
+        <f t="shared" ref="BJ29:BJ31" si="139">SUM(S29:V29)</f>
         <v>1436.3000000000002</v>
       </c>
       <c r="BK29" s="15">
-        <f t="shared" ref="BK29:BK31" si="141">SUM(W29:Z29)</f>
+        <f t="shared" ref="BK29:BK31" si="140">SUM(W29:Z29)</f>
         <v>2369.5</v>
       </c>
       <c r="BL29" s="15">
-        <f t="shared" ref="BL29:BL31" si="142">SUM(AA29:AD29)</f>
+        <f t="shared" ref="BL29:BL31" si="141">SUM(AA29:AD29)</f>
         <v>2652.5</v>
       </c>
       <c r="BM29" s="15">
@@ -6065,47 +6062,47 @@
       </c>
       <c r="BR29" s="2">
         <f>SUM(AY29:BB29)</f>
-        <v>3326.4417699999999</v>
+        <v>3335.6080000000002</v>
       </c>
       <c r="BS29" s="2">
-        <f t="shared" ref="BS29:CB29" si="143">BS26*0.07</f>
-        <v>3372.4593133000008</v>
+        <f t="shared" ref="BS29:CB29" si="142">BS26*0.07</f>
+        <v>3403.6193940000007</v>
       </c>
       <c r="BT29" s="2">
-        <f t="shared" si="143"/>
-        <v>3574.8068720980004</v>
+        <f t="shared" si="142"/>
+        <v>3607.836557640001</v>
       </c>
       <c r="BU29" s="2">
-        <f t="shared" si="143"/>
-        <v>3753.5472157029008</v>
+        <f t="shared" si="142"/>
+        <v>3788.2283855220012</v>
       </c>
       <c r="BV29" s="2">
-        <f t="shared" si="143"/>
-        <v>3903.689104331017</v>
+        <f t="shared" si="142"/>
+        <v>3939.7575209428815</v>
       </c>
       <c r="BW29" s="2">
-        <f t="shared" si="143"/>
-        <v>4020.7997774609471</v>
+        <f t="shared" si="142"/>
+        <v>4057.9502465711685</v>
       </c>
       <c r="BX29" s="2">
-        <f t="shared" si="143"/>
-        <v>4101.2157730101662</v>
+        <f t="shared" si="142"/>
+        <v>4139.1092515025921</v>
       </c>
       <c r="BY29" s="2">
-        <f t="shared" si="143"/>
-        <v>4183.2400884703702</v>
+        <f t="shared" si="142"/>
+        <v>4221.8914365326436</v>
       </c>
       <c r="BZ29" s="2">
-        <f t="shared" si="143"/>
-        <v>4266.9048902397772</v>
+        <f t="shared" si="142"/>
+        <v>4306.3292652632963</v>
       </c>
       <c r="CA29" s="2">
-        <f t="shared" si="143"/>
-        <v>4352.2429880445734</v>
+        <f t="shared" si="142"/>
+        <v>4392.4558505685627</v>
       </c>
       <c r="CB29" s="2">
-        <f t="shared" si="143"/>
-        <v>4439.2878478054645</v>
+        <f t="shared" si="142"/>
+        <v>4480.3049675799339</v>
       </c>
     </row>
     <row r="30" spans="2:80">
@@ -6153,15 +6150,15 @@
         <v>189.55600000000001</v>
       </c>
       <c r="P30" s="2">
-        <f t="shared" ref="P30:R30" si="144">P26*0.1</f>
+        <f t="shared" ref="P30:R30" si="143">P26*0.1</f>
         <v>193.191</v>
       </c>
       <c r="Q30" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>199.36</v>
       </c>
       <c r="R30" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>215.46699999999998</v>
       </c>
       <c r="S30" s="2">
@@ -6270,12 +6267,11 @@
         <v>824.7</v>
       </c>
       <c r="BA30" s="2">
-        <f>AW30*1.13</f>
-        <v>830.6629999999999</v>
+        <v>853.6</v>
       </c>
       <c r="BB30" s="2">
-        <f>AX30*1.1</f>
-        <v>854.15000000000009</v>
+        <f>AX30*1.16</f>
+        <v>900.7399999999999</v>
       </c>
       <c r="BD30" s="2">
         <v>259.03300000000002</v>
@@ -6300,15 +6296,15 @@
         <v>797.57399999999996</v>
       </c>
       <c r="BJ30" s="15">
+        <f t="shared" si="139"/>
+        <v>953.7</v>
+      </c>
+      <c r="BK30" s="15">
         <f t="shared" si="140"/>
-        <v>953.7</v>
-      </c>
-      <c r="BK30" s="15">
+        <v>1221.8</v>
+      </c>
+      <c r="BL30" s="15">
         <f t="shared" si="141"/>
-        <v>1221.8</v>
-      </c>
-      <c r="BL30" s="15">
-        <f t="shared" si="142"/>
         <v>1545</v>
       </c>
       <c r="BM30" s="15">
@@ -6333,47 +6329,47 @@
       </c>
       <c r="BR30" s="2">
         <f>SUM(AY30:BB30)</f>
-        <v>3332.3130000000001</v>
+        <v>3401.8399999999997</v>
       </c>
       <c r="BS30" s="2">
-        <f>BR30*1.07</f>
-        <v>3565.5749100000003</v>
+        <f>BR30*1.11</f>
+        <v>3776.0423999999998</v>
       </c>
       <c r="BT30" s="2">
-        <f>BS30*1.04</f>
-        <v>3708.1979064000002</v>
+        <f>BS30*1.07</f>
+        <v>4040.3653680000002</v>
       </c>
       <c r="BU30" s="2">
-        <f>BT30*1.03</f>
-        <v>3819.4438435920001</v>
+        <f>BT30*1.04</f>
+        <v>4201.9799827200004</v>
       </c>
       <c r="BV30" s="2">
-        <f>BU30*1.02</f>
-        <v>3895.8327204638404</v>
+        <f>BU30*1.03</f>
+        <v>4328.0393822016003</v>
       </c>
       <c r="BW30" s="2">
-        <f t="shared" ref="BW30:CB31" si="145">BV30*1.01</f>
-        <v>3934.7910476684788</v>
+        <f>BV30*1.02</f>
+        <v>4414.6001698456321</v>
       </c>
       <c r="BX30" s="2">
-        <f t="shared" si="145"/>
-        <v>3974.1389581451635</v>
+        <f t="shared" ref="BX30:CB30" si="144">BW30*1.02</f>
+        <v>4502.8921732425451</v>
       </c>
       <c r="BY30" s="2">
-        <f t="shared" si="145"/>
-        <v>4013.8803477266151</v>
+        <f t="shared" si="144"/>
+        <v>4592.9500167073966</v>
       </c>
       <c r="BZ30" s="2">
-        <f t="shared" si="145"/>
-        <v>4054.0191512038814</v>
+        <f t="shared" si="144"/>
+        <v>4684.8090170415444</v>
       </c>
       <c r="CA30" s="2">
-        <f t="shared" si="145"/>
-        <v>4094.5593427159201</v>
+        <f t="shared" si="144"/>
+        <v>4778.5051973823756</v>
       </c>
       <c r="CB30" s="2">
-        <f t="shared" si="145"/>
-        <v>4135.5049361430792</v>
+        <f t="shared" si="144"/>
+        <v>4874.0753013300236</v>
       </c>
     </row>
     <row r="31" spans="2:80">
@@ -6421,15 +6417,15 @@
         <v>113.7336</v>
       </c>
       <c r="P31" s="2">
-        <f t="shared" ref="P31:R31" si="146">P26*0.06</f>
+        <f t="shared" ref="P31:R31" si="145">P26*0.06</f>
         <v>115.91459999999999</v>
       </c>
       <c r="Q31" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="145"/>
         <v>119.61599999999999</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="145"/>
         <v>129.28019999999998</v>
       </c>
       <c r="S31" s="2">
@@ -6538,12 +6534,11 @@
         <v>441.2</v>
       </c>
       <c r="BA31" s="2">
-        <f t="shared" ref="BA31:BB31" si="147">AW31*1.03</f>
-        <v>429.92199999999997</v>
+        <v>457.9</v>
       </c>
       <c r="BB31" s="2">
-        <f t="shared" si="147"/>
-        <v>467.31099999999998</v>
+        <f>AX31*1.07</f>
+        <v>485.459</v>
       </c>
       <c r="BD31" s="2">
         <v>126.937</v>
@@ -6568,15 +6563,15 @@
         <v>478.54439999999994</v>
       </c>
       <c r="BJ31" s="15">
+        <f t="shared" si="139"/>
+        <v>431</v>
+      </c>
+      <c r="BK31" s="15">
         <f t="shared" si="140"/>
-        <v>431</v>
-      </c>
-      <c r="BK31" s="15">
+        <v>630.29999999999995</v>
+      </c>
+      <c r="BL31" s="15">
         <f t="shared" si="141"/>
-        <v>630.29999999999995</v>
-      </c>
-      <c r="BL31" s="15">
-        <f t="shared" si="142"/>
         <v>914.40000000000009</v>
       </c>
       <c r="BM31" s="15">
@@ -6601,47 +6596,47 @@
       </c>
       <c r="BR31" s="2">
         <f>SUM(AY31:BB31)</f>
-        <v>1759.933</v>
+        <v>1806.059</v>
       </c>
       <c r="BS31" s="2">
-        <f>BR31*1.02</f>
-        <v>1795.13166</v>
+        <f>BR31*1.05</f>
+        <v>1896.36195</v>
       </c>
       <c r="BT31" s="2">
-        <f>BS31*1.02</f>
-        <v>1831.0342932000001</v>
+        <f>BS31*1.03</f>
+        <v>1953.2528085000001</v>
       </c>
       <c r="BU31" s="2">
         <f>BT31*1.02</f>
-        <v>1867.6549790640001</v>
+        <v>1992.3178646700001</v>
       </c>
       <c r="BV31" s="2">
         <f>BU31*1.02</f>
-        <v>1905.0080786452802</v>
+        <v>2032.1642219634</v>
       </c>
       <c r="BW31" s="2">
-        <f t="shared" si="145"/>
-        <v>1924.058159431733</v>
+        <f t="shared" ref="BW31:BX31" si="146">BV31*1.02</f>
+        <v>2072.807506402668</v>
       </c>
       <c r="BX31" s="2">
-        <f t="shared" si="145"/>
-        <v>1943.2987410260503</v>
+        <f t="shared" si="146"/>
+        <v>2114.2636565307212</v>
       </c>
       <c r="BY31" s="2">
-        <f t="shared" si="145"/>
-        <v>1962.7317284363107</v>
+        <f t="shared" ref="BW30:CB31" si="147">BX31*1.01</f>
+        <v>2135.4062930960285</v>
       </c>
       <c r="BZ31" s="2">
-        <f t="shared" si="145"/>
-        <v>1982.3590457206737</v>
+        <f t="shared" si="147"/>
+        <v>2156.760356026989</v>
       </c>
       <c r="CA31" s="2">
-        <f t="shared" si="145"/>
-        <v>2002.1826361778806</v>
+        <f t="shared" si="147"/>
+        <v>2178.3279595872591</v>
       </c>
       <c r="CB31" s="2">
-        <f t="shared" si="145"/>
-        <v>2022.2044625396593</v>
+        <f t="shared" si="147"/>
+        <v>2200.1112391831316</v>
       </c>
     </row>
     <row r="32" spans="2:80" s="1" customFormat="1">
@@ -6850,11 +6845,11 @@
       </c>
       <c r="BA32" s="16">
         <f t="shared" si="166"/>
-        <v>3624.2558399999998</v>
+        <v>3248.1999999999989</v>
       </c>
       <c r="BB32" s="16">
         <f t="shared" si="166"/>
-        <v>2924.6886000000004</v>
+        <v>2630.429000000001</v>
       </c>
       <c r="BD32" s="16">
         <f>BD28-BD29-BD30-BD31</f>
@@ -6914,47 +6909,47 @@
       </c>
       <c r="BR32" s="16">
         <f t="shared" si="167"/>
-        <v>13670.64444</v>
+        <v>13000.329000000003</v>
       </c>
       <c r="BS32" s="16">
         <f t="shared" si="167"/>
-        <v>16319.389015500004</v>
+        <v>15235.543356000004</v>
       </c>
       <c r="BT32" s="16">
         <f t="shared" si="167"/>
-        <v>17952.355817044005</v>
+        <v>16684.211614380001</v>
       </c>
       <c r="BU32" s="16">
         <f t="shared" si="167"/>
-        <v>19515.289625634905</v>
+        <v>18158.598916680006</v>
       </c>
       <c r="BV32" s="16">
         <f t="shared" si="167"/>
-        <v>20967.313059160708</v>
+        <v>19529.631533459647</v>
       </c>
       <c r="BW32" s="16">
         <f t="shared" si="167"/>
-        <v>21712.349266917714</v>
+        <v>20758.829693586686</v>
       </c>
       <c r="BX32" s="16">
         <f t="shared" ref="BX32:CB32" si="168">BX28-BX29-BX30-BX31</f>
-        <v>22205.184744327074</v>
+        <v>21765.307609101648</v>
       </c>
       <c r="BY32" s="16">
         <f t="shared" si="168"/>
-        <v>22708.462816205327</v>
+        <v>22221.756397848989</v>
       </c>
       <c r="BZ32" s="16">
         <f t="shared" si="168"/>
-        <v>23222.398193291061</v>
+        <v>22687.545588736928</v>
       </c>
       <c r="CA32" s="16">
         <f t="shared" si="168"/>
-        <v>23747.209939126129</v>
+        <v>23162.864104071934</v>
       </c>
       <c r="CB32" s="16">
         <f t="shared" si="168"/>
-        <v>24283.121557697588</v>
+        <v>23647.904665749251</v>
       </c>
     </row>
     <row r="33" spans="2:150">
@@ -7120,11 +7115,10 @@
         <v>182.6</v>
       </c>
       <c r="BA33" s="2">
-        <f t="shared" ref="BA33:BB34" si="170">AW33*1.03</f>
-        <v>190.34400000000002</v>
+        <v>175.3</v>
       </c>
       <c r="BB33" s="2">
-        <f t="shared" si="170"/>
+        <f t="shared" ref="BA33:BB34" si="170">AX33*1.03</f>
         <v>198.37799999999999</v>
       </c>
       <c r="BD33" s="2">
@@ -7183,47 +7177,47 @@
       </c>
       <c r="BR33" s="2">
         <f>SUM(AY33:BB33)</f>
-        <v>755.52199999999993</v>
+        <v>740.47799999999984</v>
       </c>
       <c r="BS33" s="2">
         <f t="shared" ref="BS33:CB34" si="174">BR33*1.01</f>
-        <v>763.0772199999999</v>
+        <v>747.8827799999998</v>
       </c>
       <c r="BT33" s="2">
         <f t="shared" si="174"/>
-        <v>770.70799219999992</v>
+        <v>755.36160779999977</v>
       </c>
       <c r="BU33" s="2">
         <f t="shared" si="174"/>
-        <v>778.41507212199997</v>
+        <v>762.91522387799978</v>
       </c>
       <c r="BV33" s="2">
         <f t="shared" si="174"/>
-        <v>786.19922284322001</v>
+        <v>770.54437611677974</v>
       </c>
       <c r="BW33" s="2">
         <f t="shared" si="174"/>
-        <v>794.06121507165221</v>
+        <v>778.24981987794752</v>
       </c>
       <c r="BX33" s="2">
         <f t="shared" si="174"/>
-        <v>802.00182722236877</v>
+        <v>786.03231807672705</v>
       </c>
       <c r="BY33" s="2">
         <f t="shared" si="174"/>
-        <v>810.02184549459253</v>
+        <v>793.89264125749435</v>
       </c>
       <c r="BZ33" s="2">
         <f t="shared" si="174"/>
-        <v>818.12206394953841</v>
+        <v>801.83156767006926</v>
       </c>
       <c r="CA33" s="2">
         <f t="shared" si="174"/>
-        <v>826.30328458903375</v>
+        <v>809.84988334676996</v>
       </c>
       <c r="CB33" s="2">
         <f t="shared" si="174"/>
-        <v>834.56631743492414</v>
+        <v>817.94838218023767</v>
       </c>
     </row>
     <row r="34" spans="2:150">
@@ -7384,8 +7378,7 @@
         <v>-39.6</v>
       </c>
       <c r="BA34" s="2">
-        <f t="shared" si="170"/>
-        <v>22.350999999999999</v>
+        <v>-36.5</v>
       </c>
       <c r="BB34" s="2">
         <f t="shared" si="170"/>
@@ -7446,47 +7439,47 @@
       </c>
       <c r="BR34" s="2">
         <f>SUM(AY34:BB34)</f>
-        <v>-123.87200000000001</v>
+        <v>-182.72300000000001</v>
       </c>
       <c r="BS34" s="2">
         <f t="shared" si="174"/>
-        <v>-125.11072000000001</v>
+        <v>-184.55023000000003</v>
       </c>
       <c r="BT34" s="2">
         <f t="shared" si="174"/>
-        <v>-126.36182720000002</v>
+        <v>-186.39573230000002</v>
       </c>
       <c r="BU34" s="2">
         <f t="shared" si="174"/>
-        <v>-127.62544547200002</v>
+        <v>-188.25968962300001</v>
       </c>
       <c r="BV34" s="2">
         <f t="shared" si="174"/>
-        <v>-128.90169992672003</v>
+        <v>-190.14228651923003</v>
       </c>
       <c r="BW34" s="2">
         <f t="shared" si="174"/>
-        <v>-130.19071692598723</v>
+        <v>-192.04370938442233</v>
       </c>
       <c r="BX34" s="2">
         <f t="shared" si="174"/>
-        <v>-131.49262409524709</v>
+        <v>-193.96414647826654</v>
       </c>
       <c r="BY34" s="2">
         <f t="shared" si="174"/>
-        <v>-132.80755033619957</v>
+        <v>-195.9037879430492</v>
       </c>
       <c r="BZ34" s="2">
         <f t="shared" si="174"/>
-        <v>-134.13562583956156</v>
+        <v>-197.86282582247969</v>
       </c>
       <c r="CA34" s="2">
         <f t="shared" si="174"/>
-        <v>-135.47698209795718</v>
+        <v>-199.84145408070449</v>
       </c>
       <c r="CB34" s="2">
         <f t="shared" si="174"/>
-        <v>-136.83175191893676</v>
+        <v>-201.83986862151153</v>
       </c>
     </row>
     <row r="35" spans="2:150" s="1" customFormat="1">
@@ -7695,11 +7688,11 @@
       </c>
       <c r="BA35" s="16">
         <f t="shared" si="194"/>
-        <v>3411.5608399999996</v>
+        <v>3109.3999999999987</v>
       </c>
       <c r="BB35" s="16">
         <f t="shared" si="194"/>
-        <v>2782.0336000000002</v>
+        <v>2487.7740000000008</v>
       </c>
       <c r="BD35" s="16">
         <f>BD32-BD33-BD34</f>
@@ -7759,47 +7752,47 @@
       </c>
       <c r="BR35" s="16">
         <f t="shared" si="195"/>
-        <v>13038.994439999999</v>
+        <v>12442.574000000004</v>
       </c>
       <c r="BS35" s="16">
         <f t="shared" si="195"/>
-        <v>15681.422515500006</v>
+        <v>14672.210806000005</v>
       </c>
       <c r="BT35" s="16">
         <f t="shared" si="195"/>
-        <v>17308.009652044002</v>
+        <v>16115.245738880001</v>
       </c>
       <c r="BU35" s="16">
         <f t="shared" si="195"/>
-        <v>18864.499998984906</v>
+        <v>17583.943382425005</v>
       </c>
       <c r="BV35" s="16">
         <f t="shared" si="195"/>
-        <v>20310.015536244206</v>
+        <v>18949.229443862096</v>
       </c>
       <c r="BW35" s="16">
         <f t="shared" si="195"/>
-        <v>21048.478768772049</v>
+        <v>20172.623583093162</v>
       </c>
       <c r="BX35" s="16">
         <f t="shared" ref="BX35:CB35" si="196">BX32-BX33-BX34</f>
-        <v>21534.675541199955</v>
+        <v>21173.239437503187</v>
       </c>
       <c r="BY35" s="16">
         <f t="shared" si="196"/>
-        <v>22031.248521046931</v>
+        <v>21623.767544534545</v>
       </c>
       <c r="BZ35" s="16">
         <f t="shared" si="196"/>
-        <v>22538.411755181085</v>
+        <v>22083.576846889337</v>
       </c>
       <c r="CA35" s="16">
         <f t="shared" si="196"/>
-        <v>23056.383636635052</v>
+        <v>22552.855674805869</v>
       </c>
       <c r="CB35" s="16">
         <f t="shared" si="196"/>
-        <v>23585.3869921816</v>
+        <v>23031.796152190524</v>
       </c>
     </row>
     <row r="36" spans="2:150">
@@ -7964,12 +7957,11 @@
         <v>506.3</v>
       </c>
       <c r="BA36" s="2">
-        <f t="shared" ref="BA36:BB36" si="198">BA35*0.12</f>
-        <v>409.38730079999993</v>
+        <v>562.5</v>
       </c>
       <c r="BB36" s="2">
-        <f t="shared" si="198"/>
-        <v>333.84403200000003</v>
+        <f t="shared" ref="BA36:BB36" si="198">BB35*0.12</f>
+        <v>298.53288000000009</v>
       </c>
       <c r="BD36" s="2">
         <v>133.39599999999999</v>
@@ -8027,47 +8019,47 @@
       </c>
       <c r="BR36" s="2">
         <f>SUM(AY36:BB36)</f>
-        <v>1572.9313327999998</v>
+        <v>1690.73288</v>
       </c>
       <c r="BS36" s="2">
         <f>BS35*0.13</f>
-        <v>2038.5849270150009</v>
+        <v>1907.3874047800007</v>
       </c>
       <c r="BT36" s="2">
         <f t="shared" ref="BT36:CB36" si="202">BT35*0.13</f>
-        <v>2250.0412547657202</v>
+        <v>2094.9819460544004</v>
       </c>
       <c r="BU36" s="2">
         <f t="shared" si="202"/>
-        <v>2452.384999868038</v>
+        <v>2285.9126397152509</v>
       </c>
       <c r="BV36" s="2">
         <f t="shared" si="202"/>
-        <v>2640.3020197117467</v>
+        <v>2463.3998277020723</v>
       </c>
       <c r="BW36" s="2">
         <f t="shared" si="202"/>
-        <v>2736.3022399403667</v>
+        <v>2622.4410658021111</v>
       </c>
       <c r="BX36" s="2">
         <f t="shared" si="202"/>
-        <v>2799.5078203559942</v>
+        <v>2752.5211268754142</v>
       </c>
       <c r="BY36" s="2">
         <f t="shared" si="202"/>
-        <v>2864.062307736101</v>
+        <v>2811.0897807894908</v>
       </c>
       <c r="BZ36" s="2">
         <f t="shared" si="202"/>
-        <v>2929.9935281735411</v>
+        <v>2870.8649900956138</v>
       </c>
       <c r="CA36" s="2">
         <f t="shared" si="202"/>
-        <v>2997.329872762557</v>
+        <v>2931.871237724763</v>
       </c>
       <c r="CB36" s="2">
         <f t="shared" si="202"/>
-        <v>3066.1003089836081</v>
+        <v>2994.133499784768</v>
       </c>
     </row>
     <row r="37" spans="2:150" s="1" customFormat="1">
@@ -8276,11 +8268,11 @@
       </c>
       <c r="BA37" s="16">
         <f t="shared" si="224"/>
-        <v>3002.1735391999996</v>
+        <v>2546.8999999999987</v>
       </c>
       <c r="BB37" s="16">
         <f t="shared" si="224"/>
-        <v>2448.1895680000002</v>
+        <v>2189.2411200000006</v>
       </c>
       <c r="BD37" s="16">
         <f>BD35-BD36</f>
@@ -8340,327 +8332,327 @@
       </c>
       <c r="BR37" s="16">
         <f t="shared" si="225"/>
-        <v>11466.0631072</v>
+        <v>10751.841120000005</v>
       </c>
       <c r="BS37" s="16">
         <f t="shared" si="225"/>
-        <v>13642.837588485005</v>
+        <v>12764.823401220005</v>
       </c>
       <c r="BT37" s="16">
         <f t="shared" si="225"/>
-        <v>15057.968397278282</v>
+        <v>14020.263792825601</v>
       </c>
       <c r="BU37" s="16">
         <f t="shared" si="225"/>
-        <v>16412.114999116868</v>
+        <v>15298.030742709754</v>
       </c>
       <c r="BV37" s="16">
         <f t="shared" si="225"/>
-        <v>17669.713516532458</v>
+        <v>16485.829616160023</v>
       </c>
       <c r="BW37" s="16">
         <f t="shared" si="225"/>
-        <v>18312.176528831682</v>
+        <v>17550.18251729105</v>
       </c>
       <c r="BX37" s="16">
         <f t="shared" ref="BX37:CB37" si="226">BX35-BX36</f>
-        <v>18735.167720843961</v>
+        <v>18420.718310627773</v>
       </c>
       <c r="BY37" s="16">
         <f t="shared" si="226"/>
-        <v>19167.18621331083</v>
+        <v>18812.677763745054</v>
       </c>
       <c r="BZ37" s="16">
         <f t="shared" si="226"/>
-        <v>19608.418227007543</v>
+        <v>19212.711856793721</v>
       </c>
       <c r="CA37" s="16">
         <f t="shared" si="226"/>
-        <v>20059.053763872493</v>
+        <v>19620.984437081104</v>
       </c>
       <c r="CB37" s="16">
         <f t="shared" si="226"/>
-        <v>20519.286683197992</v>
+        <v>20037.662652405757</v>
       </c>
       <c r="CC37" s="1">
         <f>CB37*(1+$CE$46)</f>
-        <v>20314.09381636601</v>
+        <v>19837.286025881698</v>
       </c>
       <c r="CD37" s="1">
         <f t="shared" ref="CD37:EO37" si="227">CC37*(1+$CE$46)</f>
-        <v>20110.952878202352</v>
+        <v>19638.913165622882</v>
       </c>
       <c r="CE37" s="1">
         <f t="shared" si="227"/>
-        <v>19909.843349420327</v>
+        <v>19442.524033966652</v>
       </c>
       <c r="CF37" s="1">
         <f t="shared" si="227"/>
-        <v>19710.744915926123</v>
+        <v>19248.098793626985</v>
       </c>
       <c r="CG37" s="1">
         <f t="shared" si="227"/>
-        <v>19513.637466766861</v>
+        <v>19055.617805690716</v>
       </c>
       <c r="CH37" s="1">
         <f t="shared" si="227"/>
-        <v>19318.501092099192</v>
+        <v>18865.061627633808</v>
       </c>
       <c r="CI37" s="1">
         <f t="shared" si="227"/>
-        <v>19125.3160811782</v>
+        <v>18676.411011357468</v>
       </c>
       <c r="CJ37" s="1">
         <f t="shared" si="227"/>
-        <v>18934.062920366418</v>
+        <v>18489.646901243894</v>
       </c>
       <c r="CK37" s="1">
         <f t="shared" si="227"/>
-        <v>18744.722291162754</v>
+        <v>18304.750432231456</v>
       </c>
       <c r="CL37" s="1">
         <f t="shared" si="227"/>
-        <v>18557.275068251125</v>
+        <v>18121.70292790914</v>
       </c>
       <c r="CM37" s="1">
         <f t="shared" si="227"/>
-        <v>18371.702317568615</v>
+        <v>17940.48589863005</v>
       </c>
       <c r="CN37" s="1">
         <f t="shared" si="227"/>
-        <v>18187.985294392929</v>
+        <v>17761.081039643748</v>
       </c>
       <c r="CO37" s="1">
         <f t="shared" si="227"/>
-        <v>18006.105441448999</v>
+        <v>17583.470229247312</v>
       </c>
       <c r="CP37" s="1">
         <f t="shared" si="227"/>
-        <v>17826.044387034508</v>
+        <v>17407.63552695484</v>
       </c>
       <c r="CQ37" s="1">
         <f t="shared" si="227"/>
-        <v>17647.783943164162</v>
+        <v>17233.55917168529</v>
       </c>
       <c r="CR37" s="1">
         <f t="shared" si="227"/>
-        <v>17471.306103732521</v>
+        <v>17061.223579968439</v>
       </c>
       <c r="CS37" s="1">
         <f t="shared" si="227"/>
-        <v>17296.593042695196</v>
+        <v>16890.611344168756</v>
       </c>
       <c r="CT37" s="1">
         <f t="shared" si="227"/>
-        <v>17123.627112268245</v>
+        <v>16721.705230727068</v>
       </c>
       <c r="CU37" s="1">
         <f t="shared" si="227"/>
-        <v>16952.390841145563</v>
+        <v>16554.488178419797</v>
       </c>
       <c r="CV37" s="1">
         <f t="shared" si="227"/>
-        <v>16782.866932734109</v>
+        <v>16388.9432966356</v>
       </c>
       <c r="CW37" s="1">
         <f t="shared" si="227"/>
-        <v>16615.038263406768</v>
+        <v>16225.053863669244</v>
       </c>
       <c r="CX37" s="1">
         <f t="shared" si="227"/>
-        <v>16448.887880772701</v>
+        <v>16062.803325032552</v>
       </c>
       <c r="CY37" s="1">
         <f t="shared" si="227"/>
-        <v>16284.399001964974</v>
+        <v>15902.175291782225</v>
       </c>
       <c r="CZ37" s="1">
         <f t="shared" si="227"/>
-        <v>16121.555011945324</v>
+        <v>15743.153538864402</v>
       </c>
       <c r="DA37" s="1">
         <f t="shared" si="227"/>
-        <v>15960.33946182587</v>
+        <v>15585.722003475757</v>
       </c>
       <c r="DB37" s="1">
         <f t="shared" si="227"/>
-        <v>15800.73606720761</v>
+        <v>15429.864783441</v>
       </c>
       <c r="DC37" s="1">
         <f t="shared" si="227"/>
-        <v>15642.728706535534</v>
+        <v>15275.56613560659</v>
       </c>
       <c r="DD37" s="1">
         <f t="shared" si="227"/>
-        <v>15486.301419470179</v>
+        <v>15122.810474250524</v>
       </c>
       <c r="DE37" s="1">
         <f t="shared" si="227"/>
-        <v>15331.438405275478</v>
+        <v>14971.582369508018</v>
       </c>
       <c r="DF37" s="1">
         <f t="shared" si="227"/>
-        <v>15178.124021222722</v>
+        <v>14821.866545812938</v>
       </c>
       <c r="DG37" s="1">
         <f t="shared" si="227"/>
-        <v>15026.342781010495</v>
+        <v>14673.647880354809</v>
       </c>
       <c r="DH37" s="1">
         <f t="shared" si="227"/>
-        <v>14876.07935320039</v>
+        <v>14526.91140155126</v>
       </c>
       <c r="DI37" s="1">
         <f t="shared" si="227"/>
-        <v>14727.318559668385</v>
+        <v>14381.642287535748</v>
       </c>
       <c r="DJ37" s="1">
         <f t="shared" si="227"/>
-        <v>14580.045374071702</v>
+        <v>14237.82586466039</v>
       </c>
       <c r="DK37" s="1">
         <f t="shared" si="227"/>
-        <v>14434.244920330984</v>
+        <v>14095.447606013786</v>
       </c>
       <c r="DL37" s="1">
         <f t="shared" si="227"/>
-        <v>14289.902471127674</v>
+        <v>13954.493129953647</v>
       </c>
       <c r="DM37" s="1">
         <f t="shared" si="227"/>
-        <v>14147.003446416398</v>
+        <v>13814.94819865411</v>
       </c>
       <c r="DN37" s="1">
         <f t="shared" si="227"/>
-        <v>14005.533411952234</v>
+        <v>13676.798716667568</v>
       </c>
       <c r="DO37" s="1">
         <f t="shared" si="227"/>
-        <v>13865.478077832711</v>
+        <v>13540.030729500893</v>
       </c>
       <c r="DP37" s="1">
         <f t="shared" si="227"/>
-        <v>13726.823297054383</v>
+        <v>13404.630422205884</v>
       </c>
       <c r="DQ37" s="1">
         <f t="shared" si="227"/>
-        <v>13589.555064083839</v>
+        <v>13270.584117983826</v>
       </c>
       <c r="DR37" s="1">
         <f t="shared" si="227"/>
-        <v>13453.659513443001</v>
+        <v>13137.878276803987</v>
       </c>
       <c r="DS37" s="1">
         <f t="shared" si="227"/>
-        <v>13319.122918308571</v>
+        <v>13006.499494035947</v>
       </c>
       <c r="DT37" s="1">
         <f t="shared" si="227"/>
-        <v>13185.931689125486</v>
+        <v>12876.434499095587</v>
       </c>
       <c r="DU37" s="1">
         <f t="shared" si="227"/>
-        <v>13054.07237223423</v>
+        <v>12747.670154104631</v>
       </c>
       <c r="DV37" s="1">
         <f t="shared" si="227"/>
-        <v>12923.531648511887</v>
+        <v>12620.193452563584</v>
       </c>
       <c r="DW37" s="1">
         <f t="shared" si="227"/>
-        <v>12794.296332026768</v>
+        <v>12493.991518037948</v>
       </c>
       <c r="DX37" s="1">
         <f t="shared" si="227"/>
-        <v>12666.353368706501</v>
+        <v>12369.051602857569</v>
       </c>
       <c r="DY37" s="1">
         <f t="shared" si="227"/>
-        <v>12539.689835019435</v>
+        <v>12245.361086828994</v>
       </c>
       <c r="DZ37" s="1">
         <f t="shared" si="227"/>
-        <v>12414.292936669241</v>
+        <v>12122.907475960705</v>
       </c>
       <c r="EA37" s="1">
         <f t="shared" si="227"/>
-        <v>12290.150007302547</v>
+        <v>12001.678401201098</v>
       </c>
       <c r="EB37" s="1">
         <f t="shared" si="227"/>
-        <v>12167.248507229522</v>
+        <v>11881.661617189087</v>
       </c>
       <c r="EC37" s="1">
         <f t="shared" si="227"/>
-        <v>12045.576022157227</v>
+        <v>11762.845001017196</v>
       </c>
       <c r="ED37" s="1">
         <f t="shared" si="227"/>
-        <v>11925.120261935655</v>
+        <v>11645.216551007024</v>
       </c>
       <c r="EE37" s="1">
         <f t="shared" si="227"/>
-        <v>11805.869059316299</v>
+        <v>11528.764385496954</v>
       </c>
       <c r="EF37" s="1">
         <f t="shared" si="227"/>
-        <v>11687.810368723136</v>
+        <v>11413.476741641984</v>
       </c>
       <c r="EG37" s="1">
         <f t="shared" si="227"/>
-        <v>11570.932265035904</v>
+        <v>11299.341974225563</v>
       </c>
       <c r="EH37" s="1">
         <f t="shared" si="227"/>
-        <v>11455.222942385546</v>
+        <v>11186.348554483307</v>
       </c>
       <c r="EI37" s="1">
         <f t="shared" si="227"/>
-        <v>11340.67071296169</v>
+        <v>11074.485068938475</v>
       </c>
       <c r="EJ37" s="1">
         <f t="shared" si="227"/>
-        <v>11227.264005832072</v>
+        <v>10963.74021824909</v>
       </c>
       <c r="EK37" s="1">
         <f t="shared" si="227"/>
-        <v>11114.991365773751</v>
+        <v>10854.102816066599</v>
       </c>
       <c r="EL37" s="1">
         <f t="shared" si="227"/>
-        <v>11003.841452116014</v>
+        <v>10745.561787905934</v>
       </c>
       <c r="EM37" s="1">
         <f t="shared" si="227"/>
-        <v>10893.803037594853</v>
+        <v>10638.106170026875</v>
       </c>
       <c r="EN37" s="1">
         <f t="shared" si="227"/>
-        <v>10784.865007218905</v>
+        <v>10531.725108326606</v>
       </c>
       <c r="EO37" s="1">
         <f t="shared" si="227"/>
-        <v>10677.016357146716</v>
+        <v>10426.407857243339</v>
       </c>
       <c r="EP37" s="1">
         <f t="shared" ref="EP37:ET37" si="228">EO37*(1+$CE$46)</f>
-        <v>10570.246193575249</v>
+        <v>10322.143778670905</v>
       </c>
       <c r="EQ37" s="1">
         <f t="shared" si="228"/>
-        <v>10464.543731639496</v>
+        <v>10218.922340884195</v>
       </c>
       <c r="ER37" s="1">
         <f t="shared" si="228"/>
-        <v>10359.898294323102</v>
+        <v>10116.733117475353</v>
       </c>
       <c r="ES37" s="1">
         <f t="shared" si="228"/>
-        <v>10256.299311379871</v>
+        <v>10015.565786300598</v>
       </c>
       <c r="ET37" s="1">
         <f t="shared" si="228"/>
-        <v>10153.736318266072</v>
+        <v>9915.410128437592</v>
       </c>
     </row>
     <row r="38" spans="2:150">
@@ -8820,12 +8812,12 @@
         <v>425.2</v>
       </c>
       <c r="BA38" s="2">
-        <f>425.2</f>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BB38" s="2">
-        <f>425.2</f>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BD38" s="2">
         <v>428</v>
@@ -8875,48 +8867,48 @@
         <v>427.7</v>
       </c>
       <c r="BR38" s="2">
-        <f t="shared" ref="BR38:CB38" si="230">425.2</f>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BS38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BT38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BU38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BV38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BW38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BX38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BY38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="BZ38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="CA38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
       <c r="CB38" s="2">
-        <f t="shared" si="230"/>
-        <v>425.2</v>
+        <f>423.7</f>
+        <v>423.7</v>
       </c>
     </row>
     <row r="39" spans="2:150" s="1" customFormat="1">
@@ -8924,312 +8916,312 @@
         <v>38</v>
       </c>
       <c r="C39" s="8">
-        <f t="shared" ref="C39:N39" si="231">C37/C38</f>
+        <f t="shared" ref="C39:N39" si="230">C37/C38</f>
         <v>6.2827102803738547E-3</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>6.8857476635514253E-2</v>
       </c>
       <c r="E39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>7.435046728971971E-2</v>
       </c>
       <c r="F39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0.11313317757009347</v>
       </c>
       <c r="G39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0.12410046728971937</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0.16592990654205639</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0.13853971962616823</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0.19479205607476652</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>5.5364485981308532E-2</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>6.1530373831775717E-2</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>6.8766355140186836E-2</v>
       </c>
       <c r="N39" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0.10087616822429955</v>
       </c>
       <c r="O39" s="8">
-        <f t="shared" ref="O39" si="232">O37/O38</f>
+        <f t="shared" ref="O39" si="231">O37/O38</f>
         <v>9.4851161214953308E-2</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" ref="P39" si="233">P37/P38</f>
+        <f t="shared" ref="P39" si="232">P37/P38</f>
         <v>9.7238467219626173E-2</v>
       </c>
       <c r="Q39" s="8">
-        <f t="shared" ref="Q39" si="234">Q37/Q38</f>
+        <f t="shared" ref="Q39" si="233">Q37/Q38</f>
         <v>0.10169211707873844</v>
       </c>
       <c r="R39" s="8">
-        <f t="shared" ref="R39:S39" si="235">R37/R38</f>
+        <f t="shared" ref="R39:S39" si="234">R37/R38</f>
         <v>0.11426672516541356</v>
       </c>
       <c r="S39" s="8">
+        <f t="shared" si="234"/>
+        <v>0.40680272108843585</v>
+      </c>
+      <c r="T39" s="8">
+        <f t="shared" ref="T39:V39" si="235">T37/T38</f>
+        <v>0.14970521541950144</v>
+      </c>
+      <c r="U39" s="8">
         <f t="shared" si="235"/>
-        <v>0.40680272108843585</v>
-      </c>
-      <c r="T39" s="8">
-        <f t="shared" ref="T39:V39" si="236">T37/T38</f>
-        <v>0.14970521541950144</v>
-      </c>
-      <c r="U39" s="8">
-        <f t="shared" si="236"/>
         <v>0.2310476190476187</v>
       </c>
       <c r="V39" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="235"/>
         <v>0.4793922902494332</v>
       </c>
       <c r="W39" s="8">
-        <f t="shared" ref="W39" si="237">W37/W38</f>
+        <f t="shared" ref="W39" si="236">W37/W38</f>
         <v>0.66026303854875334</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" ref="X39" si="238">X37/X38</f>
+        <f t="shared" ref="X39" si="237">X37/X38</f>
         <v>0.84488707482993164</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" ref="Y39:Z39" si="239">Y37/Y38</f>
+        <f t="shared" ref="Y39:Z39" si="238">Y37/Y38</f>
         <v>0.91272680272108864</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="238"/>
         <v>0.32954557823129504</v>
       </c>
       <c r="AA39" s="8">
-        <f t="shared" ref="AA39" si="240">AA37/AA38</f>
+        <f t="shared" ref="AA39" si="239">AA37/AA38</f>
         <v>0.43492063492063548</v>
       </c>
       <c r="AB39" s="8">
-        <f t="shared" ref="AB39" si="241">AB37/AB38</f>
+        <f t="shared" ref="AB39" si="240">AB37/AB38</f>
         <v>0.6131519274376418</v>
       </c>
       <c r="AC39" s="8">
-        <f t="shared" ref="AC39:AD39" si="242">AC37/AC38</f>
+        <f t="shared" ref="AC39:AD39" si="241">AC37/AC38</f>
         <v>1.5265306122448978</v>
       </c>
       <c r="AD39" s="8">
+        <f t="shared" si="241"/>
+        <v>1.6761904761904738</v>
+      </c>
+      <c r="AE39" s="8">
+        <f t="shared" ref="AE39:AF39" si="242">AE37/AE38</f>
+        <v>1.6086167800453521</v>
+      </c>
+      <c r="AF39" s="8">
         <f t="shared" si="242"/>
-        <v>1.6761904761904738</v>
-      </c>
-      <c r="AE39" s="8">
-        <f t="shared" ref="AE39:AF39" si="243">AE37/AE38</f>
-        <v>1.6086167800453521</v>
-      </c>
-      <c r="AF39" s="8">
+        <v>1.6328798185941045</v>
+      </c>
+      <c r="AG39" s="8">
+        <f t="shared" ref="AG39:AH39" si="243">AG37/AG38</f>
+        <v>1.7789592760180994</v>
+      </c>
+      <c r="AH39" s="8">
         <f t="shared" si="243"/>
-        <v>1.6328798185941045</v>
-      </c>
-      <c r="AG39" s="8">
-        <f t="shared" ref="AG39:AH39" si="244">AG37/AG38</f>
-        <v>1.7789592760180994</v>
-      </c>
-      <c r="AH39" s="8">
+        <v>1.2260180995475112</v>
+      </c>
+      <c r="AI39" s="8">
+        <f t="shared" ref="AI39:AM39" si="244">AI37/AI38</f>
+        <v>3.8631221719457018</v>
+      </c>
+      <c r="AJ39" s="8">
         <f t="shared" si="244"/>
-        <v>1.2260180995475112</v>
-      </c>
-      <c r="AI39" s="8">
-        <f t="shared" ref="AI39:AM39" si="245">AI37/AI38</f>
-        <v>3.8631221719457018</v>
-      </c>
-      <c r="AJ39" s="8">
-        <f t="shared" si="245"/>
         <v>3.0530234657039714</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="244"/>
         <v>3.2725835591689232</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" ref="AL39" si="246">AL37/AL38</f>
+        <f t="shared" ref="AL39" si="245">AL37/AL38</f>
         <v>1.3695603156708001</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="244"/>
         <v>3.5971628011709078</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" ref="AN39:AO39" si="247">AN37/AN38</f>
+        <f t="shared" ref="AN39:AO39" si="246">AN37/AN38</f>
         <v>3.2404408457040041</v>
       </c>
       <c r="AO39" s="8">
+        <f t="shared" si="246"/>
+        <v>3.1429534726904937</v>
+      </c>
+      <c r="AP39" s="8">
+        <f t="shared" ref="AP39:AR39" si="247">AP37/AP38</f>
+        <v>0.12421383647798885</v>
+      </c>
+      <c r="AQ39" s="8">
+        <f t="shared" ref="AQ39" si="248">AQ37/AQ38</f>
+        <v>2.9314914645103318</v>
+      </c>
+      <c r="AR39" s="8">
         <f t="shared" si="247"/>
-        <v>3.1429534726904937</v>
-      </c>
-      <c r="AP39" s="8">
-        <f t="shared" ref="AP39:AR39" si="248">AP37/AP38</f>
-        <v>0.12421383647798885</v>
-      </c>
-      <c r="AQ39" s="8">
-        <f t="shared" ref="AQ39" si="249">AQ37/AQ38</f>
-        <v>2.9314914645103318</v>
-      </c>
-      <c r="AR39" s="8">
-        <f t="shared" si="248"/>
         <v>3.3512052264023438</v>
       </c>
       <c r="AS39" s="8">
-        <f t="shared" ref="AS39" si="250">AS37/AS38</f>
+        <f t="shared" ref="AS39" si="249">AS37/AS38</f>
         <v>3.7993204983012485</v>
       </c>
       <c r="AT39" s="8">
-        <f t="shared" ref="AT39:AU39" si="251">AT37/AT38</f>
+        <f t="shared" ref="AT39:AU39" si="250">AT37/AT38</f>
         <v>2.1516402844689138</v>
       </c>
       <c r="AU39" s="8">
+        <f t="shared" si="250"/>
+        <v>5.3973617218236489</v>
+      </c>
+      <c r="AV39" s="8">
+        <f t="shared" ref="AV39:AX39" si="251">AV37/AV38</f>
+        <v>4.9692200879426043</v>
+      </c>
+      <c r="AW39" s="8">
         <f t="shared" si="251"/>
-        <v>5.3973617218236489</v>
-      </c>
-      <c r="AV39" s="8">
-        <f t="shared" ref="AV39:AX39" si="252">AV37/AV38</f>
-        <v>4.9692200879426043</v>
-      </c>
-      <c r="AW39" s="8">
+        <v>5.5286549707602362</v>
+      </c>
+      <c r="AX39" s="8">
+        <f t="shared" si="251"/>
+        <v>4.3687163899929873</v>
+      </c>
+      <c r="AY39" s="8">
+        <f t="shared" ref="AY39:BB39" si="252">AY37/AY38</f>
+        <v>6.7895231383603463</v>
+      </c>
+      <c r="AZ39" s="8">
         <f t="shared" si="252"/>
-        <v>5.5286549707602362</v>
-      </c>
-      <c r="AX39" s="8">
+        <v>7.3504233301975557</v>
+      </c>
+      <c r="BA39" s="8">
         <f t="shared" si="252"/>
-        <v>4.3687163899929873</v>
-      </c>
-      <c r="AY39" s="8">
-        <f t="shared" ref="AY39:BB39" si="253">AY37/AY38</f>
-        <v>6.7895231383603463</v>
-      </c>
-      <c r="AZ39" s="8">
+        <v>6.0110927543072901</v>
+      </c>
+      <c r="BB39" s="8">
+        <f t="shared" si="252"/>
+        <v>5.1669603965069637</v>
+      </c>
+      <c r="BD39" s="8">
+        <f t="shared" ref="BD39:BX39" si="253">BD37/BD38</f>
+        <v>0.52833177570093515</v>
+      </c>
+      <c r="BE39" s="8">
         <f t="shared" si="253"/>
-        <v>7.3504233301975557</v>
-      </c>
-      <c r="BA39" s="8">
+        <v>4.0074766355140665E-2</v>
+      </c>
+      <c r="BF39" s="8">
         <f t="shared" si="253"/>
-        <v>7.0606150968955781</v>
-      </c>
-      <c r="BB39" s="8">
+        <v>0.2626238317757007</v>
+      </c>
+      <c r="BG39" s="8">
         <f t="shared" si="253"/>
-        <v>5.7577365192850429</v>
-      </c>
-      <c r="BD39" s="8">
-        <f t="shared" ref="BD39:BX39" si="254">BD37/BD38</f>
-        <v>0.52833177570093515</v>
-      </c>
-      <c r="BE39" s="8">
+        <v>0.62336214953271085</v>
+      </c>
+      <c r="BH39" s="8">
+        <f t="shared" si="253"/>
+        <v>0.28653738317757166</v>
+      </c>
+      <c r="BI39" s="8">
+        <f t="shared" si="253"/>
+        <v>0.30057183516471309</v>
+      </c>
+      <c r="BJ39" s="8">
+        <f t="shared" si="253"/>
+        <v>1.305429906542054</v>
+      </c>
+      <c r="BK39" s="8">
+        <f t="shared" si="253"/>
+        <v>2.8308722429906554</v>
+      </c>
+      <c r="BL39" s="8">
+        <f t="shared" si="253"/>
+        <v>4.3565420560747645</v>
+      </c>
+      <c r="BM39" s="8">
+        <f t="shared" si="253"/>
+        <v>6.2391402714932118</v>
+      </c>
+      <c r="BN39" s="8">
+        <f t="shared" si="253"/>
+        <v>11.537993235625699</v>
+      </c>
+      <c r="BO39" s="8">
+        <f t="shared" si="253"/>
+        <v>10.089398023360282</v>
+      </c>
+      <c r="BP39" s="8">
+        <f t="shared" si="253"/>
+        <v>12.406515255792614</v>
+      </c>
+      <c r="BQ39" s="8">
+        <f t="shared" si="253"/>
+        <v>20.368014963759627</v>
+      </c>
+      <c r="BR39" s="8">
+        <f t="shared" si="253"/>
+        <v>25.376070616001901</v>
+      </c>
+      <c r="BS39" s="8">
+        <f t="shared" si="253"/>
+        <v>30.127031865046035</v>
+      </c>
+      <c r="BT39" s="8">
+        <f t="shared" si="253"/>
+        <v>33.090072676010386</v>
+      </c>
+      <c r="BU39" s="8">
+        <f t="shared" si="253"/>
+        <v>36.105807747721869</v>
+      </c>
+      <c r="BV39" s="8">
+        <f t="shared" si="253"/>
+        <v>38.909203719990614</v>
+      </c>
+      <c r="BW39" s="8">
+        <f t="shared" si="253"/>
+        <v>41.421247385629101</v>
+      </c>
+      <c r="BX39" s="8">
+        <f t="shared" si="253"/>
+        <v>43.475851570988375</v>
+      </c>
+      <c r="BY39" s="8">
+        <f t="shared" ref="BY39:CB39" si="254">BY37/BY38</f>
+        <v>44.400938786275795</v>
+      </c>
+      <c r="BZ39" s="8">
         <f t="shared" si="254"/>
-        <v>4.0074766355140665E-2</v>
-      </c>
-      <c r="BF39" s="8">
+        <v>45.34508344770763</v>
+      </c>
+      <c r="CA39" s="8">
         <f t="shared" si="254"/>
-        <v>0.2626238317757007</v>
-      </c>
-      <c r="BG39" s="8">
+        <v>46.308672261225169</v>
+      </c>
+      <c r="CB39" s="8">
         <f t="shared" si="254"/>
-        <v>0.62336214953271085</v>
-      </c>
-      <c r="BH39" s="8">
-        <f t="shared" si="254"/>
-        <v>0.28653738317757166</v>
-      </c>
-      <c r="BI39" s="8">
-        <f t="shared" si="254"/>
-        <v>0.30057183516471309</v>
-      </c>
-      <c r="BJ39" s="8">
-        <f t="shared" si="254"/>
-        <v>1.305429906542054</v>
-      </c>
-      <c r="BK39" s="8">
-        <f t="shared" si="254"/>
-        <v>2.8308722429906554</v>
-      </c>
-      <c r="BL39" s="8">
-        <f t="shared" si="254"/>
-        <v>4.3565420560747645</v>
-      </c>
-      <c r="BM39" s="8">
-        <f t="shared" si="254"/>
-        <v>6.2391402714932118</v>
-      </c>
-      <c r="BN39" s="8">
-        <f t="shared" si="254"/>
-        <v>11.537993235625699</v>
-      </c>
-      <c r="BO39" s="8">
-        <f t="shared" si="254"/>
-        <v>10.089398023360282</v>
-      </c>
-      <c r="BP39" s="8">
-        <f t="shared" si="254"/>
-        <v>12.406515255792614</v>
-      </c>
-      <c r="BQ39" s="8">
-        <f t="shared" si="254"/>
-        <v>20.368014963759627</v>
-      </c>
-      <c r="BR39" s="8">
-        <f t="shared" si="254"/>
-        <v>26.966282001881467</v>
-      </c>
-      <c r="BS39" s="8">
-        <f t="shared" si="254"/>
-        <v>32.085695175176397</v>
-      </c>
-      <c r="BT39" s="8">
-        <f t="shared" si="254"/>
-        <v>35.413848535461625</v>
-      </c>
-      <c r="BU39" s="8">
-        <f t="shared" si="254"/>
-        <v>38.598577138092352</v>
-      </c>
-      <c r="BV39" s="8">
-        <f t="shared" si="254"/>
-        <v>41.556240631543879</v>
-      </c>
-      <c r="BW39" s="8">
-        <f t="shared" si="254"/>
-        <v>43.067207264420702</v>
-      </c>
-      <c r="BX39" s="8">
-        <f t="shared" si="254"/>
-        <v>44.06201251374403</v>
-      </c>
-      <c r="BY39" s="8">
-        <f t="shared" ref="BY39:CB39" si="255">BY37/BY38</f>
-        <v>45.078048479094143</v>
-      </c>
-      <c r="BZ39" s="8">
-        <f t="shared" si="255"/>
-        <v>46.115753120902035</v>
-      </c>
-      <c r="CA39" s="8">
-        <f t="shared" si="255"/>
-        <v>47.175573292268325</v>
-      </c>
-      <c r="CB39" s="8">
-        <f t="shared" si="255"/>
-        <v>48.257964918151437</v>
+        <v>47.292099722458715</v>
       </c>
     </row>
     <row r="41" spans="2:150">
@@ -9241,307 +9233,307 @@
         <v>0.28029290178043892</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" ref="D41:R41" si="256">D28/D26</f>
+        <f t="shared" ref="D41:R41" si="255">D28/D26</f>
         <v>0.28867223005651921</v>
       </c>
       <c r="E41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.27766661633509621</v>
+      </c>
+      <c r="F41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.30168818018600613</v>
+      </c>
+      <c r="G41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.31564953322168754</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.3174849131644345</v>
+      </c>
+      <c r="I41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.32285204252493205</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.3168230140470174</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.33482823086981423</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.31795701814440863</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.32467303859108176</v>
+      </c>
+      <c r="N41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.31478780891916075</v>
+      </c>
+      <c r="O41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.33</v>
+      </c>
+      <c r="P41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.33</v>
+      </c>
+      <c r="Q41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.33</v>
+      </c>
+      <c r="R41" s="10">
+        <f t="shared" si="255"/>
+        <v>0.33</v>
+      </c>
+      <c r="S41" s="10">
+        <f t="shared" ref="S41:AH41" si="256">S28/S26</f>
+        <v>0.37182500568655702</v>
+      </c>
+      <c r="T41" s="10">
         <f t="shared" si="256"/>
-        <v>0.27766661633509621</v>
-      </c>
-      <c r="F41" s="10">
+        <v>0.31717350103376984</v>
+      </c>
+      <c r="U41" s="10">
         <f t="shared" si="256"/>
-        <v>0.30168818018600613</v>
-      </c>
-      <c r="G41" s="10">
+        <v>0.33208038360637715</v>
+      </c>
+      <c r="V41" s="10">
         <f t="shared" si="256"/>
-        <v>0.31564953322168754</v>
-      </c>
-      <c r="H41" s="10">
+        <v>0.24481995255885089</v>
+      </c>
+      <c r="W41" s="10">
         <f t="shared" si="256"/>
-        <v>0.3174849131644345</v>
-      </c>
-      <c r="I41" s="10">
+        <v>0.4067602480472064</v>
+      </c>
+      <c r="X41" s="10">
         <f t="shared" si="256"/>
-        <v>0.32285204252493205</v>
-      </c>
-      <c r="J41" s="10">
+        <v>0.41403239268033593</v>
+      </c>
+      <c r="Y41" s="10">
         <f t="shared" si="256"/>
-        <v>0.3168230140470174</v>
-      </c>
-      <c r="K41" s="10">
+        <v>0.39677608211139082</v>
+      </c>
+      <c r="Z41" s="10">
         <f t="shared" si="256"/>
-        <v>0.33482823086981423</v>
-      </c>
-      <c r="L41" s="10">
+        <v>0.2667817442510263</v>
+      </c>
+      <c r="AA41" s="10">
         <f t="shared" si="256"/>
-        <v>0.31795701814440863</v>
-      </c>
-      <c r="M41" s="10">
+        <v>0.36505197965051983</v>
+      </c>
+      <c r="AB41" s="10">
         <f t="shared" si="256"/>
-        <v>0.32467303859108176</v>
-      </c>
-      <c r="N41" s="10">
+        <v>0.38945764777574654</v>
+      </c>
+      <c r="AC41" s="10">
         <f t="shared" si="256"/>
-        <v>0.31478780891916075</v>
-      </c>
-      <c r="O41" s="10">
+        <v>0.41026080335046639</v>
+      </c>
+      <c r="AD41" s="10">
         <f t="shared" si="256"/>
+        <v>0.36601426742271786</v>
+      </c>
+      <c r="AE41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.3759188626907074</v>
+      </c>
+      <c r="AF41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.40733571893298637</v>
+      </c>
+      <c r="AG41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.39866293532338304</v>
+      </c>
+      <c r="AH41" s="10">
+        <f t="shared" si="256"/>
+        <v>0.37311860325105356</v>
+      </c>
+      <c r="AI41" s="10">
+        <f t="shared" ref="AI41:AT41" si="257">AI28/AI26</f>
+        <v>0.46000837520938026</v>
+      </c>
+      <c r="AJ41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.45272276553433766</v>
+      </c>
+      <c r="AK41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.43788334335538182</v>
+      </c>
+      <c r="AL41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.3203533394731039</v>
+      </c>
+      <c r="AM41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.45541320318259237</v>
+      </c>
+      <c r="AN41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.41145029547935408</v>
+      </c>
+      <c r="AO41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.39579337841929951</v>
+      </c>
+      <c r="AP41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.31175099654869404</v>
+      </c>
+      <c r="AQ41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.41143172210990619</v>
+      </c>
+      <c r="AR41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.42917689592417524</v>
+      </c>
+      <c r="AS41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.42273786248639034</v>
+      </c>
+      <c r="AT41" s="10">
+        <f t="shared" si="257"/>
+        <v>0.39911466352685443</v>
+      </c>
+      <c r="AU41" s="10">
+        <f t="shared" ref="AU41:AX41" si="258">AU28/AU26</f>
+        <v>0.46884871510287707</v>
+      </c>
+      <c r="AV41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.45873651836431528</v>
+      </c>
+      <c r="AW41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.47887467301800574</v>
+      </c>
+      <c r="AX41" s="10">
+        <f t="shared" si="258"/>
+        <v>0.43713463133752994</v>
+      </c>
+      <c r="AY41" s="10">
+        <f t="shared" ref="AY41:BB41" si="259">AY28/AY26</f>
+        <v>0.50078726713965926</v>
+      </c>
+      <c r="AZ41" s="10">
+        <f t="shared" si="259"/>
+        <v>0.51934255180879485</v>
+      </c>
+      <c r="BA41" s="10">
+        <f t="shared" si="259"/>
+        <v>0.46445357636204093</v>
+      </c>
+      <c r="BB41" s="10">
+        <f t="shared" si="259"/>
+        <v>0.45</v>
+      </c>
+      <c r="BD41" s="10">
+        <f t="shared" ref="BD41:BW41" si="260">BD28/BD26</f>
+        <v>0.36344141520082063</v>
+      </c>
+      <c r="BE41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.27246859624712066</v>
+      </c>
+      <c r="BF41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.28742511821754951</v>
+      </c>
+      <c r="BG41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.31825712633087339</v>
+      </c>
+      <c r="BH41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.32274156646401203</v>
+      </c>
+      <c r="BI41" s="10">
+        <f t="shared" si="260"/>
         <v>0.33</v>
       </c>
-      <c r="P41" s="10">
-        <f t="shared" si="256"/>
-        <v>0.33</v>
-      </c>
-      <c r="Q41" s="10">
-        <f t="shared" si="256"/>
-        <v>0.33</v>
-      </c>
-      <c r="R41" s="10">
-        <f t="shared" si="256"/>
-        <v>0.33</v>
-      </c>
-      <c r="S41" s="10">
-        <f t="shared" ref="S41:AH41" si="257">S28/S26</f>
-        <v>0.37182500568655702</v>
-      </c>
-      <c r="T41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.31717350103376984</v>
-      </c>
-      <c r="U41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.33208038360637715</v>
-      </c>
-      <c r="V41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.24481995255885089</v>
-      </c>
-      <c r="W41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.4067602480472064</v>
-      </c>
-      <c r="X41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.41403239268033593</v>
-      </c>
-      <c r="Y41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.39677608211139082</v>
-      </c>
-      <c r="Z41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.2667817442510263</v>
-      </c>
-      <c r="AA41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.36505197965051983</v>
-      </c>
-      <c r="AB41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.38945764777574654</v>
-      </c>
-      <c r="AC41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.41026080335046639</v>
-      </c>
-      <c r="AD41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.36601426742271786</v>
-      </c>
-      <c r="AE41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.3759188626907074</v>
-      </c>
-      <c r="AF41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.40733571893298637</v>
-      </c>
-      <c r="AG41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.39866293532338304</v>
-      </c>
-      <c r="AH41" s="10">
-        <f t="shared" si="257"/>
-        <v>0.37311860325105356</v>
-      </c>
-      <c r="AI41" s="10">
-        <f t="shared" ref="AI41:AT41" si="258">AI28/AI26</f>
-        <v>0.46000837520938026</v>
-      </c>
-      <c r="AJ41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.45272276553433766</v>
-      </c>
-      <c r="AK41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.43788334335538182</v>
-      </c>
-      <c r="AL41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.3203533394731039</v>
-      </c>
-      <c r="AM41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.45541320318259237</v>
-      </c>
-      <c r="AN41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.41145029547935408</v>
-      </c>
-      <c r="AO41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.39579337841929951</v>
-      </c>
-      <c r="AP41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.31175099654869404</v>
-      </c>
-      <c r="AQ41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.41143172210990619</v>
-      </c>
-      <c r="AR41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.42917689592417524</v>
-      </c>
-      <c r="AS41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.42273786248639034</v>
-      </c>
-      <c r="AT41" s="10">
-        <f t="shared" si="258"/>
-        <v>0.39911466352685443</v>
-      </c>
-      <c r="AU41" s="10">
-        <f t="shared" ref="AU41:AX41" si="259">AU28/AU26</f>
-        <v>0.46884871510287707</v>
-      </c>
-      <c r="AV41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.45873651836431528</v>
-      </c>
-      <c r="AW41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.47887467301800574</v>
-      </c>
-      <c r="AX41" s="10">
-        <f t="shared" si="259"/>
-        <v>0.43713463133752994</v>
-      </c>
-      <c r="AY41" s="10">
-        <f t="shared" ref="AY41:BB41" si="260">AY28/AY26</f>
-        <v>0.50078726713965926</v>
-      </c>
-      <c r="AZ41" s="10">
+      <c r="BJ41" s="10">
         <f t="shared" si="260"/>
-        <v>0.51934255180879485</v>
-      </c>
-      <c r="BA41" s="10">
+        <v>0.31297981513657785</v>
+      </c>
+      <c r="BK41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.36893441507553748</v>
+      </c>
+      <c r="BL41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.38274287982534483</v>
+      </c>
+      <c r="BM41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.38875640204865552</v>
+      </c>
+      <c r="BN41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.4163798966954671</v>
+      </c>
+      <c r="BO41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.39370437379015416</v>
+      </c>
+      <c r="BP41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.4153774986433712</v>
+      </c>
+      <c r="BQ41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.46056373058057626</v>
+      </c>
+      <c r="BR41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.48295490667896929</v>
+      </c>
+      <c r="BS41" s="10">
+        <f t="shared" si="260"/>
+        <v>0.5</v>
+      </c>
+      <c r="BT41" s="10">
         <f t="shared" si="260"/>
         <v>0.51</v>
       </c>
-      <c r="BB41" s="10">
+      <c r="BU41" s="10">
         <f t="shared" si="260"/>
-        <v>0.47</v>
-      </c>
-      <c r="BD41" s="10">
-        <f t="shared" ref="BD41:BW41" si="261">BD28/BD26</f>
-        <v>0.36344141520082063</v>
-      </c>
-      <c r="BE41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.27246859624712066</v>
-      </c>
-      <c r="BF41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.28742511821754951</v>
-      </c>
-      <c r="BG41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.31825712633087339</v>
-      </c>
-      <c r="BH41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.32274156646401203</v>
-      </c>
-      <c r="BI41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.33</v>
-      </c>
-      <c r="BJ41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.31297981513657785</v>
-      </c>
-      <c r="BK41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.36893441507553748</v>
-      </c>
-      <c r="BL41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.38274287982534483</v>
-      </c>
-      <c r="BM41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.38875640204865552</v>
-      </c>
-      <c r="BN41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.4163798966954671</v>
-      </c>
-      <c r="BO41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.39370437379015416</v>
-      </c>
-      <c r="BP41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.4153774986433712</v>
-      </c>
-      <c r="BQ41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.46056373058057626</v>
-      </c>
-      <c r="BR41" s="10">
-        <f t="shared" si="261"/>
-        <v>0.49975874904589912</v>
-      </c>
-      <c r="BS41" s="10">
-        <f t="shared" si="261"/>
         <v>0.52</v>
       </c>
-      <c r="BT41" s="10">
-        <f t="shared" si="261"/>
+      <c r="BV41" s="10">
+        <f t="shared" si="260"/>
         <v>0.53</v>
       </c>
-      <c r="BU41" s="10">
-        <f t="shared" si="261"/>
+      <c r="BW41" s="10">
+        <f t="shared" si="260"/>
         <v>0.54</v>
       </c>
-      <c r="BV41" s="10">
+      <c r="BX41" s="10">
+        <f t="shared" ref="BX41:CB41" si="261">BX28/BX26</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BY41" s="10">
         <f t="shared" si="261"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="BW41" s="10">
+      <c r="BZ41" s="10">
         <f t="shared" si="261"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="BX41" s="10">
-        <f t="shared" ref="BX41:CB41" si="262">BX28/BX26</f>
+      <c r="CA41" s="10">
+        <f t="shared" si="261"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="BY41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="BZ41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="CA41" s="10">
-        <f t="shared" si="262"/>
-        <v>0.55000000000000004</v>
-      </c>
       <c r="CB41" s="10">
-        <f t="shared" si="262"/>
+        <f t="shared" si="261"/>
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -9554,308 +9546,308 @@
         <v>3.1077355485218686E-2</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" ref="D42:R42" si="263">D32/D26</f>
+        <f t="shared" ref="D42:R42" si="262">D32/D26</f>
         <v>5.3411722020026794E-2</v>
       </c>
       <c r="E42" s="10">
+        <f t="shared" si="262"/>
+        <v>5.1645616316108811E-2</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="262"/>
+        <v>7.0018634650238679E-2</v>
+      </c>
+      <c r="G42" s="10">
+        <f t="shared" si="262"/>
+        <v>7.6841071767411492E-2</v>
+      </c>
+      <c r="H42" s="10">
+        <f t="shared" si="262"/>
+        <v>9.6687051022562642E-2</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="262"/>
+        <v>7.8334392861805324E-2</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="262"/>
+        <v>4.3810044668114348E-2</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="262"/>
+        <v>6.1950418560715641E-2</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="262"/>
+        <v>4.5500865206536907E-2</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="262"/>
+        <v>4.2362463363352115E-2</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="262"/>
+        <v>3.2846989551552137E-2</v>
+      </c>
+      <c r="O42" s="10">
+        <f t="shared" si="262"/>
+        <v>5.000000000000001E-2</v>
+      </c>
+      <c r="P42" s="10">
+        <f t="shared" si="262"/>
+        <v>0.05</v>
+      </c>
+      <c r="Q42" s="10">
+        <f t="shared" si="262"/>
+        <v>5.0000000000000037E-2</v>
+      </c>
+      <c r="R42" s="10">
+        <f t="shared" si="262"/>
+        <v>0.05</v>
+      </c>
+      <c r="S42" s="10">
+        <f t="shared" ref="S42:AH42" si="263">S32/S26</f>
+        <v>9.7846690423838117E-2</v>
+      </c>
+      <c r="T42" s="10">
         <f t="shared" si="263"/>
-        <v>5.1645616316108811E-2</v>
-      </c>
-      <c r="F42" s="10">
+        <v>4.6060188375832804E-2</v>
+      </c>
+      <c r="U42" s="10">
         <f t="shared" si="263"/>
-        <v>7.0018634650238679E-2</v>
-      </c>
-      <c r="G42" s="10">
+        <v>6.9604395869555552E-2</v>
+      </c>
+      <c r="V42" s="10">
         <f t="shared" si="263"/>
-        <v>7.6841071767411492E-2</v>
-      </c>
-      <c r="H42" s="10">
+        <v>7.4404428490017396E-2</v>
+      </c>
+      <c r="W42" s="10">
         <f t="shared" si="263"/>
-        <v>9.6687051022562642E-2</v>
-      </c>
-      <c r="I42" s="10">
+        <v>0.12090518429034365</v>
+      </c>
+      <c r="X42" s="10">
         <f t="shared" si="263"/>
-        <v>7.8334392861805324E-2</v>
-      </c>
-      <c r="J42" s="10">
+        <v>0.11816980148290565</v>
+      </c>
+      <c r="Y42" s="10">
         <f t="shared" si="263"/>
-        <v>4.3810044668114348E-2</v>
-      </c>
-      <c r="K42" s="10">
+        <v>0.12013278718117143</v>
+      </c>
+      <c r="Z42" s="10">
         <f t="shared" si="263"/>
-        <v>6.1950418560715641E-2</v>
-      </c>
-      <c r="L42" s="10">
+        <v>5.156073336732684E-2</v>
+      </c>
+      <c r="AA42" s="10">
         <f t="shared" si="263"/>
-        <v>4.5500865206536907E-2</v>
-      </c>
-      <c r="M42" s="10">
+        <v>0.10152621101526216</v>
+      </c>
+      <c r="AB42" s="10">
         <f t="shared" si="263"/>
-        <v>4.2362463363352115E-2</v>
-      </c>
-      <c r="N42" s="10">
+        <v>0.14344911639244365</v>
+      </c>
+      <c r="AC42" s="10">
         <f t="shared" si="263"/>
-        <v>3.2846989551552137E-2</v>
-      </c>
-      <c r="O42" s="10">
+        <v>0.18814011041309728</v>
+      </c>
+      <c r="AD42" s="10">
         <f t="shared" si="263"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="P42" s="10">
+        <v>8.384854582037661E-2</v>
+      </c>
+      <c r="AE42" s="10">
         <f t="shared" si="263"/>
-        <v>0.05</v>
-      </c>
-      <c r="Q42" s="10">
+        <v>0.1661927877947296</v>
+      </c>
+      <c r="AF42" s="10">
         <f t="shared" si="263"/>
-        <v>5.0000000000000037E-2</v>
-      </c>
-      <c r="R42" s="10">
+        <v>0.22086857514638908</v>
+      </c>
+      <c r="AG42" s="10">
         <f t="shared" si="263"/>
-        <v>0.05</v>
-      </c>
-      <c r="S42" s="10">
-        <f t="shared" ref="S42:AH42" si="264">S32/S26</f>
-        <v>9.7846690423838117E-2</v>
-      </c>
-      <c r="T42" s="10">
+        <v>0.20385572139303479</v>
+      </c>
+      <c r="AH42" s="10">
+        <f t="shared" si="263"/>
+        <v>0.14358819987959059</v>
+      </c>
+      <c r="AI42" s="10">
+        <f t="shared" ref="AI42:AT42" si="264">AI32/AI26</f>
+        <v>0.27367392518146288</v>
+      </c>
+      <c r="AJ42" s="10">
         <f t="shared" si="264"/>
-        <v>4.6060188375832804E-2</v>
-      </c>
-      <c r="U42" s="10">
+        <v>0.25166852815385871</v>
+      </c>
+      <c r="AK42" s="10">
         <f t="shared" si="264"/>
-        <v>6.9604395869555552E-2</v>
-      </c>
-      <c r="V42" s="10">
+        <v>0.23455602325115246</v>
+      </c>
+      <c r="AL42" s="10">
         <f t="shared" si="264"/>
-        <v>7.4404428490017396E-2</v>
-      </c>
-      <c r="W42" s="10">
+        <v>8.1939994552034531E-2</v>
+      </c>
+      <c r="AM42" s="10">
         <f t="shared" si="264"/>
-        <v>0.12090518429034365</v>
-      </c>
-      <c r="X42" s="10">
+        <v>0.25060372658176366</v>
+      </c>
+      <c r="AN42" s="10">
         <f t="shared" si="264"/>
-        <v>0.11816980148290565</v>
-      </c>
-      <c r="Y42" s="10">
+        <v>0.19801508136660773</v>
+      </c>
+      <c r="AO42" s="10">
         <f t="shared" si="264"/>
-        <v>0.12013278718117143</v>
-      </c>
-      <c r="Z42" s="10">
+        <v>0.19342384172807112</v>
+      </c>
+      <c r="AP42" s="10">
         <f t="shared" si="264"/>
-        <v>5.156073336732684E-2</v>
-      </c>
-      <c r="AA42" s="10">
+        <v>7.0032220679818222E-2</v>
+      </c>
+      <c r="AQ42" s="10">
         <f t="shared" si="264"/>
-        <v>0.10152621101526216</v>
-      </c>
-      <c r="AB42" s="10">
+        <v>0.21004717270109657</v>
+      </c>
+      <c r="AR42" s="10">
         <f t="shared" si="264"/>
-        <v>0.14344911639244365</v>
-      </c>
-      <c r="AC42" s="10">
+        <v>0.22316270321107085</v>
+      </c>
+      <c r="AS42" s="10">
         <f t="shared" si="264"/>
-        <v>0.18814011041309728</v>
-      </c>
-      <c r="AD42" s="10">
+        <v>0.2243581488462485</v>
+      </c>
+      <c r="AT42" s="10">
         <f t="shared" si="264"/>
-        <v>8.384854582037661E-2</v>
-      </c>
-      <c r="AE42" s="10">
-        <f t="shared" si="264"/>
-        <v>0.1661927877947296</v>
-      </c>
-      <c r="AF42" s="10">
-        <f t="shared" si="264"/>
-        <v>0.22086857514638908</v>
-      </c>
-      <c r="AG42" s="10">
-        <f t="shared" si="264"/>
-        <v>0.20385572139303479</v>
-      </c>
-      <c r="AH42" s="10">
-        <f t="shared" si="264"/>
-        <v>0.14358819987959059</v>
-      </c>
-      <c r="AI42" s="10">
-        <f t="shared" ref="AI42:AT42" si="265">AI32/AI26</f>
-        <v>0.27367392518146288</v>
-      </c>
-      <c r="AJ42" s="10">
+        <v>0.16938003804003257</v>
+      </c>
+      <c r="AU42" s="10">
+        <f t="shared" ref="AU42:AX42" si="265">AU32/AU26</f>
+        <v>0.28093784683684786</v>
+      </c>
+      <c r="AV42" s="10">
         <f t="shared" si="265"/>
-        <v>0.25166852815385871</v>
-      </c>
-      <c r="AK42" s="10">
+        <v>0.27227935099850403</v>
+      </c>
+      <c r="AW42" s="10">
         <f t="shared" si="265"/>
-        <v>0.23455602325115246</v>
-      </c>
-      <c r="AL42" s="10">
+        <v>0.29613117957800245</v>
+      </c>
+      <c r="AX42" s="10">
         <f t="shared" si="265"/>
-        <v>8.1939994552034531E-2</v>
-      </c>
-      <c r="AM42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.25060372658176366</v>
-      </c>
-      <c r="AN42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.19801508136660773</v>
-      </c>
-      <c r="AO42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.19342384172807112</v>
-      </c>
-      <c r="AP42" s="10">
-        <f t="shared" si="265"/>
-        <v>7.0032220679818222E-2</v>
-      </c>
-      <c r="AQ42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.21004717270109657</v>
-      </c>
-      <c r="AR42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.22316270321107085</v>
-      </c>
-      <c r="AS42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.2243581488462485</v>
-      </c>
-      <c r="AT42" s="10">
-        <f t="shared" si="265"/>
-        <v>0.16938003804003257</v>
-      </c>
-      <c r="AU42" s="10">
-        <f t="shared" ref="AU42:AX42" si="266">AU32/AU26</f>
-        <v>0.28093784683684786</v>
-      </c>
-      <c r="AV42" s="10">
+        <v>0.22180256673010304</v>
+      </c>
+      <c r="AY42" s="10">
+        <f t="shared" ref="AY42:BB42" si="266">AY32/AY26</f>
+        <v>0.31746784535417527</v>
+      </c>
+      <c r="AZ42" s="10">
         <f t="shared" si="266"/>
-        <v>0.27227935099850403</v>
-      </c>
-      <c r="AW42" s="10">
+        <v>0.34070149469275762</v>
+      </c>
+      <c r="BA42" s="10">
         <f t="shared" si="266"/>
-        <v>0.29613117957800245</v>
-      </c>
-      <c r="AX42" s="10">
+        <v>0.28219942138780041</v>
+      </c>
+      <c r="BB42" s="10">
         <f t="shared" si="266"/>
-        <v>0.22180256673010304</v>
-      </c>
-      <c r="AY42" s="10">
-        <f t="shared" ref="AY42:BB42" si="267">AY32/AY26</f>
-        <v>0.31746784535417527</v>
-      </c>
-      <c r="AZ42" s="10">
+        <v>0.22920971272420554</v>
+      </c>
+      <c r="BD42" s="10">
+        <f t="shared" ref="BD42:BW42" si="267">BD32/BD26</f>
+        <v>0.11735339796796899</v>
+      </c>
+      <c r="BE42" s="10">
         <f t="shared" si="267"/>
-        <v>0.34070149469275762</v>
-      </c>
-      <c r="BA42" s="10">
+        <v>1.3850954289523567E-2</v>
+      </c>
+      <c r="BF42" s="10">
         <f t="shared" si="267"/>
-        <v>0.32645333222361445</v>
-      </c>
-      <c r="BB42" s="10">
+        <v>5.2198825848164897E-2</v>
+      </c>
+      <c r="BG42" s="10">
         <f t="shared" si="267"/>
-        <v>0.25485083756822885</v>
-      </c>
-      <c r="BD42" s="10">
-        <f t="shared" ref="BD42:BW42" si="268">BD32/BD26</f>
-        <v>0.11735339796796899</v>
-      </c>
-      <c r="BE42" s="10">
+        <v>7.3146805177289956E-2</v>
+      </c>
+      <c r="BH42" s="10">
+        <f t="shared" si="267"/>
+        <v>4.5109890669105875E-2</v>
+      </c>
+      <c r="BI42" s="10">
+        <f t="shared" si="267"/>
+        <v>5.0000000000000031E-2</v>
+      </c>
+      <c r="BJ42" s="10">
+        <f t="shared" si="267"/>
+        <v>7.1714541702031079E-2</v>
+      </c>
+      <c r="BK42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.10165511000233846</v>
+      </c>
+      <c r="BL42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.12910092289371833</v>
+      </c>
+      <c r="BM42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.18332666453265045</v>
+      </c>
+      <c r="BN42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.20860579286565689</v>
+      </c>
+      <c r="BO42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.17816520958008064</v>
+      </c>
+      <c r="BP42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.206204612241388</v>
+      </c>
+      <c r="BQ42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.26710665651305471</v>
+      </c>
+      <c r="BR42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.29143243937574065</v>
+      </c>
+      <c r="BS42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.31333939300029739</v>
+      </c>
+      <c r="BT42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.32371056569440521</v>
+      </c>
+      <c r="BU42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.33553993973160312</v>
+      </c>
+      <c r="BV42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.34699450412242649</v>
+      </c>
+      <c r="BW42" s="10">
+        <f t="shared" si="267"/>
+        <v>0.358091644859102</v>
+      </c>
+      <c r="BX42" s="10">
+        <f t="shared" ref="BX42:CB42" si="268">BX32/BX26</f>
+        <v>0.36809164485910201</v>
+      </c>
+      <c r="BY42" s="10">
         <f t="shared" si="268"/>
-        <v>1.3850954289523567E-2</v>
-      </c>
-      <c r="BF42" s="10">
+        <v>0.36844219498143937</v>
+      </c>
+      <c r="BZ42" s="10">
         <f t="shared" si="268"/>
-        <v>5.2198825848164897E-2</v>
-      </c>
-      <c r="BG42" s="10">
+        <v>0.36878930833787138</v>
+      </c>
+      <c r="CA42" s="10">
         <f t="shared" si="268"/>
-        <v>7.3146805177289956E-2</v>
-      </c>
-      <c r="BH42" s="10">
+        <v>0.36913301862218156</v>
+      </c>
+      <c r="CB42" s="10">
         <f t="shared" si="268"/>
-        <v>4.5109890669105875E-2</v>
-      </c>
-      <c r="BI42" s="10">
-        <f t="shared" si="268"/>
-        <v>5.0000000000000031E-2</v>
-      </c>
-      <c r="BJ42" s="10">
-        <f t="shared" si="268"/>
-        <v>7.1714541702031079E-2</v>
-      </c>
-      <c r="BK42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.10165511000233846</v>
-      </c>
-      <c r="BL42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.12910092289371833</v>
-      </c>
-      <c r="BM42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.18332666453265045</v>
-      </c>
-      <c r="BN42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.20860579286565689</v>
-      </c>
-      <c r="BO42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.17816520958008064</v>
-      </c>
-      <c r="BP42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.206204612241388</v>
-      </c>
-      <c r="BQ42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.26710665651305471</v>
-      </c>
-      <c r="BR42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.3092906611677817</v>
-      </c>
-      <c r="BS42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.33873121213942453</v>
-      </c>
-      <c r="BT42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.35153364983198732</v>
-      </c>
-      <c r="BU42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.36394114561274515</v>
-      </c>
-      <c r="BV42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.37598073896634615</v>
-      </c>
-      <c r="BW42" s="10">
-        <f t="shared" si="268"/>
-        <v>0.37800053044272786</v>
-      </c>
-      <c r="BX42" s="10">
-        <f t="shared" ref="BX42:CB42" si="269">BX32/BX26</f>
-        <v>0.37900052524230898</v>
-      </c>
-      <c r="BY42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.37999071617130592</v>
-      </c>
-      <c r="BZ42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.38097119934609702</v>
-      </c>
-      <c r="CA42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.38194206994074315</v>
-      </c>
-      <c r="CB42" s="10">
-        <f t="shared" si="269"/>
-        <v>0.38290342219622603</v>
+        <v>0.36947335919782215</v>
       </c>
     </row>
     <row r="43" spans="2:150" s="1" customFormat="1">
@@ -9867,307 +9859,307 @@
         <v>0.1162993512448228</v>
       </c>
       <c r="D43" s="9">
-        <f t="shared" ref="D43:R43" si="270">D29/D$26</f>
+        <f t="shared" ref="D43:R43" si="269">D29/D$26</f>
         <v>0.10717598740195179</v>
       </c>
       <c r="E43" s="9">
+        <f t="shared" si="269"/>
+        <v>9.7855423015753173E-2</v>
+      </c>
+      <c r="F43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.1089293159636837</v>
+      </c>
+      <c r="G43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.10794361654970637</v>
+      </c>
+      <c r="H43" s="9">
+        <f t="shared" si="269"/>
+        <v>9.0094277335167602E-2</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.10334233932534524</v>
+      </c>
+      <c r="J43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.13717731463271385</v>
+      </c>
+      <c r="K43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.12375145331374603</v>
+      </c>
+      <c r="L43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.11986424222378143</v>
+      </c>
+      <c r="M43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.11971202659986022</v>
+      </c>
+      <c r="N43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.12294517786931952</v>
+      </c>
+      <c r="O43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.12</v>
+      </c>
+      <c r="P43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.12</v>
+      </c>
+      <c r="R43" s="9">
+        <f t="shared" si="269"/>
+        <v>0.12</v>
+      </c>
+      <c r="S43" s="9">
+        <f t="shared" ref="S43:AH43" si="270">S29/S$26</f>
+        <v>0.10285086056562287</v>
+      </c>
+      <c r="T43" s="9">
         <f t="shared" si="270"/>
-        <v>9.7855423015753173E-2</v>
-      </c>
-      <c r="F43" s="9">
+        <v>9.845939581897542E-2</v>
+      </c>
+      <c r="U43" s="9">
         <f t="shared" si="270"/>
-        <v>0.1089293159636837</v>
-      </c>
-      <c r="G43" s="9">
+        <v>0.1047289915318651</v>
+      </c>
+      <c r="V43" s="9">
         <f t="shared" si="270"/>
-        <v>0.10794361654970637</v>
-      </c>
-      <c r="H43" s="9">
+        <v>0.17601689177670515</v>
+      </c>
+      <c r="W43" s="9">
         <f t="shared" si="270"/>
-        <v>9.0094277335167602E-2</v>
-      </c>
-      <c r="I43" s="9">
+        <v>0.12944787993979268</v>
+      </c>
+      <c r="X43" s="9">
         <f t="shared" si="270"/>
-        <v>0.10334233932534524</v>
-      </c>
-      <c r="J43" s="9">
+        <v>0.13505991665283143</v>
+      </c>
+      <c r="Y43" s="9">
         <f t="shared" si="270"/>
-        <v>0.13717731463271385</v>
-      </c>
-      <c r="K43" s="9">
+        <v>0.10885187226170524</v>
+      </c>
+      <c r="Z43" s="9">
         <f t="shared" si="270"/>
-        <v>0.12375145331374603</v>
-      </c>
-      <c r="L43" s="9">
+        <v>0.2215039641373806</v>
+      </c>
+      <c r="AA43" s="9">
         <f t="shared" si="270"/>
-        <v>0.11986424222378143</v>
-      </c>
-      <c r="M43" s="9">
+        <v>0.13638575536385755</v>
+      </c>
+      <c r="AB43" s="9">
         <f t="shared" si="270"/>
-        <v>0.11971202659986022</v>
-      </c>
-      <c r="N43" s="9">
+        <v>0.1225269144830388</v>
+      </c>
+      <c r="AC43" s="9">
         <f t="shared" si="270"/>
-        <v>0.12294517786931952</v>
-      </c>
-      <c r="O43" s="9">
+        <v>0.10542547115933751</v>
+      </c>
+      <c r="AD43" s="9">
         <f t="shared" si="270"/>
-        <v>0.12</v>
-      </c>
-      <c r="P43" s="9">
+        <v>0.16076458752515085</v>
+      </c>
+      <c r="AE43" s="9">
         <f t="shared" si="270"/>
-        <v>0.12</v>
-      </c>
-      <c r="Q43" s="9">
+        <v>8.7343966712898749E-2</v>
+      </c>
+      <c r="AF43" s="9">
         <f t="shared" si="270"/>
-        <v>0.12</v>
-      </c>
-      <c r="R43" s="9">
+        <v>7.065712426805465E-2</v>
+      </c>
+      <c r="AG43" s="9">
         <f t="shared" si="270"/>
-        <v>0.12</v>
-      </c>
-      <c r="S43" s="9">
-        <f t="shared" ref="S43:AH43" si="271">S29/S$26</f>
-        <v>0.10285086056562287</v>
-      </c>
-      <c r="T43" s="9">
+        <v>8.2027363184079605E-2</v>
+      </c>
+      <c r="AH43" s="9">
+        <f t="shared" si="270"/>
+        <v>0.11478025285972306</v>
+      </c>
+      <c r="AI43" s="9">
+        <f t="shared" ref="AI43:AT43" si="271">AI29/AI$26</f>
+        <v>7.1538246789503074E-2</v>
+      </c>
+      <c r="AJ43" s="9">
         <f t="shared" si="271"/>
-        <v>9.845939581897542E-2</v>
-      </c>
-      <c r="U43" s="9">
+        <v>8.2268653463728234E-2</v>
+      </c>
+      <c r="AK43" s="9">
         <f t="shared" si="271"/>
-        <v>0.1047289915318651</v>
-      </c>
-      <c r="V43" s="9">
+        <v>8.497360860559898E-2</v>
+      </c>
+      <c r="AL43" s="9">
         <f t="shared" si="271"/>
-        <v>0.17601689177670515</v>
-      </c>
-      <c r="W43" s="9">
+        <v>0.10282386208864619</v>
+      </c>
+      <c r="AM43" s="9">
         <f t="shared" si="271"/>
-        <v>0.12944787993979268</v>
-      </c>
-      <c r="X43" s="9">
+        <v>7.0667785149597095E-2</v>
+      </c>
+      <c r="AN43" s="9">
         <f t="shared" si="271"/>
-        <v>0.13505991665283143</v>
-      </c>
-      <c r="Y43" s="9">
+        <v>7.2144640594220891E-2</v>
+      </c>
+      <c r="AO43" s="9">
         <f t="shared" si="271"/>
-        <v>0.10885187226170524</v>
-      </c>
-      <c r="Z43" s="9">
+        <v>7.1666498435449685E-2</v>
+      </c>
+      <c r="AP43" s="9">
         <f t="shared" si="271"/>
-        <v>0.2215039641373806</v>
-      </c>
-      <c r="AA43" s="9">
+        <v>0.1059079736630965</v>
+      </c>
+      <c r="AQ43" s="9">
         <f t="shared" si="271"/>
-        <v>0.13638575536385755</v>
-      </c>
-      <c r="AB43" s="9">
+        <v>6.8051216075476317E-2</v>
+      </c>
+      <c r="AR43" s="9">
         <f t="shared" si="271"/>
-        <v>0.1225269144830388</v>
-      </c>
-      <c r="AC43" s="9">
+        <v>7.6606451455302732E-2</v>
+      </c>
+      <c r="AS43" s="9">
         <f t="shared" si="271"/>
-        <v>0.10542547115933751</v>
-      </c>
-      <c r="AD43" s="9">
+        <v>6.5408525235023468E-2</v>
+      </c>
+      <c r="AT43" s="9">
         <f t="shared" si="271"/>
-        <v>0.16076458752515085</v>
-      </c>
-      <c r="AE43" s="9">
-        <f t="shared" si="271"/>
-        <v>8.7343966712898749E-2</v>
-      </c>
-      <c r="AF43" s="9">
-        <f t="shared" si="271"/>
-        <v>7.065712426805465E-2</v>
-      </c>
-      <c r="AG43" s="9">
-        <f t="shared" si="271"/>
-        <v>8.2027363184079605E-2</v>
-      </c>
-      <c r="AH43" s="9">
-        <f t="shared" si="271"/>
-        <v>0.11478025285972306</v>
-      </c>
-      <c r="AI43" s="9">
-        <f t="shared" ref="AI43:AT43" si="272">AI29/AI$26</f>
-        <v>7.1538246789503074E-2</v>
-      </c>
-      <c r="AJ43" s="9">
+        <v>0.10377230323340278</v>
+      </c>
+      <c r="AU43" s="9">
+        <f t="shared" ref="AU43:AX43" si="272">AU29/AU$26</f>
+        <v>6.982626141893622E-2</v>
+      </c>
+      <c r="AV43" s="9">
         <f t="shared" si="272"/>
-        <v>8.2268653463728234E-2</v>
-      </c>
-      <c r="AK43" s="9">
+        <v>6.7379410626301095E-2</v>
+      </c>
+      <c r="AW43" s="9">
         <f t="shared" si="272"/>
-        <v>8.497360860559898E-2</v>
-      </c>
-      <c r="AL43" s="9">
+        <v>6.5437112583590334E-2</v>
+      </c>
+      <c r="AX43" s="9">
         <f t="shared" si="272"/>
-        <v>0.10282386208864619</v>
-      </c>
-      <c r="AM43" s="9">
-        <f t="shared" si="272"/>
-        <v>7.0667785149597095E-2</v>
-      </c>
-      <c r="AN43" s="9">
-        <f t="shared" si="272"/>
-        <v>7.2144640594220891E-2</v>
-      </c>
-      <c r="AO43" s="9">
-        <f t="shared" si="272"/>
-        <v>7.1666498435449685E-2</v>
-      </c>
-      <c r="AP43" s="9">
-        <f t="shared" si="272"/>
-        <v>0.1059079736630965</v>
-      </c>
-      <c r="AQ43" s="9">
-        <f t="shared" si="272"/>
-        <v>6.8051216075476317E-2</v>
-      </c>
-      <c r="AR43" s="9">
-        <f t="shared" si="272"/>
-        <v>7.6606451455302732E-2</v>
-      </c>
-      <c r="AS43" s="9">
-        <f t="shared" si="272"/>
-        <v>6.5408525235023468E-2</v>
-      </c>
-      <c r="AT43" s="9">
-        <f t="shared" si="272"/>
-        <v>0.10377230323340278</v>
-      </c>
-      <c r="AU43" s="9">
-        <f t="shared" ref="AU43:AX43" si="273">AU29/AU$26</f>
-        <v>6.982626141893622E-2</v>
-      </c>
-      <c r="AV43" s="9">
+        <v>9.5271556141121358E-2</v>
+      </c>
+      <c r="AY43" s="9">
+        <f t="shared" ref="AY43:BB43" si="273">AY29/AY$26</f>
+        <v>6.5295746860416587E-2</v>
+      </c>
+      <c r="AZ43" s="9">
         <f t="shared" si="273"/>
-        <v>6.7379410626301095E-2</v>
-      </c>
-      <c r="AW43" s="9">
+        <v>6.4381904830673686E-2</v>
+      </c>
+      <c r="BA43" s="9">
         <f t="shared" si="273"/>
-        <v>6.5437112583590334E-2</v>
-      </c>
-      <c r="AX43" s="9">
+        <v>6.8312728599602093E-2</v>
+      </c>
+      <c r="BB43" s="9">
         <f t="shared" si="273"/>
-        <v>9.5271556141121358E-2</v>
-      </c>
-      <c r="AY43" s="9">
-        <f t="shared" ref="AY43:BB43" si="274">AY29/AY$26</f>
-        <v>6.5295746860416587E-2</v>
-      </c>
-      <c r="AZ43" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="BD43" s="9">
+        <f t="shared" ref="BD43:BW43" si="274">BD29/BD$26</f>
+        <v>0.12564466386671314</v>
+      </c>
+      <c r="BE43" s="9">
         <f t="shared" si="274"/>
-        <v>6.4381904830673686E-2</v>
-      </c>
-      <c r="BA43" s="9">
+        <v>0.13430067254373584</v>
+      </c>
+      <c r="BF43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.10742606916989633</v>
+      </c>
+      <c r="BG43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.11030407713034202</v>
+      </c>
+      <c r="BH43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.12155581722634566</v>
+      </c>
+      <c r="BI43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="BJ43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.12283917484368646</v>
+      </c>
+      <c r="BK43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.15001855063742303</v>
+      </c>
+      <c r="BL43" s="9">
+        <f t="shared" si="274"/>
+        <v>0.13161159075121565</v>
+      </c>
+      <c r="BM43" s="9">
+        <f t="shared" si="274"/>
+        <v>8.9164532650448144E-2</v>
+      </c>
+      <c r="BN43" s="9">
+        <f t="shared" si="274"/>
+        <v>8.5697642313105685E-2</v>
+      </c>
+      <c r="BO43" s="9">
+        <f t="shared" si="274"/>
+        <v>8.0042763698933442E-2</v>
+      </c>
+      <c r="BP43" s="9">
+        <f t="shared" si="274"/>
+        <v>7.8814943970489243E-2</v>
+      </c>
+      <c r="BQ43" s="9">
+        <f t="shared" si="274"/>
+        <v>7.4805966016168873E-2</v>
+      </c>
+      <c r="BR43" s="9">
+        <f t="shared" si="274"/>
+        <v>7.4775367318875963E-2</v>
+      </c>
+      <c r="BS43" s="9">
         <f t="shared" si="274"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BB43" s="9">
+      <c r="BT43" s="9">
         <f t="shared" si="274"/>
-        <v>0.1</v>
-      </c>
-      <c r="BD43" s="9">
-        <f t="shared" ref="BD43:BW43" si="275">BD29/BD$26</f>
-        <v>0.12564466386671314</v>
-      </c>
-      <c r="BE43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.13430067254373584</v>
-      </c>
-      <c r="BF43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.10742606916989633</v>
-      </c>
-      <c r="BG43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.11030407713034202</v>
-      </c>
-      <c r="BH43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.12155581722634566</v>
-      </c>
-      <c r="BI43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="BJ43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.12283917484368646</v>
-      </c>
-      <c r="BK43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.15001855063742303</v>
-      </c>
-      <c r="BL43" s="9">
-        <f t="shared" si="275"/>
-        <v>0.13161159075121565</v>
-      </c>
-      <c r="BM43" s="9">
-        <f t="shared" si="275"/>
-        <v>8.9164532650448144E-2</v>
-      </c>
-      <c r="BN43" s="9">
-        <f t="shared" si="275"/>
-        <v>8.5697642313105685E-2</v>
-      </c>
-      <c r="BO43" s="9">
-        <f t="shared" si="275"/>
-        <v>8.0042763698933442E-2</v>
-      </c>
-      <c r="BP43" s="9">
-        <f t="shared" si="275"/>
-        <v>7.8814943970489243E-2</v>
-      </c>
-      <c r="BQ43" s="9">
-        <f t="shared" si="275"/>
-        <v>7.4805966016168873E-2</v>
-      </c>
-      <c r="BR43" s="9">
-        <f t="shared" si="275"/>
-        <v>7.5258878898866732E-2</v>
-      </c>
-      <c r="BS43" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BU43" s="9">
+        <f t="shared" si="274"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BV43" s="9">
+        <f t="shared" si="274"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BW43" s="9">
+        <f t="shared" si="274"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BX43" s="9">
+        <f t="shared" ref="BX43:CB43" si="275">BX29/BX$26</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BY43" s="9">
         <f t="shared" si="275"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BT43" s="9">
+      <c r="BZ43" s="9">
         <f t="shared" si="275"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BU43" s="9">
+      <c r="CA43" s="9">
         <f t="shared" si="275"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BV43" s="9">
+      <c r="CB43" s="9">
         <f t="shared" si="275"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BW43" s="9">
-        <f t="shared" si="275"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BX43" s="9">
-        <f t="shared" ref="BX43:CB43" si="276">BX29/BX$26</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BY43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BZ43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="CA43" s="9">
-        <f t="shared" si="276"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="CB43" s="9">
-        <f t="shared" si="276"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -10184,192 +10176,192 @@
         <v>0.19934764881761358</v>
       </c>
       <c r="H44" s="9">
-        <f t="shared" ref="H44:AL44" si="277">H30/D30-1</f>
+        <f t="shared" ref="H44:AL44" si="276">H30/D30-1</f>
         <v>0.23684040976741194</v>
       </c>
       <c r="I44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.2659933012350848</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.28277352030001635</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.29730758770737009</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.34622597280825129</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.42007225947268778</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.43681082970542451</v>
       </c>
       <c r="O44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.32458457367266225</v>
       </c>
       <c r="P44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.24590322518234764</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.16067581886563964</v>
       </c>
       <c r="R44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.19134689815326755</v>
       </c>
       <c r="S44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.35632741775517518</v>
       </c>
       <c r="T44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.38256958139871955</v>
       </c>
       <c r="U44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.28009630818619558</v>
       </c>
       <c r="V44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>-0.19105941977193741</v>
       </c>
       <c r="W44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.16958381952547641</v>
       </c>
       <c r="X44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.18757019842755507</v>
       </c>
       <c r="Y44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.2813479623824453</v>
       </c>
       <c r="Z44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.58864027538726327</v>
       </c>
       <c r="AA44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.23977386099102094</v>
       </c>
       <c r="AB44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.20807061790668357</v>
       </c>
       <c r="AC44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.16146788990825689</v>
       </c>
       <c r="AD44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.47778981581798519</v>
       </c>
       <c r="AE44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.21727467811158796</v>
       </c>
       <c r="AF44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.1351774530271399</v>
       </c>
       <c r="AG44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.19483938915218535</v>
       </c>
       <c r="AH44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.18988269794721413</v>
       </c>
       <c r="AI44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.15733803437637728</v>
       </c>
       <c r="AJ44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.23517241379310327</v>
       </c>
       <c r="AK44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.24261789334508577</v>
       </c>
       <c r="AL44" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v>0.32984185664407484</v>
       </c>
       <c r="AM44" s="9">
-        <f t="shared" ref="AM44:AM45" si="278">AM30/AI30-1</f>
+        <f t="shared" ref="AM44:AM45" si="277">AM30/AI30-1</f>
         <v>0.25190403655750182</v>
       </c>
       <c r="AN44" s="9">
-        <f t="shared" ref="AN44:AN45" si="279">AN30/AJ30-1</f>
+        <f t="shared" ref="AN44:AN45" si="278">AN30/AJ30-1</f>
         <v>0.3340777963893542</v>
       </c>
       <c r="AO44" s="9">
-        <f t="shared" ref="AO44:AO45" si="280">AO30/AK30-1</f>
+        <f t="shared" ref="AO44:AO45" si="279">AO30/AK30-1</f>
         <v>0.17520837027841818</v>
       </c>
       <c r="AP44" s="9">
-        <f t="shared" ref="AP44:AP45" si="281">AP30/AL30-1</f>
+        <f t="shared" ref="AP44:AP45" si="280">AP30/AL30-1</f>
         <v>4.0772200772200673E-2</v>
       </c>
       <c r="AQ44" s="9">
-        <f t="shared" ref="AQ44:AQ45" si="282">AQ30/AM30-1</f>
+        <f t="shared" ref="AQ44:AQ45" si="281">AQ30/AM30-1</f>
         <v>4.5323193916349647E-2</v>
       </c>
       <c r="AR44" s="9">
-        <f t="shared" ref="AR44:AR45" si="283">AR30/AN30-1</f>
+        <f t="shared" ref="AR44:AR45" si="282">AR30/AN30-1</f>
         <v>-8.2031249999999889E-2</v>
       </c>
       <c r="AS44" s="9">
-        <f t="shared" ref="AS44:AS45" si="284">AS30/AO30-1</f>
+        <f t="shared" ref="AS44:AS45" si="283">AS30/AO30-1</f>
         <v>-8.2993813188471099E-3</v>
       </c>
       <c r="AT44" s="9">
-        <f t="shared" ref="AT44:AT45" si="285">AT30/AP30-1</f>
+        <f t="shared" ref="AT44:AT45" si="284">AT30/AP30-1</f>
         <v>-8.9033981302866216E-4</v>
       </c>
       <c r="AU44" s="9">
-        <f t="shared" ref="AU44:AU45" si="286">AU30/AQ30-1</f>
+        <f t="shared" ref="AU44:AU45" si="285">AU30/AQ30-1</f>
         <v>2.2115524516223006E-2</v>
       </c>
       <c r="AV44" s="9">
-        <f t="shared" ref="AV44:AV45" si="287">AV30/AR30-1</f>
+        <f t="shared" ref="AV44:AV45" si="286">AV30/AR30-1</f>
         <v>8.1003039513677821E-2</v>
       </c>
       <c r="AW44" s="9">
-        <f t="shared" ref="AW44:AW45" si="288">AW30/AS30-1</f>
+        <f t="shared" ref="AW44:AW45" si="287">AW30/AS30-1</f>
         <v>0.11853317102860617</v>
       </c>
       <c r="AX44" s="9">
-        <f t="shared" ref="AX44:AX45" si="289">AX30/AT30-1</f>
+        <f t="shared" ref="AX44:AX45" si="288">AX30/AT30-1</f>
         <v>0.15327491459973275</v>
       </c>
       <c r="AY44" s="9">
-        <f t="shared" ref="AY44:AY45" si="290">AY30/AU30-1</f>
+        <f t="shared" ref="AY44:AY45" si="289">AY30/AU30-1</f>
         <v>0.17124555160142352</v>
       </c>
       <c r="AZ44" s="9">
-        <f t="shared" ref="AZ44:AZ45" si="291">AZ30/AV30-1</f>
+        <f t="shared" ref="AZ44:AZ45" si="290">AZ30/AV30-1</f>
         <v>0.15942640236187278</v>
       </c>
       <c r="BA44" s="9">
-        <f t="shared" ref="BA44:BA45" si="292">BA30/AW30-1</f>
-        <v>0.12999999999999989</v>
+        <f t="shared" ref="BA44:BA45" si="291">BA30/AW30-1</f>
+        <v>0.16120255747517342</v>
       </c>
       <c r="BB44" s="9">
-        <f t="shared" ref="BB44:BB45" si="293">BB30/AX30-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="BB44:BB45" si="292">BB30/AX30-1</f>
+        <v>0.15999999999999992</v>
       </c>
       <c r="BD44" s="9"/>
       <c r="BE44" s="9">
@@ -10377,96 +10369,96 @@
         <v>0.27013932587739764</v>
       </c>
       <c r="BF44" s="9">
-        <f t="shared" ref="BF44:BW44" si="294">BF30/BE30-1</f>
+        <f t="shared" ref="BF44:BW44" si="293">BF30/BE30-1</f>
         <v>0.15124556241793519</v>
       </c>
       <c r="BG44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.24698958996116382</v>
       </c>
       <c r="BH44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.37785319729590672</v>
       </c>
       <c r="BI44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.22554929477910646</v>
       </c>
       <c r="BJ44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.19575111525701705</v>
       </c>
       <c r="BK44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.28111565481807688</v>
       </c>
       <c r="BL44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.2645277459486004</v>
       </c>
       <c r="BM44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.18414239482200645</v>
       </c>
       <c r="BN44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.24290789833287785</v>
       </c>
       <c r="BO44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>0.19218083468930036</v>
       </c>
       <c r="BP44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>-1.2947729536316288E-2</v>
       </c>
       <c r="BQ44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v>9.3280514238732293E-2</v>
       </c>
       <c r="BR44" s="9">
-        <f t="shared" si="294"/>
-        <v>0.13909653380734266</v>
+        <f t="shared" si="293"/>
+        <v>0.16286319819511852</v>
       </c>
       <c r="BS44" s="9">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="BT44" s="9">
+        <f t="shared" si="293"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="BT44" s="9">
-        <f t="shared" si="294"/>
+      <c r="BU44" s="9">
+        <f t="shared" si="293"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BU44" s="9">
-        <f t="shared" si="294"/>
+      <c r="BV44" s="9">
+        <f t="shared" si="293"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BV44" s="9">
-        <f t="shared" si="294"/>
+      <c r="BW44" s="9">
+        <f t="shared" si="293"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BW44" s="9">
-        <f t="shared" si="294"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BX44" s="9">
-        <f t="shared" ref="BX44" si="295">BX30/BW30-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BX44" si="294">BX30/BW30-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BY44" s="9">
-        <f t="shared" ref="BY44:BY45" si="296">BY30/BX30-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BY44:BY45" si="295">BY30/BX30-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BZ44" s="9">
-        <f t="shared" ref="BZ44:BZ45" si="297">BZ30/BY30-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BZ44:BZ45" si="296">BZ30/BY30-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="CA44" s="9">
-        <f t="shared" ref="CA44:CA45" si="298">CA30/BZ30-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="CA44:CA45" si="297">CA30/BZ30-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="CB44" s="9">
-        <f t="shared" ref="CB44:CB45" si="299">CB30/CA30-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="CB44:CB45" si="298">CB30/CA30-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="45" spans="2:150" s="1" customFormat="1">
@@ -10478,292 +10470,292 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9">
-        <f t="shared" ref="G45:AL45" si="300">G31/C31-1</f>
+        <f t="shared" ref="G45:AL45" si="299">G31/C31-1</f>
         <v>0.26682681412319265</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.3688075905483077</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.68842916188786218</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.64360364267129233</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.63665474060822902</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.5980604525610691</v>
       </c>
       <c r="M45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.42125499846201153</v>
       </c>
       <c r="N45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.43849188026859109</v>
       </c>
       <c r="O45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.24313961241242099</v>
       </c>
       <c r="P45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.20862719746418357</v>
       </c>
       <c r="Q45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>7.8671139487068498E-2</v>
       </c>
       <c r="R45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.1856000440197354</v>
       </c>
       <c r="S45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.70837817496324762</v>
       </c>
       <c r="T45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.84532405753891249</v>
       </c>
       <c r="U45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.80159844836811156</v>
       </c>
       <c r="V45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>-2.4905608128700303</v>
       </c>
       <c r="W45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.43232115285640749</v>
       </c>
       <c r="X45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.45488546049555856</v>
       </c>
       <c r="Y45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.59628770301624123</v>
       </c>
       <c r="Z45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.57343020238713027</v>
       </c>
       <c r="AA45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>-0.27416457060725841</v>
       </c>
       <c r="AB45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>-0.27795629820051415</v>
       </c>
       <c r="AC45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>-0.32209302325581401</v>
       </c>
       <c r="AD45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>-1.8393799472295516</v>
       </c>
       <c r="AE45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.24801980198019802</v>
       </c>
       <c r="AF45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.23275478415665329</v>
       </c>
       <c r="AG45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.1646655231560894</v>
       </c>
       <c r="AH45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>8.2514734774066456E-2</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.17889726299087672</v>
       </c>
       <c r="AJ45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.20866425992779791</v>
       </c>
       <c r="AK45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.18483063328424154</v>
       </c>
       <c r="AL45" s="9">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v>0.44392014519056255</v>
       </c>
       <c r="AM45" s="9">
+        <f t="shared" si="277"/>
+        <v>0.338829071332436</v>
+      </c>
+      <c r="AN45" s="9">
         <f t="shared" si="278"/>
-        <v>0.338829071332436</v>
-      </c>
-      <c r="AN45" s="9">
+        <v>0.22252090800477897</v>
+      </c>
+      <c r="AO45" s="9">
         <f t="shared" si="279"/>
-        <v>0.22252090800477897</v>
-      </c>
-      <c r="AO45" s="9">
+        <v>0.15972653822249838</v>
+      </c>
+      <c r="AP45" s="9">
         <f t="shared" si="280"/>
-        <v>0.15972653822249838</v>
-      </c>
-      <c r="AP45" s="9">
+        <v>-1.3323278029160446E-2</v>
+      </c>
+      <c r="AQ45" s="9">
         <f t="shared" si="281"/>
-        <v>-1.3323278029160446E-2</v>
-      </c>
-      <c r="AQ45" s="9">
+        <v>7.5395828097510886E-3</v>
+      </c>
+      <c r="AR45" s="9">
         <f t="shared" si="282"/>
-        <v>7.5395828097510886E-3</v>
-      </c>
-      <c r="AR45" s="9">
+        <v>-1.9056926459809498E-2</v>
+      </c>
+      <c r="AS45" s="9">
         <f t="shared" si="283"/>
-        <v>-1.9056926459809498E-2</v>
-      </c>
-      <c r="AS45" s="9">
+        <v>0.282422293676313</v>
+      </c>
+      <c r="AT45" s="9">
         <f t="shared" si="284"/>
-        <v>0.282422293676313</v>
-      </c>
-      <c r="AT45" s="9">
+        <v>0.11923566878980885</v>
+      </c>
+      <c r="AU45" s="9">
         <f t="shared" si="285"/>
-        <v>0.11923566878980885</v>
-      </c>
-      <c r="AU45" s="9">
+        <v>7.7326016462959668E-3</v>
+      </c>
+      <c r="AV45" s="9">
         <f t="shared" si="286"/>
-        <v>7.7326016462959668E-3</v>
-      </c>
-      <c r="AV45" s="9">
+        <v>6.3511830635118338E-2</v>
+      </c>
+      <c r="AW45" s="9">
         <f t="shared" si="287"/>
-        <v>6.3511830635118338E-2</v>
-      </c>
-      <c r="AW45" s="9">
+        <v>-0.1278729628081906</v>
+      </c>
+      <c r="AX45" s="9">
         <f t="shared" si="288"/>
-        <v>-0.1278729628081906</v>
-      </c>
-      <c r="AX45" s="9">
+        <v>3.2779421807420883E-2</v>
+      </c>
+      <c r="AY45" s="9">
         <f t="shared" si="289"/>
-        <v>3.2779421807420883E-2</v>
-      </c>
-      <c r="AY45" s="9">
+        <v>4.3316831683168244E-2</v>
+      </c>
+      <c r="AZ45" s="9">
         <f t="shared" si="290"/>
-        <v>4.3316831683168244E-2</v>
-      </c>
-      <c r="AZ45" s="9">
+        <v>3.3255269320842995E-2</v>
+      </c>
+      <c r="BA45" s="9">
         <f t="shared" si="291"/>
-        <v>3.3255269320842995E-2</v>
-      </c>
-      <c r="BA45" s="9">
+        <v>9.7029228557738323E-2</v>
+      </c>
+      <c r="BB45" s="9">
         <f t="shared" si="292"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="BB45" s="9">
-        <f t="shared" si="293"/>
-        <v>3.0000000000000027E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="BD45" s="9"/>
       <c r="BE45" s="9">
-        <f t="shared" ref="BE45:BW45" si="301">BE31/BD31-1</f>
+        <f t="shared" ref="BE45:BW45" si="300">BE31/BD31-1</f>
         <v>-5.7114946784625475E-2</v>
       </c>
       <c r="BF45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.50643762480469889</v>
       </c>
       <c r="BG45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.49605936739119594</v>
       </c>
       <c r="BH45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.51007447885193602</v>
       </c>
       <c r="BI45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.17483508417028948</v>
       </c>
       <c r="BJ45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-9.9352118633088016E-2</v>
       </c>
       <c r="BK45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.46241299303944294</v>
       </c>
       <c r="BL45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.45073774393146149</v>
       </c>
       <c r="BM45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.17694663167104108</v>
       </c>
       <c r="BN45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.25590039026203293</v>
       </c>
       <c r="BO45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.16373187333530637</v>
       </c>
       <c r="BP45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>9.3712251255642309E-2</v>
       </c>
       <c r="BQ45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>-1.0579550078474553E-2</v>
       </c>
       <c r="BR45" s="9">
-        <f t="shared" si="301"/>
-        <v>3.3977439633394058E-2</v>
+        <f t="shared" si="300"/>
+        <v>6.1076904999706194E-2</v>
       </c>
       <c r="BS45" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BT45" s="9">
+        <f t="shared" si="300"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BU45" s="9">
+        <f t="shared" si="300"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BT45" s="9">
-        <f t="shared" si="301"/>
+      <c r="BV45" s="9">
+        <f t="shared" si="300"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BU45" s="9">
-        <f t="shared" si="301"/>
+      <c r="BW45" s="9">
+        <f t="shared" si="300"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BV45" s="9">
-        <f t="shared" si="301"/>
+      <c r="BX45" s="9">
+        <f t="shared" ref="BX45" si="301">BX31/BW31-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BW45" s="9">
-        <f t="shared" si="301"/>
+      <c r="BY45" s="9">
+        <f t="shared" si="295"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BX45" s="9">
-        <f t="shared" ref="BX45" si="302">BX31/BW31-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BY45" s="9">
+      <c r="BZ45" s="9">
         <f t="shared" si="296"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BZ45" s="9">
+      <c r="CA45" s="9">
         <f t="shared" si="297"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="CA45" s="9">
+      <c r="CB45" s="9">
         <f t="shared" si="298"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="CB45" s="9">
-        <f t="shared" si="299"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -10780,195 +10772,195 @@
         <v>65</v>
       </c>
       <c r="G47" s="10">
-        <f t="shared" ref="G47:R47" si="303">G26/C26-1</f>
+        <f t="shared" ref="G47:R47" si="302">G26/C26-1</f>
         <v>0.24036852966079758</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.25345249361307398</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.27435196596018629</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.2633510036333313</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.2385974526194623</v>
       </c>
       <c r="L47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.22701090042054384</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.23337273454838536</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.22805860736781414</v>
       </c>
       <c r="O47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.20496157657763581</v>
       </c>
       <c r="P47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.17463187681112702</v>
       </c>
       <c r="Q47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.14683134342524973</v>
       </c>
       <c r="R47" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.18172050854122612</v>
       </c>
       <c r="S47" s="10">
-        <f t="shared" ref="S47" si="304">S26/O26-1</f>
+        <f t="shared" ref="S47" si="303">S26/O26-1</f>
         <v>0.39156766338179749</v>
       </c>
       <c r="T47" s="10">
-        <f t="shared" ref="T47" si="305">T26/P26-1</f>
+        <f t="shared" ref="T47" si="304">T26/P26-1</f>
         <v>0.44205475410345207</v>
       </c>
       <c r="U47" s="10">
-        <f t="shared" ref="U47" si="306">U26/Q26-1</f>
+        <f t="shared" ref="U47" si="305">U26/Q26-1</f>
         <v>0.49673555377207057</v>
       </c>
       <c r="V47" s="10">
-        <f t="shared" ref="V47" si="307">V26/R26-1</f>
+        <f t="shared" ref="V47" si="306">V26/R26-1</f>
         <v>0.52455457216186252</v>
       </c>
       <c r="W47" s="10">
-        <f t="shared" ref="W47" si="308">W26/S26-1</f>
+        <f t="shared" ref="W47" si="307">W26/S26-1</f>
         <v>0.40339525362044126</v>
       </c>
       <c r="X47" s="10">
-        <f t="shared" ref="X47" si="309">X26/T26-1</f>
+        <f t="shared" ref="X47" si="308">X26/T26-1</f>
         <v>0.40273058810016082</v>
       </c>
       <c r="Y47" s="10">
-        <f t="shared" ref="Y47" si="310">Y26/U26-1</f>
+        <f t="shared" ref="Y47" si="309">Y26/U26-1</f>
         <v>0.34020015469728815</v>
       </c>
       <c r="Z47" s="10">
-        <f t="shared" ref="Z47" si="311">Z26/V26-1</f>
+        <f t="shared" ref="Z47" si="310">Z26/V26-1</f>
         <v>0.27428972222086934</v>
       </c>
       <c r="AA47" s="10">
-        <f t="shared" ref="AA47" si="312">AA26/W26-1</f>
+        <f t="shared" ref="AA47" si="311">AA26/W26-1</f>
         <v>0.22127267363898739</v>
       </c>
       <c r="AB47" s="10">
-        <f t="shared" ref="AB47" si="313">AB26/X26-1</f>
+        <f t="shared" ref="AB47" si="312">AB26/X26-1</f>
         <v>0.25975742645299182</v>
       </c>
       <c r="AC47" s="10">
-        <f t="shared" ref="AC47" si="314">AC26/Y26-1</f>
+        <f t="shared" ref="AC47" si="313">AC26/Y26-1</f>
         <v>0.31357428208301785</v>
       </c>
       <c r="AD47" s="10">
-        <f t="shared" ref="AD47" si="315">AD26/Z26-1</f>
+        <f t="shared" ref="AD47" si="314">AD26/Z26-1</f>
         <v>0.30604203185834744</v>
       </c>
       <c r="AE47" s="10">
-        <f t="shared" ref="AE47" si="316">AE26/AA26-1</f>
+        <f t="shared" ref="AE47" si="315">AE26/AA26-1</f>
         <v>0.27582393275823924</v>
       </c>
       <c r="AF47" s="10">
-        <f t="shared" ref="AF47" si="317">AF26/AB26-1</f>
+        <f t="shared" ref="AF47" si="316">AF26/AB26-1</f>
         <v>0.24883201300020308</v>
       </c>
       <c r="AG47" s="10">
-        <f t="shared" ref="AG47" si="318">AG26/AC26-1</f>
+        <f t="shared" ref="AG47" si="317">AG26/AC26-1</f>
         <v>0.22444317532838376</v>
       </c>
       <c r="AH47" s="10">
-        <f t="shared" ref="AH47" si="319">AH26/AD26-1</f>
+        <f t="shared" ref="AH47" si="318">AH26/AD26-1</f>
         <v>0.21529175050301808</v>
       </c>
       <c r="AI47" s="10">
-        <f t="shared" ref="AI47" si="320">AI26/AE26-1</f>
+        <f t="shared" ref="AI47" si="319">AI26/AE26-1</f>
         <v>0.24202496532593609</v>
       </c>
       <c r="AJ47" s="10">
-        <f t="shared" ref="AJ47" si="321">AJ26/AF26-1</f>
+        <f t="shared" ref="AJ47" si="320">AJ26/AF26-1</f>
         <v>0.19417696811971386</v>
       </c>
       <c r="AK47" s="10">
-        <f t="shared" ref="AK47" si="322">AK26/AG26-1</f>
+        <f t="shared" ref="AK47" si="321">AK26/AG26-1</f>
         <v>0.16347947761194037</v>
       </c>
       <c r="AL47" s="10">
-        <f t="shared" ref="AL47" si="323">AL26/AH26-1</f>
+        <f t="shared" ref="AL47" si="322">AL26/AH26-1</f>
         <v>0.16034015653220957</v>
       </c>
       <c r="AM47" s="10">
-        <f t="shared" ref="AM47" si="324">AM26/AI26-1</f>
+        <f t="shared" ref="AM47" si="323">AM26/AI26-1</f>
         <v>9.8241206030150741E-2</v>
       </c>
       <c r="AN47" s="10">
-        <f t="shared" ref="AN47" si="325">AN26/AJ26-1</f>
+        <f t="shared" ref="AN47" si="324">AN26/AJ26-1</f>
         <v>8.5578468495464355E-2</v>
       </c>
       <c r="AO47" s="10">
-        <f t="shared" ref="AO47" si="326">AO26/AK26-1</f>
+        <f t="shared" ref="AO47" si="325">AO26/AK26-1</f>
         <v>5.9076635264248001E-2</v>
       </c>
       <c r="AP47" s="10">
-        <f t="shared" ref="AP47" si="327">AP26/AL26-1</f>
+        <f t="shared" ref="AP47" si="326">AP26/AL26-1</f>
         <v>1.8523082510733868E-2</v>
       </c>
       <c r="AQ47" s="10">
-        <f t="shared" ref="AQ47" si="328">AQ26/AM26-1</f>
+        <f t="shared" ref="AQ47" si="327">AQ26/AM26-1</f>
         <v>3.7329367802943603E-2</v>
       </c>
       <c r="AR47" s="10">
-        <f t="shared" ref="AR47" si="329">AR26/AN26-1</f>
+        <f t="shared" ref="AR47" si="328">AR26/AN26-1</f>
         <v>2.7251853803590853E-2</v>
       </c>
       <c r="AS47" s="10">
-        <f t="shared" ref="AS47" si="330">AS26/AO26-1</f>
+        <f t="shared" ref="AS47" si="329">AS26/AO26-1</f>
         <v>7.7735439588169974E-2</v>
       </c>
       <c r="AT47" s="10">
-        <f t="shared" ref="AT47" si="331">AT26/AP26-1</f>
+        <f t="shared" ref="AT47" si="330">AT26/AP26-1</f>
         <v>0.12489652449663136</v>
       </c>
       <c r="AU47" s="10">
-        <f t="shared" ref="AU47" si="332">AU26/AQ26-1</f>
+        <f t="shared" ref="AU47" si="331">AU26/AQ26-1</f>
         <v>0.14812228144336204</v>
       </c>
       <c r="AV47" s="10">
-        <f t="shared" ref="AV47" si="333">AV26/AR26-1</f>
+        <f t="shared" ref="AV47" si="332">AV26/AR26-1</f>
         <v>0.16757661255847456</v>
       </c>
       <c r="AW47" s="10">
-        <f t="shared" ref="AW47" si="334">AW26/AS26-1</f>
+        <f t="shared" ref="AW47" si="333">AW26/AS26-1</f>
         <v>0.15020429188569029</v>
       </c>
       <c r="AX47" s="10">
-        <f t="shared" ref="AX47" si="335">AX26/AT26-1</f>
+        <f t="shared" ref="AX47" si="334">AX26/AT26-1</f>
         <v>0.16005117290100546</v>
       </c>
       <c r="AY47" s="10">
-        <f t="shared" ref="AY47" si="336">AY26/AU26-1</f>
+        <f t="shared" ref="AY47" si="335">AY26/AU26-1</f>
         <v>0.12511739093315111</v>
       </c>
       <c r="AZ47" s="10">
-        <f t="shared" ref="AZ47" si="337">AZ26/AV26-1</f>
+        <f t="shared" ref="AZ47" si="336">AZ26/AV26-1</f>
         <v>0.15899699768811537</v>
       </c>
       <c r="BA47" s="10">
-        <f t="shared" ref="BA47" si="338">BA26/AW26-1</f>
-        <v>0.12999999999999989</v>
+        <f t="shared" ref="BA47" si="337">BA26/AW26-1</f>
+        <v>0.17156757967164382</v>
       </c>
       <c r="BB47" s="10">
-        <f t="shared" ref="BB47" si="339">BB26/AX26-1</f>
+        <f t="shared" ref="BB47" si="338">BB26/AX26-1</f>
         <v>0.12000000000000011</v>
       </c>
       <c r="BC47" s="10"/>
@@ -10977,15 +10969,15 @@
         <v>-0.51767354003612276</v>
       </c>
       <c r="BE47" s="10">
-        <f t="shared" ref="BE47:BG47" si="340">BE26/BD26-1</f>
+        <f t="shared" ref="BE47:BG47" si="339">BE26/BD26-1</f>
         <v>0.12628967879380015</v>
       </c>
       <c r="BF47" s="10">
-        <f t="shared" si="340"/>
+        <f t="shared" si="339"/>
         <v>0.21203109094828276</v>
       </c>
       <c r="BG47" s="10">
-        <f t="shared" si="340"/>
+        <f t="shared" si="339"/>
         <v>0.25833306283006174</v>
       </c>
       <c r="BH47" s="10">
@@ -10993,83 +10985,83 @@
         <v>0.23159576184233854</v>
       </c>
       <c r="BI47" s="10">
-        <f t="shared" ref="BI47:BX47" si="341">BI26/BH26-1</f>
+        <f t="shared" ref="BI47:BX47" si="340">BI26/BH26-1</f>
         <v>0.17644768184607984</v>
       </c>
       <c r="BJ47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.46601117890001431</v>
       </c>
       <c r="BK47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.3508386486955255</v>
       </c>
       <c r="BL47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.27599656870505318</v>
       </c>
       <c r="BM47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.24005160265952163</v>
       </c>
       <c r="BN47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.18832426376440448</v>
       </c>
       <c r="BO47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>6.4548497235559887E-2</v>
       </c>
       <c r="BP47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>6.6666455800301172E-2</v>
       </c>
       <c r="BQ47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>0.15649713995961223</v>
       </c>
       <c r="BR47" s="10">
-        <f t="shared" si="341"/>
-        <v>0.13330694932681064</v>
+        <f t="shared" si="340"/>
+        <v>0.14377822050260414</v>
       </c>
       <c r="BS47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BT47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BU47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BV47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BW47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BX47" s="10">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BY47" s="10">
-        <f t="shared" ref="BY47" si="342">BY26/BX26-1</f>
+        <f t="shared" ref="BY47" si="341">BY26/BX26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BZ47" s="10">
-        <f t="shared" ref="BZ47" si="343">BZ26/BY26-1</f>
+        <f t="shared" ref="BZ47" si="342">BZ26/BY26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="CA47" s="10">
-        <f t="shared" ref="CA47" si="344">CA26/BZ26-1</f>
+        <f t="shared" ref="CA47" si="343">CA26/BZ26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="CB47" s="10">
-        <f t="shared" ref="CB47" si="345">CB26/CA26-1</f>
+        <f t="shared" ref="CB47" si="344">CB26/CA26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="CD47" t="s">
@@ -11088,211 +11080,211 @@
         <v>4.4348368736699895E-2</v>
       </c>
       <c r="E48" s="10">
-        <f t="shared" ref="E48:R48" si="346">E26/D26-1</f>
+        <f t="shared" ref="E48:R48" si="345">E26/D26-1</f>
         <v>3.4250943544435364E-2</v>
       </c>
       <c r="F48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>6.2595897464645001E-2</v>
       </c>
       <c r="G48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>8.07152642461475E-2</v>
       </c>
       <c r="H48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>5.5364624053904965E-2</v>
       </c>
       <c r="I48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>5.1495553216299061E-2</v>
       </c>
       <c r="J48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>5.3422939169821548E-2</v>
       </c>
       <c r="K48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>5.9540198608768691E-2</v>
       </c>
       <c r="L48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>4.5492137008471545E-2</v>
       </c>
       <c r="M48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>5.6947371365129396E-2</v>
       </c>
       <c r="N48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>4.8884146218695301E-2</v>
       </c>
       <c r="O48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>3.9612621501393219E-2</v>
       </c>
       <c r="P48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>1.9176391145624416E-2</v>
       </c>
       <c r="Q48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>3.1932129343499538E-2</v>
       </c>
       <c r="R48" s="10">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v>8.0793539325842545E-2</v>
       </c>
       <c r="S48" s="10">
-        <f t="shared" ref="S48" si="347">S26/R26-1</f>
+        <f t="shared" ref="S48" si="346">S26/R26-1</f>
         <v>0.22422459123670935</v>
       </c>
       <c r="T48" s="10">
-        <f t="shared" ref="T48" si="348">T26/S26-1</f>
+        <f t="shared" ref="T48" si="347">T26/S26-1</f>
         <v>5.6152854651603468E-2</v>
       </c>
       <c r="U48" s="10">
-        <f t="shared" ref="U48" si="349">U26/T26-1</f>
+        <f t="shared" ref="U48" si="348">U26/T26-1</f>
         <v>7.1061624167240822E-2</v>
       </c>
       <c r="V48" s="10">
-        <f t="shared" ref="V48" si="350">V26/U26-1</f>
+        <f t="shared" ref="V48" si="349">V26/U26-1</f>
         <v>0.10088166729895054</v>
       </c>
       <c r="W48" s="10">
-        <f t="shared" ref="W48" si="351">W26/V26-1</f>
+        <f t="shared" ref="W48" si="350">W26/V26-1</f>
         <v>0.12693308070353182</v>
       </c>
       <c r="X48" s="10">
-        <f t="shared" ref="X48" si="352">X26/W26-1</f>
+        <f t="shared" ref="X48" si="351">X26/W26-1</f>
         <v>5.5652647468472649E-2</v>
       </c>
       <c r="Y48" s="10">
-        <f t="shared" ref="Y48" si="353">Y26/X26-1</f>
+        <f t="shared" ref="Y48" si="352">Y26/X26-1</f>
         <v>2.3316213802253571E-2</v>
       </c>
       <c r="Z48" s="10">
-        <f t="shared" ref="Z48" si="354">Z26/Y26-1</f>
+        <f t="shared" ref="Z48" si="353">Z26/Y26-1</f>
         <v>4.6740808903493969E-2</v>
       </c>
       <c r="AA48" s="10">
-        <f t="shared" ref="AA48" si="355">AA26/Z26-1</f>
+        <f t="shared" ref="AA48" si="354">AA26/Z26-1</f>
         <v>8.0046831174609201E-2</v>
       </c>
       <c r="AB48" s="10">
-        <f t="shared" ref="AB48" si="356">AB26/AA26-1</f>
+        <f t="shared" ref="AB48" si="355">AB26/AA26-1</f>
         <v>8.8918380889183801E-2</v>
       </c>
       <c r="AC48" s="10">
-        <f t="shared" ref="AC48" si="357">AC26/AB26-1</f>
+        <f t="shared" ref="AC48" si="356">AC26/AB26-1</f>
         <v>6.7032297379646666E-2</v>
       </c>
       <c r="AD48" s="10">
-        <f t="shared" ref="AD48" si="358">AD26/AC26-1</f>
+        <f t="shared" ref="AD48" si="357">AD26/AC26-1</f>
         <v>4.073862554730634E-2</v>
       </c>
       <c r="AE48" s="10">
-        <f t="shared" ref="AE48" si="359">AE26/AD26-1</f>
+        <f t="shared" ref="AE48" si="358">AE26/AD26-1</f>
         <v>5.5057618437900135E-2</v>
       </c>
       <c r="AF48" s="10">
-        <f t="shared" ref="AF48" si="360">AF26/AE26-1</f>
+        <f t="shared" ref="AF48" si="359">AF26/AE26-1</f>
         <v>6.5880721220527017E-2</v>
       </c>
       <c r="AG48" s="10">
-        <f t="shared" ref="AG48" si="361">AG26/AF26-1</f>
+        <f t="shared" ref="AG48" si="360">AG26/AF26-1</f>
         <v>4.6193884189980494E-2</v>
       </c>
       <c r="AH48" s="10">
-        <f t="shared" ref="AH48" si="362">AH26/AG26-1</f>
+        <f t="shared" ref="AH48" si="361">AH26/AG26-1</f>
         <v>3.2960199004975044E-2</v>
       </c>
       <c r="AI48" s="10">
-        <f t="shared" ref="AI48" si="363">AI26/AH26-1</f>
+        <f t="shared" ref="AI48" si="362">AI26/AH26-1</f>
         <v>7.8266104756171018E-2</v>
       </c>
       <c r="AJ48" s="10">
-        <f t="shared" ref="AJ48" si="364">AJ26/AI26-1</f>
+        <f t="shared" ref="AJ48" si="363">AJ26/AI26-1</f>
         <v>2.4818537130094853E-2</v>
       </c>
       <c r="AK48" s="10">
-        <f t="shared" ref="AK48" si="365">AK26/AJ26-1</f>
+        <f t="shared" ref="AK48" si="364">AK26/AJ26-1</f>
         <v>1.9300444032798403E-2</v>
       </c>
       <c r="AL48" s="10">
-        <f t="shared" ref="AL48" si="366">AL26/AK26-1</f>
+        <f t="shared" ref="AL48" si="365">AL26/AK26-1</f>
         <v>3.0173047370882555E-2</v>
       </c>
       <c r="AM48" s="10">
-        <f t="shared" ref="AM48" si="367">AM26/AL26-1</f>
+        <f t="shared" ref="AM48" si="366">AM26/AL26-1</f>
         <v>2.0559583879210752E-2</v>
       </c>
       <c r="AN48" s="10">
-        <f t="shared" ref="AN48" si="368">AN26/AM26-1</f>
+        <f t="shared" ref="AN48" si="367">AN26/AM26-1</f>
         <v>1.3002364066193817E-2</v>
       </c>
       <c r="AO48" s="10">
-        <f t="shared" ref="AO48" si="369">AO26/AN26-1</f>
+        <f t="shared" ref="AO48" si="368">AO26/AN26-1</f>
         <v>-5.5833678372918527E-3</v>
       </c>
       <c r="AP48" s="10">
-        <f t="shared" ref="AP48" si="370">AP26/AO26-1</f>
+        <f t="shared" ref="AP48" si="369">AP26/AO26-1</f>
         <v>-9.2737458362773806E-3</v>
       </c>
       <c r="AQ48" s="10">
-        <f t="shared" ref="AQ48" si="371">AQ26/AP26-1</f>
+        <f t="shared" ref="AQ48" si="370">AQ26/AP26-1</f>
         <v>3.9403471682734503E-2</v>
       </c>
       <c r="AR48" s="10">
-        <f t="shared" ref="AR48" si="372">AR26/AQ26-1</f>
+        <f t="shared" ref="AR48" si="371">AR26/AQ26-1</f>
         <v>3.1611836059548537E-3</v>
       </c>
       <c r="AS48" s="10">
-        <f t="shared" ref="AS48" si="373">AS26/AR26-1</f>
+        <f t="shared" ref="AS48" si="372">AS26/AR26-1</f>
         <v>4.3286553564667374E-2</v>
       </c>
       <c r="AT48" s="10">
-        <f t="shared" ref="AT48" si="374">AT26/AS26-1</f>
+        <f t="shared" ref="AT48" si="373">AT26/AS26-1</f>
         <v>3.407986700539678E-2</v>
       </c>
       <c r="AU48" s="10">
-        <f t="shared" ref="AU48" si="375">AU26/AT26-1</f>
+        <f t="shared" ref="AU48" si="374">AU26/AT26-1</f>
         <v>6.0864052169187666E-2</v>
       </c>
       <c r="AV48" s="10">
-        <f t="shared" ref="AV48" si="376">AV26/AU26-1</f>
+        <f t="shared" ref="AV48" si="375">AV26/AU26-1</f>
         <v>2.0159224792964947E-2</v>
       </c>
       <c r="AW48" s="10">
-        <f t="shared" ref="AW48" si="377">AW26/AV26-1</f>
+        <f t="shared" ref="AW48" si="376">AW26/AV26-1</f>
         <v>2.7763539171278495E-2</v>
       </c>
       <c r="AX48" s="10">
-        <f t="shared" ref="AX48" si="378">AX26/AW26-1</f>
+        <f t="shared" ref="AX48" si="377">AX26/AW26-1</f>
         <v>4.2932608629270952E-2</v>
       </c>
       <c r="AY48" s="10">
-        <f t="shared" ref="AY48" si="379">AY26/AX26-1</f>
+        <f t="shared" ref="AY48" si="378">AY26/AX26-1</f>
         <v>2.8917191236031758E-2</v>
       </c>
       <c r="AZ48" s="10">
-        <f t="shared" ref="AZ48" si="380">AZ26/AY26-1</f>
+        <f t="shared" ref="AZ48" si="379">AZ26/AY26-1</f>
         <v>5.0878324543764508E-2</v>
       </c>
       <c r="BA48" s="10">
-        <f t="shared" ref="BA48" si="381">BA26/AZ26-1</f>
-        <v>2.0498772474546456E-3</v>
+        <f t="shared" ref="BA48" si="380">BA26/AZ26-1</f>
+        <v>3.8910751678821409E-2</v>
       </c>
       <c r="BB48" s="10">
-        <f t="shared" ref="BB48" si="382">BB26/BA26-1</f>
-        <v>3.3703116517507903E-2</v>
+        <f t="shared" ref="BB48" si="381">BB26/BA26-1</f>
+        <v>-2.972989409485205E-3</v>
       </c>
       <c r="CD48" t="s">
         <v>86</v>
       </c>
       <c r="CE48" s="2">
         <f>NPV(CE47,BQ37:ET37)</f>
-        <v>276530.74098197947</v>
+        <v>267707.08312152151</v>
       </c>
     </row>
     <row r="49" spans="2:83">
@@ -11304,308 +11296,308 @@
         <v>-1.8913978494623451</v>
       </c>
       <c r="D49" s="9">
-        <f t="shared" ref="D49:BW49" si="383">D36/D35</f>
+        <f t="shared" ref="D49:BW49" si="382">D36/D35</f>
         <v>0.36823940491757517</v>
       </c>
       <c r="E49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.3570144066597965</v>
+      </c>
+      <c r="F49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.34569752986325059</v>
+      </c>
+      <c r="G49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.40282649757150618</v>
+      </c>
+      <c r="H49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.39493235183859821</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.39207685288659683</v>
+      </c>
+      <c r="J49" s="9">
+        <f t="shared" si="382"/>
+        <v>-0.83168556112136249</v>
+      </c>
+      <c r="K49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.38333420080154013</v>
+      </c>
+      <c r="L49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.34959249197332665</v>
+      </c>
+      <c r="M49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.30318670391590535</v>
+      </c>
+      <c r="N49" s="9">
+        <f t="shared" si="382"/>
+        <v>-1.0829313006561061</v>
+      </c>
+      <c r="O49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.3</v>
+      </c>
+      <c r="P49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.3</v>
+      </c>
+      <c r="R49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.3</v>
+      </c>
+      <c r="S49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.2026666666666665</v>
+      </c>
+      <c r="T49" s="9">
+        <f t="shared" si="382"/>
+        <v>-3.5783633841885929</v>
+      </c>
+      <c r="U49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.11622662457065554</v>
+      </c>
+      <c r="V49" s="9">
+        <f t="shared" si="382"/>
+        <v>-0.62110848694905363</v>
+      </c>
+      <c r="W49" s="9">
+        <f t="shared" si="382"/>
+        <v>3.1595471537468882E-2</v>
+      </c>
+      <c r="X49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.12984732196904594</v>
+      </c>
+      <c r="Y49" s="9">
+        <f t="shared" si="382"/>
+        <v>-6.3406092881683265E-2</v>
+      </c>
+      <c r="Z49" s="9">
+        <f t="shared" si="382"/>
+        <v>-0.21686416097851588</v>
+      </c>
+      <c r="AA49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.22473726758286156</v>
+      </c>
+      <c r="AB49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.45995606151388052</v>
+      </c>
+      <c r="AC49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.34019406057042051</v>
+      </c>
+      <c r="AD49" s="9">
+        <f t="shared" si="382"/>
+        <v>-1.4517412935323439</v>
+      </c>
+      <c r="AE49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.10901783471489572</v>
+      </c>
+      <c r="AF49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.30458715596330271</v>
+      </c>
+      <c r="AG49" s="9">
+        <f t="shared" si="382"/>
+        <v>8.3352762881790637E-2</v>
+      </c>
+      <c r="AH49" s="9">
+        <f t="shared" si="382"/>
+        <v>-7.0525483998419611E-2</v>
+      </c>
+      <c r="AI49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.16105733798457228</v>
+      </c>
+      <c r="AJ49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.15107597716293369</v>
+      </c>
+      <c r="AK49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.12757375075255875</v>
+      </c>
+      <c r="AL49" s="9">
+        <f t="shared" si="382"/>
+        <v>-0.10275962236746554</v>
+      </c>
+      <c r="AM49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.19305955447795117</v>
+      </c>
+      <c r="AN49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.1122681619323433</v>
+      </c>
+      <c r="AO49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.13786300018496819</v>
+      </c>
+      <c r="AP49" s="9">
+        <f t="shared" si="382"/>
+        <v>-0.40712468193383566</v>
+      </c>
+      <c r="AQ49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.1115120157941317</v>
+      </c>
+      <c r="AR49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.11415470731852555</v>
+      </c>
+      <c r="AS49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.12132006286013612</v>
+      </c>
+      <c r="AT49" s="9">
+        <f t="shared" si="382"/>
+        <v>0.18315624455669755</v>
+      </c>
+      <c r="AU49" s="9">
+        <f t="shared" ref="AU49:AX49" si="383">AU36/AU35</f>
+        <v>0.10800887325021039</v>
+      </c>
+      <c r="AV49" s="9">
         <f t="shared" si="383"/>
-        <v>0.3570144066597965</v>
-      </c>
-      <c r="F49" s="9">
+        <v>0.14583499085050527</v>
+      </c>
+      <c r="AW49" s="9">
         <f t="shared" si="383"/>
-        <v>0.34569752986325059</v>
-      </c>
-      <c r="G49" s="9">
+        <v>0.12556883347515627</v>
+      </c>
+      <c r="AX49" s="9">
         <f t="shared" si="383"/>
-        <v>0.40282649757150618</v>
-      </c>
-      <c r="H49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.39493235183859821</v>
-      </c>
-      <c r="I49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.39207685288659683</v>
-      </c>
-      <c r="J49" s="9">
-        <f t="shared" si="383"/>
-        <v>-0.83168556112136249</v>
-      </c>
-      <c r="K49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.38333420080154013</v>
-      </c>
-      <c r="L49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.34959249197332665</v>
-      </c>
-      <c r="M49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.30318670391590535</v>
-      </c>
-      <c r="N49" s="9">
-        <f t="shared" si="383"/>
-        <v>-1.0829313006561061</v>
-      </c>
-      <c r="O49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.3</v>
-      </c>
-      <c r="P49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.3</v>
-      </c>
-      <c r="Q49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.3</v>
-      </c>
-      <c r="R49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.3</v>
-      </c>
-      <c r="S49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.2026666666666665</v>
-      </c>
-      <c r="T49" s="9">
-        <f t="shared" si="383"/>
-        <v>-3.5783633841885929</v>
-      </c>
-      <c r="U49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.11622662457065554</v>
-      </c>
-      <c r="V49" s="9">
-        <f t="shared" si="383"/>
-        <v>-0.62110848694905363</v>
-      </c>
-      <c r="W49" s="9">
-        <f t="shared" si="383"/>
-        <v>3.1595471537468882E-2</v>
-      </c>
-      <c r="X49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.12984732196904594</v>
-      </c>
-      <c r="Y49" s="9">
-        <f t="shared" si="383"/>
-        <v>-6.3406092881683265E-2</v>
-      </c>
-      <c r="Z49" s="9">
-        <f t="shared" si="383"/>
-        <v>-0.21686416097851588</v>
-      </c>
-      <c r="AA49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.22473726758286156</v>
-      </c>
-      <c r="AB49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.45995606151388052</v>
-      </c>
-      <c r="AC49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.34019406057042051</v>
-      </c>
-      <c r="AD49" s="9">
-        <f t="shared" si="383"/>
-        <v>-1.4517412935323439</v>
-      </c>
-      <c r="AE49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.10901783471489572</v>
-      </c>
-      <c r="AF49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.30458715596330271</v>
-      </c>
-      <c r="AG49" s="9">
-        <f t="shared" si="383"/>
-        <v>8.3352762881790637E-2</v>
-      </c>
-      <c r="AH49" s="9">
-        <f t="shared" si="383"/>
-        <v>-7.0525483998419611E-2</v>
-      </c>
-      <c r="AI49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.16105733798457228</v>
-      </c>
-      <c r="AJ49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.15107597716293369</v>
-      </c>
-      <c r="AK49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.12757375075255875</v>
-      </c>
-      <c r="AL49" s="9">
-        <f t="shared" si="383"/>
-        <v>-0.10275962236746554</v>
-      </c>
-      <c r="AM49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.19305955447795117</v>
-      </c>
-      <c r="AN49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.1122681619323433</v>
-      </c>
-      <c r="AO49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.13786300018496819</v>
-      </c>
-      <c r="AP49" s="9">
-        <f t="shared" si="383"/>
-        <v>-0.40712468193383566</v>
-      </c>
-      <c r="AQ49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.1115120157941317</v>
-      </c>
-      <c r="AR49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.11415470731852555</v>
-      </c>
-      <c r="AS49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.12132006286013612</v>
-      </c>
-      <c r="AT49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.18315624455669755</v>
-      </c>
-      <c r="AU49" s="9">
-        <f t="shared" ref="AU49:AX49" si="384">AU36/AU35</f>
-        <v>0.10800887325021039</v>
-      </c>
-      <c r="AV49" s="9">
+        <v>0.12449629837878357</v>
+      </c>
+      <c r="AY49" s="9">
+        <f t="shared" ref="AY49:BB49" si="384">AY36/AY35</f>
+        <v>0.10063167065998695</v>
+      </c>
+      <c r="AZ49" s="9">
         <f t="shared" si="384"/>
-        <v>0.14583499085050527</v>
-      </c>
-      <c r="AW49" s="9">
+        <v>0.13941129498581928</v>
+      </c>
+      <c r="BA49" s="9">
         <f t="shared" si="384"/>
-        <v>0.12556883347515627</v>
-      </c>
-      <c r="AX49" s="9">
+        <v>0.18090306811603532</v>
+      </c>
+      <c r="BB49" s="9">
         <f t="shared" si="384"/>
-        <v>0.12449629837878357</v>
-      </c>
-      <c r="AY49" s="9">
-        <f t="shared" ref="AY49:BB49" si="385">AY36/AY35</f>
-        <v>0.10063167065998695</v>
-      </c>
-      <c r="AZ49" s="9">
-        <f t="shared" si="385"/>
-        <v>0.13941129498581928</v>
-      </c>
-      <c r="BA49" s="9">
-        <f t="shared" si="385"/>
-        <v>0.12</v>
-      </c>
-      <c r="BB49" s="9">
-        <f t="shared" si="385"/>
         <v>0.12</v>
       </c>
       <c r="BC49" s="9"/>
       <c r="BD49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.37103709925957218</v>
       </c>
       <c r="BE49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.43727034120734615</v>
       </c>
       <c r="BF49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.34295684908285323</v>
       </c>
       <c r="BG49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.23634037364505703</v>
       </c>
       <c r="BH49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.13563383656841535</v>
       </c>
       <c r="BI49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.36781576933181465</v>
       </c>
       <c r="BJ49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>-0.1517137886396058</v>
       </c>
       <c r="BK49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>1.2389823090606799E-2</v>
       </c>
       <c r="BL49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>9.4810427690664612E-2</v>
       </c>
       <c r="BM49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.1370591732640736</v>
       </c>
       <c r="BN49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.12393425783256297</v>
       </c>
       <c r="BO49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.14666210722291886</v>
       </c>
       <c r="BP49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.12850098301479357</v>
       </c>
       <c r="BQ49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.12584416236014256</v>
       </c>
       <c r="BR49" s="9">
-        <f t="shared" si="383"/>
-        <v>0.12063287088877692</v>
+        <f t="shared" si="382"/>
+        <v>0.13588288725467892</v>
       </c>
       <c r="BS49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.13</v>
       </c>
       <c r="BT49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.13</v>
       </c>
       <c r="BU49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.13</v>
       </c>
       <c r="BV49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.13</v>
       </c>
       <c r="BW49" s="9">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v>0.13</v>
       </c>
       <c r="BX49" s="9">
-        <f t="shared" ref="BX49:CB49" si="386">BX36/BX35</f>
+        <f t="shared" ref="BX49:CB49" si="385">BX36/BX35</f>
         <v>0.13</v>
       </c>
       <c r="BY49" s="9">
-        <f t="shared" si="386"/>
+        <f t="shared" si="385"/>
         <v>0.13</v>
       </c>
       <c r="BZ49" s="9">
-        <f t="shared" si="386"/>
+        <f t="shared" si="385"/>
         <v>0.13</v>
       </c>
       <c r="CA49" s="9">
-        <f t="shared" si="386"/>
+        <f t="shared" si="385"/>
         <v>0.13</v>
       </c>
       <c r="CB49" s="9">
-        <f t="shared" si="386"/>
+        <f t="shared" si="385"/>
         <v>0.13</v>
       </c>
       <c r="CD49" t="s">
@@ -11625,315 +11617,315 @@
         <v>2.6260765790884709E-3</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" ref="D50:BW50" si="387">D37/D26</f>
+        <f t="shared" ref="D50:BW50" si="386">D37/D26</f>
         <v>2.7559165566332481E-2</v>
       </c>
       <c r="E50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.8772177913361615E-2</v>
+      </c>
+      <c r="F50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.1201296767441269E-2</v>
+      </c>
+      <c r="G50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.1819903959486218E-2</v>
+      </c>
+      <c r="H50" s="10">
+        <f t="shared" si="386"/>
+        <v>5.2982415042595363E-2</v>
+      </c>
+      <c r="I50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.2070138892830594E-2</v>
+      </c>
+      <c r="J50" s="10">
+        <f t="shared" si="386"/>
+        <v>5.6152372690486112E-2</v>
+      </c>
+      <c r="K50" s="10">
+        <f t="shared" si="386"/>
+        <v>1.5062973220886558E-2</v>
+      </c>
+      <c r="L50" s="10">
+        <f t="shared" si="386"/>
+        <v>1.6012097083104825E-2</v>
+      </c>
+      <c r="M50" s="10">
+        <f t="shared" si="386"/>
+        <v>1.6930949086924114E-2</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.3679163378274956E-2</v>
+      </c>
+      <c r="O50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.1416519128911782E-2</v>
+      </c>
+      <c r="P50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.1542444508284551E-2</v>
+      </c>
+      <c r="Q50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.1831975376053397E-2</v>
+      </c>
+      <c r="R50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.2697748783246163E-2</v>
+      </c>
+      <c r="S50" s="10">
+        <f t="shared" si="386"/>
+        <v>6.8011221472439223E-2</v>
+      </c>
+      <c r="T50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.3697737192740688E-2</v>
+      </c>
+      <c r="U50" s="10">
+        <f t="shared" si="386"/>
+        <v>3.4147348496527299E-2</v>
+      </c>
+      <c r="V50" s="10">
+        <f t="shared" si="386"/>
+        <v>6.4358497274812854E-2</v>
+      </c>
+      <c r="W50" s="10">
+        <f t="shared" si="386"/>
+        <v>7.865633532835789E-2</v>
+      </c>
+      <c r="X50" s="10">
+        <f t="shared" si="386"/>
+        <v>9.5344214962571117E-2</v>
+      </c>
+      <c r="Y50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.10065297820072844</v>
+      </c>
+      <c r="Z50" s="10">
+        <f t="shared" si="386"/>
+        <v>3.4718596318485888E-2</v>
+      </c>
+      <c r="AA50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.2424242424242475E-2</v>
+      </c>
+      <c r="AB50" s="10">
+        <f t="shared" si="386"/>
+        <v>5.4925858216534638E-2</v>
+      </c>
+      <c r="AC50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.12815533980582522</v>
+      </c>
+      <c r="AD50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.13521126760563359</v>
+      </c>
+      <c r="AE50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.12298890429958396</v>
+      </c>
+      <c r="AF50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.11712752114508784</v>
+      </c>
+      <c r="AG50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.1222481343283582</v>
+      </c>
+      <c r="AH50" s="10">
+        <f t="shared" si="386"/>
+        <v>8.1562311860325101E-2</v>
+      </c>
+      <c r="AI50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.23834450027917367</v>
+      </c>
+      <c r="AJ50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.18430085265193824</v>
+      </c>
+      <c r="AK50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.1936393398810716</v>
+      </c>
+      <c r="AL50" s="10">
+        <f t="shared" si="386"/>
+        <v>7.8787957402098749E-2</v>
+      </c>
+      <c r="AM50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.2030427819720888</v>
+      </c>
+      <c r="AN50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.18076310209407664</v>
+      </c>
+      <c r="AO50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.17642828303219954</v>
+      </c>
+      <c r="AP50" s="10">
+        <f t="shared" si="386"/>
+        <v>7.0427019523440397E-3</v>
+      </c>
+      <c r="AQ50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.15990933039269739</v>
+      </c>
+      <c r="AR50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.18169604143001972</v>
+      </c>
+      <c r="AS50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.19637777023309191</v>
+      </c>
+      <c r="AT50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.10618376958608816</v>
+      </c>
+      <c r="AU50" s="10">
+        <f t="shared" ref="AU50:AX50" si="387">AU37/AU26</f>
+        <v>0.24889012208657038</v>
+      </c>
+      <c r="AV50" s="10">
         <f t="shared" si="387"/>
-        <v>2.8772177913361615E-2</v>
-      </c>
-      <c r="F50" s="10">
+        <v>0.22461895745504373</v>
+      </c>
+      <c r="AW50" s="10">
         <f t="shared" si="387"/>
-        <v>4.1201296767441269E-2</v>
-      </c>
-      <c r="G50" s="10">
+        <v>0.24056714199924686</v>
+      </c>
+      <c r="AX50" s="10">
         <f t="shared" si="387"/>
-        <v>4.1819903959486218E-2</v>
-      </c>
-      <c r="H50" s="10">
-        <f t="shared" si="387"/>
-        <v>5.2982415042595363E-2</v>
-      </c>
-      <c r="I50" s="10">
-        <f t="shared" si="387"/>
-        <v>4.2070138892830594E-2</v>
-      </c>
-      <c r="J50" s="10">
-        <f t="shared" si="387"/>
-        <v>5.6152372690486112E-2</v>
-      </c>
-      <c r="K50" s="10">
-        <f t="shared" si="387"/>
-        <v>1.5062973220886558E-2</v>
-      </c>
-      <c r="L50" s="10">
-        <f t="shared" si="387"/>
-        <v>1.6012097083104825E-2</v>
-      </c>
-      <c r="M50" s="10">
-        <f t="shared" si="387"/>
-        <v>1.6930949086924114E-2</v>
-      </c>
-      <c r="N50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.3679163378274956E-2</v>
-      </c>
-      <c r="O50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.1416519128911782E-2</v>
-      </c>
-      <c r="P50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.1542444508284551E-2</v>
-      </c>
-      <c r="Q50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.1831975376053397E-2</v>
-      </c>
-      <c r="R50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.2697748783246163E-2</v>
-      </c>
-      <c r="S50" s="10">
-        <f t="shared" si="387"/>
-        <v>6.8011221472439223E-2</v>
-      </c>
-      <c r="T50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.3697737192740688E-2</v>
-      </c>
-      <c r="U50" s="10">
-        <f t="shared" si="387"/>
-        <v>3.4147348496527299E-2</v>
-      </c>
-      <c r="V50" s="10">
-        <f t="shared" si="387"/>
-        <v>6.4358497274812854E-2</v>
-      </c>
-      <c r="W50" s="10">
-        <f t="shared" si="387"/>
-        <v>7.865633532835789E-2</v>
-      </c>
-      <c r="X50" s="10">
-        <f t="shared" si="387"/>
-        <v>9.5344214962571117E-2</v>
-      </c>
-      <c r="Y50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.10065297820072844</v>
-      </c>
-      <c r="Z50" s="10">
-        <f t="shared" si="387"/>
-        <v>3.4718596318485888E-2</v>
-      </c>
-      <c r="AA50" s="10">
-        <f t="shared" si="387"/>
-        <v>4.2424242424242475E-2</v>
-      </c>
-      <c r="AB50" s="10">
-        <f t="shared" si="387"/>
-        <v>5.4925858216534638E-2</v>
-      </c>
-      <c r="AC50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.12815533980582522</v>
-      </c>
-      <c r="AD50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.13521126760563359</v>
-      </c>
-      <c r="AE50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.12298890429958396</v>
-      </c>
-      <c r="AF50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.11712752114508784</v>
-      </c>
-      <c r="AG50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.1222481343283582</v>
-      </c>
-      <c r="AH50" s="10">
-        <f t="shared" si="387"/>
-        <v>8.1562311860325101E-2</v>
-      </c>
-      <c r="AI50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.23834450027917367</v>
-      </c>
-      <c r="AJ50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.18430085265193824</v>
-      </c>
-      <c r="AK50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.1936393398810716</v>
-      </c>
-      <c r="AL50" s="10">
-        <f t="shared" si="387"/>
-        <v>7.8787957402098749E-2</v>
-      </c>
-      <c r="AM50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.2030427819720888</v>
-      </c>
-      <c r="AN50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.18076310209407664</v>
-      </c>
-      <c r="AO50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.17642828303219954</v>
-      </c>
-      <c r="AP50" s="10">
-        <f t="shared" si="387"/>
-        <v>7.0427019523440397E-3</v>
-      </c>
-      <c r="AQ50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.15990933039269739</v>
-      </c>
-      <c r="AR50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.18169604143001972</v>
-      </c>
-      <c r="AS50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.19637777023309191</v>
-      </c>
-      <c r="AT50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.10618376958608816</v>
-      </c>
-      <c r="AU50" s="10">
-        <f t="shared" ref="AU50:AX50" si="388">AU37/AU26</f>
-        <v>0.24889012208657038</v>
-      </c>
-      <c r="AV50" s="10">
+        <v>0.18235495047089256</v>
+      </c>
+      <c r="AY50" s="10">
+        <f t="shared" ref="AY50:BB50" si="388">AY37/AY26</f>
+        <v>0.27414918238039226</v>
+      </c>
+      <c r="AZ50" s="10">
         <f t="shared" si="388"/>
-        <v>0.22461895745504373</v>
-      </c>
-      <c r="AW50" s="10">
+        <v>0.28209618022961952</v>
+      </c>
+      <c r="BA50" s="10">
         <f t="shared" si="388"/>
-        <v>0.24056714199924686</v>
-      </c>
-      <c r="AX50" s="10">
+        <v>0.22127138302216265</v>
+      </c>
+      <c r="BB50" s="10">
         <f t="shared" si="388"/>
-        <v>0.18235495047089256</v>
-      </c>
-      <c r="AY50" s="10">
-        <f t="shared" ref="AY50:BB50" si="389">AY37/AY26</f>
-        <v>0.27414918238039226</v>
-      </c>
-      <c r="AZ50" s="10">
+        <v>0.19076558546123765</v>
+      </c>
+      <c r="BD50" s="10">
+        <f t="shared" si="386"/>
+        <v>7.056344721939907E-2</v>
+      </c>
+      <c r="BE50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.7521917101518256E-3</v>
+      </c>
+      <c r="BF50" s="10">
+        <f t="shared" si="386"/>
+        <v>2.569468669091898E-2</v>
+      </c>
+      <c r="BG50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.8467878828395504E-2</v>
+      </c>
+      <c r="BH50" s="10">
+        <f t="shared" si="386"/>
+        <v>1.8089505275528082E-2</v>
+      </c>
+      <c r="BI50" s="10">
+        <f t="shared" si="386"/>
+        <v>1.6129505907978094E-2</v>
+      </c>
+      <c r="BJ50" s="10">
+        <f t="shared" si="386"/>
+        <v>4.7784721245814774E-2</v>
+      </c>
+      <c r="BK50" s="10">
+        <f t="shared" si="386"/>
+        <v>7.6710054526016591E-2</v>
+      </c>
+      <c r="BL50" s="10">
+        <f t="shared" si="386"/>
+        <v>9.2517614369355919E-2</v>
+      </c>
+      <c r="BM50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.11034330985915493</v>
+      </c>
+      <c r="BN50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.17230105122800393</v>
+      </c>
+      <c r="BO50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.14207543111628429</v>
+      </c>
+      <c r="BP50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.16036390270228595</v>
+      </c>
+      <c r="BQ50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.22336407621362567</v>
+      </c>
+      <c r="BR50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.24102738364405979</v>
+      </c>
+      <c r="BS50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.26252572178327416</v>
+      </c>
+      <c r="BT50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.27202409250483583</v>
+      </c>
+      <c r="BU50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.28268151838002836</v>
+      </c>
+      <c r="BV50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.29291347678042357</v>
+      </c>
+      <c r="BW50" s="10">
+        <f t="shared" si="386"/>
+        <v>0.30274219780009026</v>
+      </c>
+      <c r="BX50" s="10">
+        <f t="shared" ref="BX50:CB50" si="389">BX37/BX26</f>
+        <v>0.3115284481258484</v>
+      </c>
+      <c r="BY50" s="10">
         <f t="shared" si="389"/>
-        <v>0.28209618022961952</v>
-      </c>
-      <c r="BA50" s="10">
+        <v>0.31191883146661104</v>
+      </c>
+      <c r="BZ50" s="10">
         <f t="shared" si="389"/>
-        <v>0.27041952860187762</v>
-      </c>
-      <c r="BB50" s="10">
+        <v>0.31230538751971898</v>
+      </c>
+      <c r="CA50" s="10">
         <f t="shared" si="389"/>
-        <v>0.2133297753239782</v>
-      </c>
-      <c r="BD50" s="10">
-        <f t="shared" si="387"/>
-        <v>7.056344721939907E-2</v>
-      </c>
-      <c r="BE50" s="10">
-        <f t="shared" si="387"/>
-        <v>4.7521917101518256E-3</v>
-      </c>
-      <c r="BF50" s="10">
-        <f t="shared" si="387"/>
-        <v>2.569468669091898E-2</v>
-      </c>
-      <c r="BG50" s="10">
-        <f t="shared" si="387"/>
-        <v>4.8467878828395504E-2</v>
-      </c>
-      <c r="BH50" s="10">
-        <f t="shared" si="387"/>
-        <v>1.8089505275528082E-2</v>
-      </c>
-      <c r="BI50" s="10">
-        <f t="shared" si="387"/>
-        <v>1.6129505907978094E-2</v>
-      </c>
-      <c r="BJ50" s="10">
-        <f t="shared" si="387"/>
-        <v>4.7784721245814774E-2</v>
-      </c>
-      <c r="BK50" s="10">
-        <f t="shared" si="387"/>
-        <v>7.6710054526016591E-2</v>
-      </c>
-      <c r="BL50" s="10">
-        <f t="shared" si="387"/>
-        <v>9.2517614369355919E-2</v>
-      </c>
-      <c r="BM50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.11034330985915493</v>
-      </c>
-      <c r="BN50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.17230105122800393</v>
-      </c>
-      <c r="BO50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.14207543111628429</v>
-      </c>
-      <c r="BP50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.16036390270228595</v>
-      </c>
-      <c r="BQ50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.22336407621362567</v>
-      </c>
-      <c r="BR50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.25941324529228976</v>
-      </c>
-      <c r="BS50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.28317573096514848</v>
-      </c>
-      <c r="BT50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.29485726796504369</v>
-      </c>
-      <c r="BU50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.30606996100435202</v>
-      </c>
-      <c r="BV50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.31684898902040992</v>
-      </c>
-      <c r="BW50" s="10">
-        <f t="shared" si="387"/>
-        <v>0.31880531933069328</v>
-      </c>
-      <c r="BX50" s="10">
-        <f t="shared" ref="BX50:CB50" si="390">BX37/BX26</f>
-        <v>0.31977389463137285</v>
-      </c>
-      <c r="BY50" s="10">
-        <f t="shared" si="390"/>
-        <v>0.32073297409577106</v>
-      </c>
-      <c r="BZ50" s="10">
-        <f t="shared" si="390"/>
-        <v>0.32168265082032232</v>
-      </c>
-      <c r="CA50" s="10">
-        <f t="shared" si="390"/>
-        <v>0.32262301698875051</v>
+        <v>0.31268815380760051</v>
       </c>
       <c r="CB50" s="10">
-        <f t="shared" si="390"/>
-        <v>0.32355416388101771</v>
+        <f t="shared" si="389"/>
+        <v>0.31306716748481667</v>
       </c>
       <c r="CD50" t="s">
         <v>87</v>
       </c>
       <c r="CE50" s="2">
         <f>CE48+CE49</f>
-        <v>268679.64098197949</v>
+        <v>259855.98312152151</v>
       </c>
     </row>
     <row r="51" spans="2:83">
@@ -11942,7 +11934,7 @@
       </c>
       <c r="CE51" s="17">
         <f>CE50/BW38</f>
-        <v>631.89003053146632</v>
+        <v>613.30182469086981</v>
       </c>
     </row>
     <row r="52" spans="2:83" s="1" customFormat="1">
@@ -11954,19 +11946,19 @@
         <v>397.81099999999992</v>
       </c>
       <c r="BE52" s="7">
-        <f t="shared" ref="BE52:BH52" si="391">BE54-BE67</f>
+        <f t="shared" ref="BE52:BH52" si="390">BE54-BE67</f>
         <v>348.07799999999997</v>
       </c>
       <c r="BF52" s="7">
-        <f t="shared" si="391"/>
+        <f t="shared" si="390"/>
         <v>700.40499999999997</v>
       </c>
       <c r="BG52" s="7">
-        <f t="shared" si="391"/>
+        <f t="shared" si="390"/>
         <v>722.75099999999986</v>
       </c>
       <c r="BH52" s="7">
-        <f t="shared" si="391"/>
+        <f t="shared" si="390"/>
         <v>-60.690000000000055</v>
       </c>
       <c r="CD52" t="s">
@@ -11974,7 +11966,7 @@
       </c>
       <c r="CE52" s="17">
         <f>Main!D3</f>
-        <v>1230.08</v>
+        <v>1094.69</v>
       </c>
     </row>
     <row r="53" spans="2:83">
@@ -11983,7 +11975,7 @@
       </c>
       <c r="CE53" s="10">
         <f>CE51/CE52-1</f>
-        <v>-0.48630167913349831</v>
+        <v>-0.43974839937254406</v>
       </c>
     </row>
     <row r="54" spans="2:83">
@@ -12561,27 +12553,27 @@
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
       <c r="G74" s="7">
-        <f t="shared" ref="G74:L74" si="392">G37</f>
+        <f t="shared" ref="G74:L74" si="391">G37</f>
         <v>53.114999999999888</v>
       </c>
       <c r="H74" s="7">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>71.018000000000129</v>
       </c>
       <c r="I74" s="7">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>59.295000000000009</v>
       </c>
       <c r="J74" s="16">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>83.371000000000066</v>
       </c>
       <c r="K74" s="16">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>23.696000000000051</v>
       </c>
       <c r="L74" s="16">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v>26.335000000000008</v>
       </c>
       <c r="M74" s="16">
